--- a/lang/es/headTags.xlsx
+++ b/lang/es/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1189</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1850">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1851">
   <si>
     <t>en</t>
   </si>
@@ -5164,349 +5164,352 @@
     <t>El retorcido país de las maravillas</t>
   </si>
   <si>
+    <t>ULTRAKILL</t>
+  </si>
+  <si>
+    <t>Umineko - When They Cry</t>
+  </si>
+  <si>
+    <t>Umineko - Cuando lloran</t>
+  </si>
+  <si>
+    <t>Undertale</t>
+  </si>
+  <si>
+    <t>Undertale AU</t>
+  </si>
+  <si>
+    <t>Undertale Yellow</t>
+  </si>
+  <si>
+    <t>Undertale Amarillo</t>
+  </si>
+  <si>
+    <t>Universal Symbol</t>
+  </si>
+  <si>
+    <t>Up</t>
+  </si>
+  <si>
+    <t>Arriba</t>
+  </si>
+  <si>
+    <t>Urban Wildlife</t>
+  </si>
+  <si>
+    <t>Vida salvaje urbana</t>
+  </si>
+  <si>
+    <t>V for Vendetta</t>
+  </si>
+  <si>
+    <t>V de Vendetta</t>
+  </si>
+  <si>
+    <t>Valentines</t>
+  </si>
+  <si>
+    <t>Valorant</t>
+  </si>
+  <si>
+    <t>Vanilla (removed)</t>
+  </si>
+  <si>
+    <t>Vainilla (eliminado)</t>
+  </si>
+  <si>
+    <t>Vanilla Block</t>
+  </si>
+  <si>
+    <t>Bloque de vainilla</t>
+  </si>
+  <si>
+    <t>Vanilla Food</t>
+  </si>
+  <si>
+    <t>Comida de vainilla</t>
+  </si>
+  <si>
+    <t>Vanilla Helmet</t>
+  </si>
+  <si>
+    <t>Casco Vainilla</t>
+  </si>
+  <si>
+    <t>Vanilla Item</t>
+  </si>
+  <si>
+    <t>Objeto de vainilla</t>
+  </si>
+  <si>
+    <t>Vanilla Mob</t>
+  </si>
+  <si>
+    <t>Mafia de vainilla</t>
+  </si>
+  <si>
+    <t>Vault Hunters</t>
+  </si>
+  <si>
+    <t>Cazadores de bóvedas</t>
+  </si>
+  <si>
+    <t>Vegetable</t>
+  </si>
+  <si>
+    <t>Vegetal</t>
+  </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>Vehículo</t>
+  </si>
+  <si>
+    <t>Vikings</t>
+  </si>
+  <si>
+    <t>Vikingos</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>Aldeano</t>
+  </si>
+  <si>
+    <t>Villager (Desert)</t>
+  </si>
+  <si>
+    <t>Aldeano (desierto)</t>
+  </si>
+  <si>
+    <t>Villager (Jungle)</t>
+  </si>
+  <si>
+    <t>Aldeano (Selva)</t>
+  </si>
+  <si>
+    <t>Villager (Plains)</t>
+  </si>
+  <si>
+    <t>Aldeano (Llanura)</t>
+  </si>
+  <si>
+    <t>Villager (Savanna)</t>
+  </si>
+  <si>
+    <t>Aldeano (sabana)</t>
+  </si>
+  <si>
+    <t>Villager (Snowy Tundra)</t>
+  </si>
+  <si>
+    <t>Aldeano (Tundra nevada)</t>
+  </si>
+  <si>
+    <t>Villager (Swamp)</t>
+  </si>
+  <si>
+    <t>Aldeano (pantano)</t>
+  </si>
+  <si>
+    <t>Villager (Taiga)</t>
+  </si>
+  <si>
+    <t>Aldeano (Taiga)</t>
+  </si>
+  <si>
+    <t>Virtual Youtuber</t>
+  </si>
+  <si>
+    <t>Youtuber virtual</t>
+  </si>
+  <si>
+    <t>Vocaloid</t>
+  </si>
+  <si>
+    <t>Voltron</t>
+  </si>
+  <si>
+    <t>Wakfu</t>
+  </si>
+  <si>
+    <t>Walking Dead</t>
+  </si>
+  <si>
+    <t>Wall-E</t>
+  </si>
+  <si>
+    <t>Wallace and Gromit</t>
+  </si>
+  <si>
+    <t>Wallace y Gromit</t>
+  </si>
+  <si>
+    <t>War of the Worlds</t>
+  </si>
+  <si>
+    <t>La Guerra de los Mundos</t>
+  </si>
+  <si>
+    <t>Warcraft</t>
+  </si>
+  <si>
+    <t>Warframe</t>
+  </si>
+  <si>
+    <t>Warhammer</t>
+  </si>
+  <si>
+    <t>Warrior Cats</t>
+  </si>
+  <si>
+    <t>We Bear Bears</t>
+  </si>
+  <si>
+    <t>Nosotros los Osos</t>
+  </si>
+  <si>
+    <t>We Happy Few</t>
+  </si>
+  <si>
+    <t>Weather</t>
+  </si>
+  <si>
+    <t>Tiempo</t>
+  </si>
+  <si>
+    <t>Welcome Home</t>
+  </si>
+  <si>
+    <t>Bienvenido a casa</t>
+  </si>
+  <si>
+    <t>Who is this?</t>
+  </si>
+  <si>
+    <t>¿Quién es?</t>
+  </si>
+  <si>
+    <t>Wild Update</t>
+  </si>
+  <si>
+    <t>Wings of Fire</t>
+  </si>
+  <si>
+    <t>Alas de fuego</t>
+  </si>
+  <si>
+    <t>Winnie the Pooh</t>
+  </si>
+  <si>
+    <t>Winter</t>
+  </si>
+  <si>
+    <t>Invierno</t>
+  </si>
+  <si>
+    <t>Witcher</t>
+  </si>
+  <si>
+    <t>Wonderful Wonder World</t>
+  </si>
+  <si>
+    <t>Maravilloso Mundo Maravilloso</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>Madera</t>
+  </si>
+  <si>
+    <t>Wool</t>
+  </si>
+  <si>
+    <t>Lana</t>
+  </si>
+  <si>
+    <t>Work Safety Helmet</t>
+  </si>
+  <si>
+    <t>Casco de seguridad</t>
+  </si>
+  <si>
+    <t>Wreck It Ralph</t>
+  </si>
+  <si>
+    <t>Wybel</t>
+  </si>
+  <si>
+    <t>Wynncraft</t>
+  </si>
+  <si>
+    <t>X-Men</t>
+  </si>
+  <si>
+    <t>Xenoblade Chronicles</t>
+  </si>
+  <si>
+    <t>Yandere Simulator</t>
+  </si>
+  <si>
+    <t>Simulador Yandere</t>
+  </si>
+  <si>
+    <t>Yellow Submarine</t>
+  </si>
+  <si>
+    <t>Yokai</t>
+  </si>
+  <si>
+    <t>Yooka Laylee</t>
+  </si>
+  <si>
+    <t>Young</t>
+  </si>
+  <si>
+    <t>Joven</t>
+  </si>
+  <si>
+    <t>Youtube</t>
+  </si>
+  <si>
+    <t>Yu-Gi-Oh</t>
+  </si>
+  <si>
+    <t>Yume Nikki</t>
+  </si>
+  <si>
+    <t>Zero no Tsukaima</t>
+  </si>
+  <si>
+    <t>Zero Wing</t>
+  </si>
+  <si>
+    <t>Ala Zero</t>
+  </si>
+  <si>
+    <t>Zodiac Sign</t>
+  </si>
+  <si>
+    <t>Signo del Zodiaco</t>
+  </si>
+  <si>
+    <t>Zombie</t>
+  </si>
+  <si>
+    <t>Zombie (Vanilla)</t>
+  </si>
+  <si>
+    <t>Zombie (Vainilla)</t>
+  </si>
+  <si>
+    <t>Zootopia</t>
+  </si>
+  <si>
     <t>Ultrakill</t>
-  </si>
-  <si>
-    <t>Umineko - When They Cry</t>
-  </si>
-  <si>
-    <t>Umineko - Cuando lloran</t>
-  </si>
-  <si>
-    <t>Undertale</t>
-  </si>
-  <si>
-    <t>Undertale AU</t>
-  </si>
-  <si>
-    <t>Undertale Yellow</t>
-  </si>
-  <si>
-    <t>Undertale Amarillo</t>
-  </si>
-  <si>
-    <t>Universal Symbol</t>
-  </si>
-  <si>
-    <t>Up</t>
-  </si>
-  <si>
-    <t>Arriba</t>
-  </si>
-  <si>
-    <t>Urban Wildlife</t>
-  </si>
-  <si>
-    <t>Vida salvaje urbana</t>
-  </si>
-  <si>
-    <t>V for Vendetta</t>
-  </si>
-  <si>
-    <t>V de Vendetta</t>
-  </si>
-  <si>
-    <t>Valentines</t>
-  </si>
-  <si>
-    <t>Valorant</t>
-  </si>
-  <si>
-    <t>Vanilla (removed)</t>
-  </si>
-  <si>
-    <t>Vainilla (eliminado)</t>
-  </si>
-  <si>
-    <t>Vanilla Block</t>
-  </si>
-  <si>
-    <t>Bloque de vainilla</t>
-  </si>
-  <si>
-    <t>Vanilla Food</t>
-  </si>
-  <si>
-    <t>Comida de vainilla</t>
-  </si>
-  <si>
-    <t>Vanilla Helmet</t>
-  </si>
-  <si>
-    <t>Casco Vainilla</t>
-  </si>
-  <si>
-    <t>Vanilla Item</t>
-  </si>
-  <si>
-    <t>Objeto de vainilla</t>
-  </si>
-  <si>
-    <t>Vanilla Mob</t>
-  </si>
-  <si>
-    <t>Mafia de vainilla</t>
-  </si>
-  <si>
-    <t>Vault Hunters</t>
-  </si>
-  <si>
-    <t>Cazadores de bóvedas</t>
-  </si>
-  <si>
-    <t>Vegetable</t>
-  </si>
-  <si>
-    <t>Vegetal</t>
-  </si>
-  <si>
-    <t>Vehicle</t>
-  </si>
-  <si>
-    <t>Vehículo</t>
-  </si>
-  <si>
-    <t>Vikings</t>
-  </si>
-  <si>
-    <t>Vikingos</t>
-  </si>
-  <si>
-    <t>Villager</t>
-  </si>
-  <si>
-    <t>Aldeano</t>
-  </si>
-  <si>
-    <t>Villager (Desert)</t>
-  </si>
-  <si>
-    <t>Aldeano (desierto)</t>
-  </si>
-  <si>
-    <t>Villager (Jungle)</t>
-  </si>
-  <si>
-    <t>Aldeano (Selva)</t>
-  </si>
-  <si>
-    <t>Villager (Plains)</t>
-  </si>
-  <si>
-    <t>Aldeano (Llanura)</t>
-  </si>
-  <si>
-    <t>Villager (Savanna)</t>
-  </si>
-  <si>
-    <t>Aldeano (sabana)</t>
-  </si>
-  <si>
-    <t>Villager (Snowy Tundra)</t>
-  </si>
-  <si>
-    <t>Aldeano (Tundra nevada)</t>
-  </si>
-  <si>
-    <t>Villager (Swamp)</t>
-  </si>
-  <si>
-    <t>Aldeano (pantano)</t>
-  </si>
-  <si>
-    <t>Villager (Taiga)</t>
-  </si>
-  <si>
-    <t>Aldeano (Taiga)</t>
-  </si>
-  <si>
-    <t>Virtual Youtuber</t>
-  </si>
-  <si>
-    <t>Youtuber virtual</t>
-  </si>
-  <si>
-    <t>Vocaloid</t>
-  </si>
-  <si>
-    <t>Voltron</t>
-  </si>
-  <si>
-    <t>Wakfu</t>
-  </si>
-  <si>
-    <t>Walking Dead</t>
-  </si>
-  <si>
-    <t>Wall-E</t>
-  </si>
-  <si>
-    <t>Wallace and Gromit</t>
-  </si>
-  <si>
-    <t>Wallace y Gromit</t>
-  </si>
-  <si>
-    <t>War of the Worlds</t>
-  </si>
-  <si>
-    <t>La Guerra de los Mundos</t>
-  </si>
-  <si>
-    <t>Warcraft</t>
-  </si>
-  <si>
-    <t>Warframe</t>
-  </si>
-  <si>
-    <t>Warhammer</t>
-  </si>
-  <si>
-    <t>Warrior Cats</t>
-  </si>
-  <si>
-    <t>We Bear Bears</t>
-  </si>
-  <si>
-    <t>Nosotros los Osos</t>
-  </si>
-  <si>
-    <t>We Happy Few</t>
-  </si>
-  <si>
-    <t>Weather</t>
-  </si>
-  <si>
-    <t>Tiempo</t>
-  </si>
-  <si>
-    <t>Welcome Home</t>
-  </si>
-  <si>
-    <t>Bienvenido a casa</t>
-  </si>
-  <si>
-    <t>Who is this?</t>
-  </si>
-  <si>
-    <t>¿Quién es?</t>
-  </si>
-  <si>
-    <t>Wild Update</t>
-  </si>
-  <si>
-    <t>Wings of Fire</t>
-  </si>
-  <si>
-    <t>Alas de fuego</t>
-  </si>
-  <si>
-    <t>Winnie the Pooh</t>
-  </si>
-  <si>
-    <t>Winter</t>
-  </si>
-  <si>
-    <t>Invierno</t>
-  </si>
-  <si>
-    <t>Witcher</t>
-  </si>
-  <si>
-    <t>Wonderful Wonder World</t>
-  </si>
-  <si>
-    <t>Maravilloso Mundo Maravilloso</t>
-  </si>
-  <si>
-    <t>Wood</t>
-  </si>
-  <si>
-    <t>Madera</t>
-  </si>
-  <si>
-    <t>Wool</t>
-  </si>
-  <si>
-    <t>Lana</t>
-  </si>
-  <si>
-    <t>Work Safety Helmet</t>
-  </si>
-  <si>
-    <t>Casco de seguridad</t>
-  </si>
-  <si>
-    <t>Wreck It Ralph</t>
-  </si>
-  <si>
-    <t>Wybel</t>
-  </si>
-  <si>
-    <t>Wynncraft</t>
-  </si>
-  <si>
-    <t>X-Men</t>
-  </si>
-  <si>
-    <t>Xenoblade Chronicles</t>
-  </si>
-  <si>
-    <t>Yandere Simulator</t>
-  </si>
-  <si>
-    <t>Simulador Yandere</t>
-  </si>
-  <si>
-    <t>Yellow Submarine</t>
-  </si>
-  <si>
-    <t>Yokai</t>
-  </si>
-  <si>
-    <t>Yooka Laylee</t>
-  </si>
-  <si>
-    <t>Young</t>
-  </si>
-  <si>
-    <t>Joven</t>
-  </si>
-  <si>
-    <t>Youtube</t>
-  </si>
-  <si>
-    <t>Yu-Gi-Oh</t>
-  </si>
-  <si>
-    <t>Yume Nikki</t>
-  </si>
-  <si>
-    <t>Zero no Tsukaima</t>
-  </si>
-  <si>
-    <t>Zero Wing</t>
-  </si>
-  <si>
-    <t>Ala Zero</t>
-  </si>
-  <si>
-    <t>Zodiac Sign</t>
-  </si>
-  <si>
-    <t>Signo del Zodiaco</t>
-  </si>
-  <si>
-    <t>Zombie</t>
-  </si>
-  <si>
-    <t>Zombie (Vanilla)</t>
-  </si>
-  <si>
-    <t>Zombie (Vainilla)</t>
-  </si>
-  <si>
-    <t>Zootopia</t>
   </si>
   <si>
     <t>Hypixel (Mutations) Tag</t>
@@ -5913,7 +5916,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1188"/>
+  <dimension ref="A1:B1189"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -15325,28 +15328,28 @@
         <v>1830</v>
       </c>
       <c r="B1176" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B1177" t="s">
         <v>1832</v>
-      </c>
-      <c r="B1177" t="s">
-        <v>1833</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B1178" t="s">
         <v>1834</v>
-      </c>
-      <c r="B1178" t="s">
-        <v>1835</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="B1179" t="s">
         <v>1836</v>
@@ -15357,7 +15360,7 @@
         <v>1837</v>
       </c>
       <c r="B1180" t="s">
-        <v>716</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
@@ -15365,7 +15368,7 @@
         <v>1838</v>
       </c>
       <c r="B1181" t="s">
-        <v>1838</v>
+        <v>716</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
@@ -15381,12 +15384,12 @@
         <v>1840</v>
       </c>
       <c r="B1183" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="B1184" t="s">
         <v>1842</v>
@@ -15405,27 +15408,35 @@
         <v>1844</v>
       </c>
       <c r="B1186" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B1187" t="s">
         <v>1846</v>
-      </c>
-      <c r="B1187" t="s">
-        <v>1847</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B1188" t="s">
         <v>1848</v>
       </c>
-      <c r="B1188" t="s">
+    </row>
+    <row r="1189" spans="1:2">
+      <c r="A1189" t="s">
         <v>1849</v>
       </c>
+      <c r="B1189" t="s">
+        <v>1850</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1188"/>
+  <autoFilter ref="A1:B1189"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/es/headTags.xlsx
+++ b/lang/es/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1190</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1851">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1852">
   <si>
     <t>en</t>
   </si>
@@ -3725,6 +3725,9 @@
   </si>
   <si>
     <t>Objetos de código abierto</t>
+  </si>
+  <si>
+    <t>Opus Magnum</t>
   </si>
   <si>
     <t>Orb</t>
@@ -5916,7 +5919,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1189"/>
+  <dimension ref="A1:B1190"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -12304,68 +12307,68 @@
         <v>1236</v>
       </c>
       <c r="B798" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B799" t="s">
         <v>1238</v>
-      </c>
-      <c r="B799" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B800" t="s">
         <v>1240</v>
-      </c>
-      <c r="B800" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B801" t="s">
         <v>1242</v>
-      </c>
-      <c r="B801" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B802" t="s">
         <v>1244</v>
-      </c>
-      <c r="B802" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B803" t="s">
         <v>1246</v>
-      </c>
-      <c r="B803" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B804" t="s">
         <v>1248</v>
-      </c>
-      <c r="B804" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B805" t="s">
         <v>1250</v>
-      </c>
-      <c r="B805" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="B806" t="s">
         <v>1252</v>
@@ -12400,36 +12403,36 @@
         <v>1256</v>
       </c>
       <c r="B810" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B811" t="s">
         <v>1258</v>
-      </c>
-      <c r="B811" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="812" spans="1:2">
       <c r="A812" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B812" t="s">
         <v>1260</v>
-      </c>
-      <c r="B812" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="813" spans="1:2">
       <c r="A813" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B813" t="s">
         <v>1262</v>
-      </c>
-      <c r="B813" t="s">
-        <v>1263</v>
       </c>
     </row>
     <row r="814" spans="1:2">
       <c r="A814" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B814" t="s">
         <v>1264</v>
@@ -12440,36 +12443,36 @@
         <v>1265</v>
       </c>
       <c r="B815" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B816" t="s">
         <v>1267</v>
-      </c>
-      <c r="B816" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B817" t="s">
         <v>1269</v>
-      </c>
-      <c r="B817" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B818" t="s">
         <v>1271</v>
-      </c>
-      <c r="B818" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="B819" t="s">
         <v>1273</v>
@@ -12480,12 +12483,12 @@
         <v>1274</v>
       </c>
       <c r="B820" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B821" t="s">
         <v>1276</v>
@@ -12496,12 +12499,12 @@
         <v>1277</v>
       </c>
       <c r="B822" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="B823" t="s">
         <v>1279</v>
@@ -12512,12 +12515,12 @@
         <v>1280</v>
       </c>
       <c r="B824" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="B825" t="s">
         <v>1282</v>
@@ -12528,12 +12531,12 @@
         <v>1283</v>
       </c>
       <c r="B826" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B827" t="s">
         <v>1285</v>
@@ -12544,7 +12547,7 @@
         <v>1286</v>
       </c>
       <c r="B828" t="s">
-        <v>714</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="829" spans="1:2">
@@ -12552,20 +12555,20 @@
         <v>1287</v>
       </c>
       <c r="B829" t="s">
-        <v>1288</v>
+        <v>714</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B830" t="s">
         <v>1289</v>
-      </c>
-      <c r="B830" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B831" t="s">
         <v>1291</v>
@@ -12600,36 +12603,36 @@
         <v>1295</v>
       </c>
       <c r="B835" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B836" t="s">
         <v>1297</v>
-      </c>
-      <c r="B836" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B837" t="s">
         <v>1299</v>
-      </c>
-      <c r="B837" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B838" t="s">
         <v>1301</v>
-      </c>
-      <c r="B838" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="B839" t="s">
         <v>1303</v>
@@ -12640,20 +12643,20 @@
         <v>1304</v>
       </c>
       <c r="B840" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B841" t="s">
         <v>1306</v>
-      </c>
-      <c r="B841" t="s">
-        <v>1307</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="B842" t="s">
         <v>1308</v>
@@ -12688,108 +12691,108 @@
         <v>1312</v>
       </c>
       <c r="B846" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B847" t="s">
         <v>1314</v>
-      </c>
-      <c r="B847" t="s">
-        <v>1315</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B848" t="s">
         <v>1316</v>
-      </c>
-      <c r="B848" t="s">
-        <v>1317</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B849" t="s">
         <v>1318</v>
-      </c>
-      <c r="B849" t="s">
-        <v>1319</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B850" t="s">
         <v>1320</v>
-      </c>
-      <c r="B850" t="s">
-        <v>1321</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B851" t="s">
         <v>1322</v>
-      </c>
-      <c r="B851" t="s">
-        <v>1323</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B852" t="s">
         <v>1324</v>
-      </c>
-      <c r="B852" t="s">
-        <v>1325</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B853" t="s">
         <v>1326</v>
-      </c>
-      <c r="B853" t="s">
-        <v>1327</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B854" t="s">
         <v>1328</v>
-      </c>
-      <c r="B854" t="s">
-        <v>1329</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B855" t="s">
         <v>1330</v>
-      </c>
-      <c r="B855" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B856" t="s">
         <v>1332</v>
-      </c>
-      <c r="B856" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B857" t="s">
         <v>1334</v>
-      </c>
-      <c r="B857" t="s">
-        <v>1335</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B858" t="s">
         <v>1336</v>
-      </c>
-      <c r="B858" t="s">
-        <v>1337</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="B859" t="s">
         <v>1338</v>
@@ -12848,12 +12851,12 @@
         <v>1345</v>
       </c>
       <c r="B866" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="B867" t="s">
         <v>1347</v>
@@ -12880,20 +12883,20 @@
         <v>1350</v>
       </c>
       <c r="B870" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B871" t="s">
         <v>1352</v>
-      </c>
-      <c r="B871" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="B872" t="s">
         <v>1354</v>
@@ -12904,31 +12907,31 @@
         <v>1355</v>
       </c>
       <c r="B873" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B874" t="s">
         <v>1357</v>
-      </c>
-      <c r="B874" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B875" t="s">
         <v>1359</v>
-      </c>
-      <c r="B875" t="s">
-        <v>1360</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B876" t="s">
         <v>1361</v>
-      </c>
-      <c r="B876" t="s">
-        <v>1360</v>
       </c>
     </row>
     <row r="877" spans="1:2">
@@ -12936,12 +12939,12 @@
         <v>1362</v>
       </c>
       <c r="B877" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="B878" t="s">
         <v>1364</v>
@@ -12960,28 +12963,28 @@
         <v>1366</v>
       </c>
       <c r="B880" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B881" t="s">
         <v>1368</v>
-      </c>
-      <c r="B881" t="s">
-        <v>1369</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B882" t="s">
         <v>1370</v>
-      </c>
-      <c r="B882" t="s">
-        <v>1371</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="B883" t="s">
         <v>1372</v>
@@ -12992,20 +12995,20 @@
         <v>1373</v>
       </c>
       <c r="B884" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B885" t="s">
         <v>1375</v>
-      </c>
-      <c r="B885" t="s">
-        <v>1376</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="B886" t="s">
         <v>1377</v>
@@ -13016,12 +13019,12 @@
         <v>1378</v>
       </c>
       <c r="B887" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="B888" t="s">
         <v>1380</v>
@@ -13048,12 +13051,12 @@
         <v>1383</v>
       </c>
       <c r="B891" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="B892" t="s">
         <v>1385</v>
@@ -13072,28 +13075,28 @@
         <v>1387</v>
       </c>
       <c r="B894" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B895" t="s">
         <v>1389</v>
-      </c>
-      <c r="B895" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B896" t="s">
         <v>1391</v>
-      </c>
-      <c r="B896" t="s">
-        <v>1392</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B897" t="s">
         <v>1393</v>
@@ -13112,44 +13115,44 @@
         <v>1395</v>
       </c>
       <c r="B899" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B900" t="s">
         <v>1397</v>
-      </c>
-      <c r="B900" t="s">
-        <v>1398</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B901" t="s">
         <v>1399</v>
-      </c>
-      <c r="B901" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B902" t="s">
         <v>1401</v>
-      </c>
-      <c r="B902" t="s">
-        <v>1402</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B903" t="s">
         <v>1403</v>
-      </c>
-      <c r="B903" t="s">
-        <v>1404</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="B904" t="s">
         <v>1405</v>
@@ -13208,36 +13211,36 @@
         <v>1412</v>
       </c>
       <c r="B911" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B912" t="s">
         <v>1414</v>
-      </c>
-      <c r="B912" t="s">
-        <v>1415</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B913" t="s">
         <v>1416</v>
-      </c>
-      <c r="B913" t="s">
-        <v>1417</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B914" t="s">
         <v>1418</v>
-      </c>
-      <c r="B914" t="s">
-        <v>1419</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="B915" t="s">
         <v>1420</v>
@@ -13256,44 +13259,44 @@
         <v>1422</v>
       </c>
       <c r="B917" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B918" t="s">
         <v>1424</v>
-      </c>
-      <c r="B918" t="s">
-        <v>1425</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B919" t="s">
         <v>1426</v>
-      </c>
-      <c r="B919" t="s">
-        <v>1427</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B920" t="s">
         <v>1428</v>
-      </c>
-      <c r="B920" t="s">
-        <v>1429</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B921" t="s">
         <v>1430</v>
-      </c>
-      <c r="B921" t="s">
-        <v>1431</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="B922" t="s">
         <v>1432</v>
@@ -13312,36 +13315,36 @@
         <v>1434</v>
       </c>
       <c r="B924" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B925" t="s">
         <v>1436</v>
-      </c>
-      <c r="B925" t="s">
-        <v>1437</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B926" t="s">
         <v>1438</v>
-      </c>
-      <c r="B926" t="s">
-        <v>1439</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B927" t="s">
         <v>1440</v>
-      </c>
-      <c r="B927" t="s">
-        <v>1441</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B928" t="s">
         <v>1442</v>
@@ -13352,20 +13355,20 @@
         <v>1443</v>
       </c>
       <c r="B929" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B930" t="s">
         <v>1445</v>
-      </c>
-      <c r="B930" t="s">
-        <v>1446</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B931" t="s">
         <v>1447</v>
@@ -13384,12 +13387,12 @@
         <v>1449</v>
       </c>
       <c r="B933" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="B934" t="s">
         <v>1451</v>
@@ -13400,28 +13403,28 @@
         <v>1452</v>
       </c>
       <c r="B935" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B936" t="s">
         <v>1454</v>
-      </c>
-      <c r="B936" t="s">
-        <v>1455</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B937" t="s">
         <v>1456</v>
-      </c>
-      <c r="B937" t="s">
-        <v>1457</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="B938" t="s">
         <v>1458</v>
@@ -13432,20 +13435,20 @@
         <v>1459</v>
       </c>
       <c r="B939" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B940" t="s">
         <v>1461</v>
-      </c>
-      <c r="B940" t="s">
-        <v>1462</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="B941" t="s">
         <v>1463</v>
@@ -13480,12 +13483,12 @@
         <v>1467</v>
       </c>
       <c r="B945" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B946" t="s">
         <v>1469</v>
@@ -13536,36 +13539,36 @@
         <v>1475</v>
       </c>
       <c r="B952" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B953" t="s">
         <v>1477</v>
-      </c>
-      <c r="B953" t="s">
-        <v>1478</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B954" t="s">
         <v>1479</v>
-      </c>
-      <c r="B954" t="s">
-        <v>1480</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B955" t="s">
         <v>1481</v>
-      </c>
-      <c r="B955" t="s">
-        <v>1482</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="B956" t="s">
         <v>1483</v>
@@ -13584,52 +13587,52 @@
         <v>1485</v>
       </c>
       <c r="B958" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B959" t="s">
         <v>1487</v>
-      </c>
-      <c r="B959" t="s">
-        <v>1488</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B960" t="s">
         <v>1489</v>
-      </c>
-      <c r="B960" t="s">
-        <v>1490</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B961" t="s">
         <v>1491</v>
-      </c>
-      <c r="B961" t="s">
-        <v>1492</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B962" t="s">
         <v>1493</v>
-      </c>
-      <c r="B962" t="s">
-        <v>1494</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B963" t="s">
         <v>1495</v>
-      </c>
-      <c r="B963" t="s">
-        <v>1496</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="B964" t="s">
         <v>1497</v>
@@ -13664,20 +13667,20 @@
         <v>1501</v>
       </c>
       <c r="B968" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B969" t="s">
         <v>1503</v>
-      </c>
-      <c r="B969" t="s">
-        <v>1504</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="B970" t="s">
         <v>1505</v>
@@ -13688,68 +13691,68 @@
         <v>1506</v>
       </c>
       <c r="B971" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B972" t="s">
         <v>1508</v>
-      </c>
-      <c r="B972" t="s">
-        <v>1509</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B973" t="s">
         <v>1510</v>
-      </c>
-      <c r="B973" t="s">
-        <v>1511</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B974" t="s">
         <v>1512</v>
-      </c>
-      <c r="B974" t="s">
-        <v>1513</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B975" t="s">
         <v>1514</v>
-      </c>
-      <c r="B975" t="s">
-        <v>1515</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B976" t="s">
         <v>1516</v>
-      </c>
-      <c r="B976" t="s">
-        <v>1517</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B977" t="s">
         <v>1518</v>
-      </c>
-      <c r="B977" t="s">
-        <v>1519</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B978" t="s">
         <v>1520</v>
-      </c>
-      <c r="B978" t="s">
-        <v>1521</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="B979" t="s">
         <v>1522</v>
@@ -13768,20 +13771,20 @@
         <v>1524</v>
       </c>
       <c r="B981" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B982" t="s">
         <v>1526</v>
-      </c>
-      <c r="B982" t="s">
-        <v>1527</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B983" t="s">
         <v>1528</v>
@@ -13808,44 +13811,44 @@
         <v>1531</v>
       </c>
       <c r="B986" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B987" t="s">
         <v>1533</v>
-      </c>
-      <c r="B987" t="s">
-        <v>1534</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B988" t="s">
         <v>1535</v>
-      </c>
-      <c r="B988" t="s">
-        <v>1536</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B989" t="s">
         <v>1537</v>
-      </c>
-      <c r="B989" t="s">
-        <v>1538</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B990" t="s">
         <v>1539</v>
-      </c>
-      <c r="B990" t="s">
-        <v>1540</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="B991" t="s">
         <v>1541</v>
@@ -13856,12 +13859,12 @@
         <v>1542</v>
       </c>
       <c r="B992" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="B993" t="s">
         <v>1544</v>
@@ -13872,20 +13875,20 @@
         <v>1545</v>
       </c>
       <c r="B994" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B995" t="s">
         <v>1547</v>
-      </c>
-      <c r="B995" t="s">
-        <v>1548</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="B996" t="s">
         <v>1549</v>
@@ -13912,12 +13915,12 @@
         <v>1552</v>
       </c>
       <c r="B999" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="B1000" t="s">
         <v>1554</v>
@@ -13928,20 +13931,20 @@
         <v>1555</v>
       </c>
       <c r="B1001" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B1002" t="s">
         <v>1557</v>
-      </c>
-      <c r="B1002" t="s">
-        <v>1558</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="B1003" t="s">
         <v>1559</v>
@@ -13976,12 +13979,12 @@
         <v>1563</v>
       </c>
       <c r="B1007" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="B1008" t="s">
         <v>1565</v>
@@ -14016,20 +14019,20 @@
         <v>1569</v>
       </c>
       <c r="B1012" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B1013" t="s">
         <v>1571</v>
-      </c>
-      <c r="B1013" t="s">
-        <v>1572</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="B1014" t="s">
         <v>1573</v>
@@ -14064,20 +14067,20 @@
         <v>1577</v>
       </c>
       <c r="B1018" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B1019" t="s">
         <v>1579</v>
-      </c>
-      <c r="B1019" t="s">
-        <v>1580</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="B1020" t="s">
         <v>1581</v>
@@ -14088,28 +14091,28 @@
         <v>1582</v>
       </c>
       <c r="B1021" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B1022" t="s">
         <v>1584</v>
-      </c>
-      <c r="B1022" t="s">
-        <v>1585</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B1023" t="s">
         <v>1586</v>
-      </c>
-      <c r="B1023" t="s">
-        <v>1587</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B1024" t="s">
         <v>1588</v>
@@ -14120,12 +14123,12 @@
         <v>1589</v>
       </c>
       <c r="B1025" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="B1026" t="s">
         <v>1591</v>
@@ -14144,12 +14147,12 @@
         <v>1593</v>
       </c>
       <c r="B1028" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="B1029" t="s">
         <v>1595</v>
@@ -14200,20 +14203,20 @@
         <v>1601</v>
       </c>
       <c r="B1035" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B1036" t="s">
         <v>1603</v>
-      </c>
-      <c r="B1036" t="s">
-        <v>1604</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="B1037" t="s">
         <v>1605</v>
@@ -14224,28 +14227,28 @@
         <v>1606</v>
       </c>
       <c r="B1038" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B1039" t="s">
         <v>1608</v>
-      </c>
-      <c r="B1039" t="s">
-        <v>1609</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B1040" t="s">
         <v>1610</v>
-      </c>
-      <c r="B1040" t="s">
-        <v>1611</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="B1041" t="s">
         <v>1612</v>
@@ -14264,28 +14267,28 @@
         <v>1614</v>
       </c>
       <c r="B1043" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B1044" t="s">
         <v>1616</v>
-      </c>
-      <c r="B1044" t="s">
-        <v>1617</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B1045" t="s">
         <v>1618</v>
-      </c>
-      <c r="B1045" t="s">
-        <v>1619</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="B1046" t="s">
         <v>1620</v>
@@ -14304,12 +14307,12 @@
         <v>1622</v>
       </c>
       <c r="B1048" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1049" t="s">
         <v>1624</v>
@@ -14328,180 +14331,180 @@
         <v>1626</v>
       </c>
       <c r="B1051" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B1052" t="s">
         <v>1628</v>
-      </c>
-      <c r="B1052" t="s">
-        <v>1629</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B1053" t="s">
         <v>1630</v>
-      </c>
-      <c r="B1053" t="s">
-        <v>1631</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B1054" t="s">
         <v>1632</v>
-      </c>
-      <c r="B1054" t="s">
-        <v>1633</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B1055" t="s">
         <v>1634</v>
-      </c>
-      <c r="B1055" t="s">
-        <v>1635</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B1056" t="s">
         <v>1636</v>
-      </c>
-      <c r="B1056" t="s">
-        <v>1637</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B1057" t="s">
         <v>1638</v>
-      </c>
-      <c r="B1057" t="s">
-        <v>1639</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
+        <v>1639</v>
+      </c>
+      <c r="B1058" t="s">
         <v>1640</v>
-      </c>
-      <c r="B1058" t="s">
-        <v>1641</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B1059" t="s">
         <v>1642</v>
-      </c>
-      <c r="B1059" t="s">
-        <v>1643</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B1060" t="s">
         <v>1644</v>
-      </c>
-      <c r="B1060" t="s">
-        <v>1645</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B1061" t="s">
         <v>1646</v>
-      </c>
-      <c r="B1061" t="s">
-        <v>1647</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B1062" t="s">
         <v>1648</v>
-      </c>
-      <c r="B1062" t="s">
-        <v>1649</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B1063" t="s">
         <v>1650</v>
-      </c>
-      <c r="B1063" t="s">
-        <v>1651</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B1064" t="s">
         <v>1652</v>
-      </c>
-      <c r="B1064" t="s">
-        <v>1653</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B1065" t="s">
         <v>1654</v>
-      </c>
-      <c r="B1065" t="s">
-        <v>1655</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B1066" t="s">
         <v>1656</v>
-      </c>
-      <c r="B1066" t="s">
-        <v>1657</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B1067" t="s">
         <v>1658</v>
-      </c>
-      <c r="B1067" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B1068" t="s">
         <v>1660</v>
-      </c>
-      <c r="B1068" t="s">
-        <v>1661</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B1069" t="s">
         <v>1662</v>
-      </c>
-      <c r="B1069" t="s">
-        <v>1663</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B1070" t="s">
         <v>1664</v>
-      </c>
-      <c r="B1070" t="s">
-        <v>1665</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B1071" t="s">
         <v>1666</v>
-      </c>
-      <c r="B1071" t="s">
-        <v>1667</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B1072" t="s">
         <v>1668</v>
-      </c>
-      <c r="B1072" t="s">
-        <v>1669</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="B1073" t="s">
         <v>1670</v>
@@ -14512,12 +14515,12 @@
         <v>1671</v>
       </c>
       <c r="B1074" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="B1075" t="s">
         <v>1673</v>
@@ -14544,12 +14547,12 @@
         <v>1676</v>
       </c>
       <c r="B1078" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="B1079" t="s">
         <v>1678</v>
@@ -14560,12 +14563,12 @@
         <v>1679</v>
       </c>
       <c r="B1080" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="B1081" t="s">
         <v>1681</v>
@@ -14592,12 +14595,12 @@
         <v>1684</v>
       </c>
       <c r="B1084" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="B1085" t="s">
         <v>1686</v>
@@ -14616,36 +14619,36 @@
         <v>1688</v>
       </c>
       <c r="B1087" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B1088" t="s">
         <v>1690</v>
-      </c>
-      <c r="B1088" t="s">
-        <v>1691</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B1089" t="s">
         <v>1692</v>
-      </c>
-      <c r="B1089" t="s">
-        <v>1693</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B1090" t="s">
         <v>1694</v>
-      </c>
-      <c r="B1090" t="s">
-        <v>1695</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="B1091" t="s">
         <v>1696</v>
@@ -14664,44 +14667,44 @@
         <v>1698</v>
       </c>
       <c r="B1093" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B1094" t="s">
         <v>1700</v>
-      </c>
-      <c r="B1094" t="s">
-        <v>1701</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B1095" t="s">
         <v>1702</v>
-      </c>
-      <c r="B1095" t="s">
-        <v>1703</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B1096" t="s">
         <v>1704</v>
-      </c>
-      <c r="B1096" t="s">
-        <v>1705</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B1097" t="s">
         <v>1706</v>
-      </c>
-      <c r="B1097" t="s">
-        <v>1707</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="B1098" t="s">
         <v>1708</v>
@@ -14712,28 +14715,28 @@
         <v>1709</v>
       </c>
       <c r="B1099" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B1100" t="s">
         <v>1711</v>
-      </c>
-      <c r="B1100" t="s">
-        <v>1712</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B1101" t="s">
         <v>1713</v>
-      </c>
-      <c r="B1101" t="s">
-        <v>1714</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="B1102" t="s">
         <v>1715</v>
@@ -14744,12 +14747,12 @@
         <v>1716</v>
       </c>
       <c r="B1103" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="B1104" t="s">
         <v>1718</v>
@@ -14768,12 +14771,12 @@
         <v>1720</v>
       </c>
       <c r="B1106" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="B1107" t="s">
         <v>1722</v>
@@ -14784,28 +14787,28 @@
         <v>1723</v>
       </c>
       <c r="B1108" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B1109" t="s">
         <v>1725</v>
-      </c>
-      <c r="B1109" t="s">
-        <v>1726</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B1110" t="s">
         <v>1727</v>
-      </c>
-      <c r="B1110" t="s">
-        <v>1728</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="B1111" t="s">
         <v>1729</v>
@@ -14824,156 +14827,156 @@
         <v>1731</v>
       </c>
       <c r="B1113" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B1114" t="s">
         <v>1733</v>
-      </c>
-      <c r="B1114" t="s">
-        <v>1734</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1115" t="s">
         <v>1735</v>
-      </c>
-      <c r="B1115" t="s">
-        <v>1736</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B1116" t="s">
         <v>1737</v>
-      </c>
-      <c r="B1116" t="s">
-        <v>1738</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B1117" t="s">
         <v>1739</v>
-      </c>
-      <c r="B1117" t="s">
-        <v>1740</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B1118" t="s">
         <v>1741</v>
-      </c>
-      <c r="B1118" t="s">
-        <v>1742</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B1119" t="s">
         <v>1743</v>
-      </c>
-      <c r="B1119" t="s">
-        <v>1744</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
+        <v>1744</v>
+      </c>
+      <c r="B1120" t="s">
         <v>1745</v>
-      </c>
-      <c r="B1120" t="s">
-        <v>1746</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B1121" t="s">
         <v>1747</v>
-      </c>
-      <c r="B1121" t="s">
-        <v>1748</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B1122" t="s">
         <v>1749</v>
-      </c>
-      <c r="B1122" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B1123" t="s">
         <v>1751</v>
-      </c>
-      <c r="B1123" t="s">
-        <v>1752</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B1124" t="s">
         <v>1753</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>1754</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B1125" t="s">
         <v>1755</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>1756</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B1126" t="s">
         <v>1757</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>1758</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B1127" t="s">
         <v>1759</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>1760</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B1128" t="s">
         <v>1761</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>1762</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B1129" t="s">
         <v>1763</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>1764</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B1130" t="s">
         <v>1765</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>1766</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>1766</v>
+      </c>
+      <c r="B1131" t="s">
         <v>1767</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>1768</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="B1132" t="s">
         <v>1769</v>
@@ -15016,20 +15019,20 @@
         <v>1774</v>
       </c>
       <c r="B1137" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B1138" t="s">
         <v>1776</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>1777</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="B1139" t="s">
         <v>1778</v>
@@ -15064,12 +15067,12 @@
         <v>1782</v>
       </c>
       <c r="B1143" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="B1144" t="s">
         <v>1784</v>
@@ -15080,28 +15083,28 @@
         <v>1785</v>
       </c>
       <c r="B1145" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B1146" t="s">
         <v>1787</v>
-      </c>
-      <c r="B1146" t="s">
-        <v>1788</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B1147" t="s">
         <v>1789</v>
-      </c>
-      <c r="B1147" t="s">
-        <v>1790</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="B1148" t="s">
         <v>1791</v>
@@ -15112,12 +15115,12 @@
         <v>1792</v>
       </c>
       <c r="B1149" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="B1150" t="s">
         <v>1794</v>
@@ -15128,12 +15131,12 @@
         <v>1795</v>
       </c>
       <c r="B1151" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="B1152" t="s">
         <v>1797</v>
@@ -15144,36 +15147,36 @@
         <v>1798</v>
       </c>
       <c r="B1153" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B1154" t="s">
         <v>1800</v>
-      </c>
-      <c r="B1154" t="s">
-        <v>1801</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B1155" t="s">
         <v>1802</v>
-      </c>
-      <c r="B1155" t="s">
-        <v>1803</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B1156" t="s">
         <v>1804</v>
-      </c>
-      <c r="B1156" t="s">
-        <v>1805</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="B1157" t="s">
         <v>1806</v>
@@ -15216,12 +15219,12 @@
         <v>1811</v>
       </c>
       <c r="B1162" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="B1163" t="s">
         <v>1813</v>
@@ -15248,12 +15251,12 @@
         <v>1816</v>
       </c>
       <c r="B1166" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="B1167" t="s">
         <v>1818</v>
@@ -15288,20 +15291,20 @@
         <v>1822</v>
       </c>
       <c r="B1171" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B1172" t="s">
         <v>1824</v>
-      </c>
-      <c r="B1172" t="s">
-        <v>1825</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="B1173" t="s">
         <v>1826</v>
@@ -15312,12 +15315,12 @@
         <v>1827</v>
       </c>
       <c r="B1174" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="B1175" t="s">
         <v>1829</v>
@@ -15336,28 +15339,28 @@
         <v>1831</v>
       </c>
       <c r="B1177" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B1178" t="s">
         <v>1833</v>
-      </c>
-      <c r="B1178" t="s">
-        <v>1834</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B1179" t="s">
         <v>1835</v>
-      </c>
-      <c r="B1179" t="s">
-        <v>1836</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="B1180" t="s">
         <v>1837</v>
@@ -15368,7 +15371,7 @@
         <v>1838</v>
       </c>
       <c r="B1181" t="s">
-        <v>716</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
@@ -15376,7 +15379,7 @@
         <v>1839</v>
       </c>
       <c r="B1182" t="s">
-        <v>1839</v>
+        <v>716</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
@@ -15392,12 +15395,12 @@
         <v>1841</v>
       </c>
       <c r="B1184" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B1185" t="s">
         <v>1843</v>
@@ -15416,27 +15419,35 @@
         <v>1845</v>
       </c>
       <c r="B1187" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B1188" t="s">
         <v>1847</v>
-      </c>
-      <c r="B1188" t="s">
-        <v>1848</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B1189" t="s">
         <v>1849</v>
       </c>
-      <c r="B1189" t="s">
+    </row>
+    <row r="1190" spans="1:2">
+      <c r="A1190" t="s">
         <v>1850</v>
       </c>
+      <c r="B1190" t="s">
+        <v>1851</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1189"/>
+  <autoFilter ref="A1:B1190"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/es/headTags.xlsx
+++ b/lang/es/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1191</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1854">
   <si>
     <t>en</t>
   </si>
@@ -755,6 +755,12 @@
   </si>
   <si>
     <t>Cáliz</t>
+  </si>
+  <si>
+    <t>Chaos Cubed</t>
+  </si>
+  <si>
+    <t>Caos al cubo</t>
   </si>
   <si>
     <t>Charlie and the Chocolate Factory</t>
@@ -5919,7 +5925,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1190"/>
+  <dimension ref="A1:B1191"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -7283,20 +7289,20 @@
         <v>260</v>
       </c>
       <c r="B170" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B171" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B172" t="s">
         <v>263</v>
@@ -7323,20 +7329,20 @@
         <v>268</v>
       </c>
       <c r="B175" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B176" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B177" t="s">
         <v>271</v>
@@ -7355,20 +7361,20 @@
         <v>274</v>
       </c>
       <c r="B179" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B180" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B181" t="s">
         <v>277</v>
@@ -7379,12 +7385,12 @@
         <v>278</v>
       </c>
       <c r="B182" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B183" t="s">
         <v>279</v>
@@ -7392,15 +7398,15 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B184" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B185" t="s">
         <v>282</v>
@@ -7411,12 +7417,12 @@
         <v>283</v>
       </c>
       <c r="B186" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B187" t="s">
         <v>285</v>
@@ -7507,12 +7513,12 @@
         <v>306</v>
       </c>
       <c r="B198" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B199" t="s">
         <v>308</v>
@@ -7547,28 +7553,28 @@
         <v>315</v>
       </c>
       <c r="B203" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B204" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B205" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="A206" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B206" t="s">
         <v>319</v>
@@ -7579,28 +7585,28 @@
         <v>320</v>
       </c>
       <c r="B207" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B208" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B209" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B210" t="s">
         <v>324</v>
@@ -7611,12 +7617,12 @@
         <v>325</v>
       </c>
       <c r="B211" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B212" t="s">
         <v>327</v>
@@ -7635,12 +7641,12 @@
         <v>330</v>
       </c>
       <c r="B214" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B215" t="s">
         <v>332</v>
@@ -7659,52 +7665,52 @@
         <v>335</v>
       </c>
       <c r="B217" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B218" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="219" spans="1:2">
       <c r="A219" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B219" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B220" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="221" spans="1:2">
       <c r="A221" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B221" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B222" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B223" t="s">
         <v>342</v>
@@ -7715,36 +7721,36 @@
         <v>343</v>
       </c>
       <c r="B224" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B225" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="226" spans="1:2">
       <c r="A226" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B226" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B227" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B228" t="s">
         <v>348</v>
@@ -7763,52 +7769,52 @@
         <v>351</v>
       </c>
       <c r="B230" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B231" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="232" spans="1:2">
       <c r="A232" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B232" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B233" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B234" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B235" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="236" spans="1:2">
       <c r="A236" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B236" t="s">
         <v>358</v>
@@ -7851,12 +7857,12 @@
         <v>367</v>
       </c>
       <c r="B241" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="242" spans="1:2">
       <c r="A242" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B242" t="s">
         <v>369</v>
@@ -7867,12 +7873,12 @@
         <v>370</v>
       </c>
       <c r="B243" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B244" t="s">
         <v>372</v>
@@ -7923,12 +7929,12 @@
         <v>383</v>
       </c>
       <c r="B250" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B251" t="s">
         <v>385</v>
@@ -7939,20 +7945,20 @@
         <v>386</v>
       </c>
       <c r="B252" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B253" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="254" spans="1:2">
       <c r="A254" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B254" t="s">
         <v>389</v>
@@ -7963,36 +7969,36 @@
         <v>390</v>
       </c>
       <c r="B255" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B256" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B257" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B258" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B259" t="s">
         <v>395</v>
@@ -8035,20 +8041,20 @@
         <v>404</v>
       </c>
       <c r="B264" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="265" spans="1:2">
       <c r="A265" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B265" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="266" spans="1:2">
       <c r="A266" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B266" t="s">
         <v>407</v>
@@ -8067,28 +8073,28 @@
         <v>410</v>
       </c>
       <c r="B268" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B269" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="270" spans="1:2">
       <c r="A270" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B270" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B271" t="s">
         <v>414</v>
@@ -8099,44 +8105,44 @@
         <v>415</v>
       </c>
       <c r="B272" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B273" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B274" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B275" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="276" spans="1:2">
       <c r="A276" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B276" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="277" spans="1:2">
       <c r="A277" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B277" t="s">
         <v>421</v>
@@ -8163,36 +8169,36 @@
         <v>426</v>
       </c>
       <c r="B280" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="281" spans="1:2">
       <c r="A281" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B281" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="282" spans="1:2">
       <c r="A282" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B282" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="283" spans="1:2">
       <c r="A283" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B283" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="284" spans="1:2">
       <c r="A284" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B284" t="s">
         <v>431</v>
@@ -8203,12 +8209,12 @@
         <v>432</v>
       </c>
       <c r="B285" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B286" t="s">
         <v>434</v>
@@ -8219,12 +8225,12 @@
         <v>435</v>
       </c>
       <c r="B287" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B288" t="s">
         <v>437</v>
@@ -8235,12 +8241,12 @@
         <v>438</v>
       </c>
       <c r="B289" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="290" spans="1:2">
       <c r="A290" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B290" t="s">
         <v>440</v>
@@ -8251,15 +8257,15 @@
         <v>441</v>
       </c>
       <c r="B291" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" t="s">
+        <v>443</v>
+      </c>
+      <c r="B292" t="s">
         <v>442</v>
-      </c>
-      <c r="B292" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -8275,20 +8281,20 @@
         <v>446</v>
       </c>
       <c r="B294" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="295" spans="1:2">
       <c r="A295" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B295" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="296" spans="1:2">
       <c r="A296" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B296" t="s">
         <v>449</v>
@@ -8323,12 +8329,12 @@
         <v>456</v>
       </c>
       <c r="B300" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="301" spans="1:2">
       <c r="A301" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B301" t="s">
         <v>458</v>
@@ -8339,12 +8345,12 @@
         <v>459</v>
       </c>
       <c r="B302" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B303" t="s">
         <v>461</v>
@@ -8387,20 +8393,20 @@
         <v>470</v>
       </c>
       <c r="B308" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="309" spans="1:2">
       <c r="A309" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B309" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="310" spans="1:2">
       <c r="A310" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B310" t="s">
         <v>473</v>
@@ -8419,20 +8425,20 @@
         <v>476</v>
       </c>
       <c r="B312" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B313" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="314" spans="1:2">
       <c r="A314" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B314" t="s">
         <v>479</v>
@@ -8467,76 +8473,76 @@
         <v>486</v>
       </c>
       <c r="B318" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B319" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="320" spans="1:2">
       <c r="A320" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B320" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B321" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B322" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="323" spans="1:2">
       <c r="A323" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B323" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B324" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="325" spans="1:2">
       <c r="A325" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B325" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="326" spans="1:2">
       <c r="A326" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B326" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B327" t="s">
         <v>496</v>
@@ -8547,28 +8553,28 @@
         <v>497</v>
       </c>
       <c r="B328" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B329" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="330" spans="1:2">
       <c r="A330" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B330" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B331" t="s">
         <v>501</v>
@@ -8579,12 +8585,12 @@
         <v>502</v>
       </c>
       <c r="B332" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B333" t="s">
         <v>504</v>
@@ -8635,12 +8641,12 @@
         <v>515</v>
       </c>
       <c r="B339" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="A340" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B340" t="s">
         <v>517</v>
@@ -8795,12 +8801,12 @@
         <v>554</v>
       </c>
       <c r="B359" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B360" t="s">
         <v>556</v>
@@ -8827,12 +8833,12 @@
         <v>561</v>
       </c>
       <c r="B363" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="364" spans="1:2">
       <c r="A364" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B364" t="s">
         <v>563</v>
@@ -8883,15 +8889,15 @@
         <v>574</v>
       </c>
       <c r="B370" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="371" spans="1:2">
       <c r="A371" t="s">
+        <v>576</v>
+      </c>
+      <c r="B371" t="s">
         <v>575</v>
-      </c>
-      <c r="B371" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -8907,20 +8913,20 @@
         <v>579</v>
       </c>
       <c r="B373" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="374" spans="1:2">
       <c r="A374" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B374" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="375" spans="1:2">
       <c r="A375" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B375" t="s">
         <v>582</v>
@@ -8931,12 +8937,12 @@
         <v>583</v>
       </c>
       <c r="B376" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="377" spans="1:2">
       <c r="A377" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B377" t="s">
         <v>585</v>
@@ -8963,31 +8969,31 @@
         <v>590</v>
       </c>
       <c r="B380" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
     </row>
     <row r="381" spans="1:2">
       <c r="A381" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B381" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="382" spans="1:2">
       <c r="A382" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B382" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="383" spans="1:2">
       <c r="A383" t="s">
+        <v>594</v>
+      </c>
+      <c r="B383" t="s">
         <v>593</v>
-      </c>
-      <c r="B383" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -9003,12 +9009,12 @@
         <v>597</v>
       </c>
       <c r="B385" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="386" spans="1:2">
       <c r="A386" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B386" t="s">
         <v>599</v>
@@ -9019,12 +9025,12 @@
         <v>600</v>
       </c>
       <c r="B387" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="388" spans="1:2">
       <c r="A388" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B388" t="s">
         <v>602</v>
@@ -9043,116 +9049,116 @@
         <v>605</v>
       </c>
       <c r="B390" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="391" spans="1:2">
       <c r="A391" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B391" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="392" spans="1:2">
       <c r="A392" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B392" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="393" spans="1:2">
       <c r="A393" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B393" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="394" spans="1:2">
       <c r="A394" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B394" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="395" spans="1:2">
       <c r="A395" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B395" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="396" spans="1:2">
       <c r="A396" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B396" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="397" spans="1:2">
       <c r="A397" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B397" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="398" spans="1:2">
       <c r="A398" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B398" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="399" spans="1:2">
       <c r="A399" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B399" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="400" spans="1:2">
       <c r="A400" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B400" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="401" spans="1:2">
       <c r="A401" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B401" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="402" spans="1:2">
       <c r="A402" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B402" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="403" spans="1:2">
       <c r="A403" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B403" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="404" spans="1:2">
       <c r="A404" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B404" t="s">
         <v>620</v>
@@ -9176,10 +9182,10 @@
     </row>
     <row r="407" spans="1:2">
       <c r="A407" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B407" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -9211,20 +9217,20 @@
         <v>632</v>
       </c>
       <c r="B411" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="412" spans="1:2">
       <c r="A412" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B412" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="413" spans="1:2">
       <c r="A413" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B413" t="s">
         <v>635</v>
@@ -9235,20 +9241,20 @@
         <v>636</v>
       </c>
       <c r="B414" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="415" spans="1:2">
       <c r="A415" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B415" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="416" spans="1:2">
       <c r="A416" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B416" t="s">
         <v>639</v>
@@ -9259,20 +9265,20 @@
         <v>640</v>
       </c>
       <c r="B417" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="418" spans="1:2">
       <c r="A418" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B418" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="419" spans="1:2">
       <c r="A419" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B419" t="s">
         <v>643</v>
@@ -9371,36 +9377,36 @@
         <v>666</v>
       </c>
       <c r="B431" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="432" spans="1:2">
       <c r="A432" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B432" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="433" spans="1:2">
       <c r="A433" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B433" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="434" spans="1:2">
       <c r="A434" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B434" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="435" spans="1:2">
       <c r="A435" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B435" t="s">
         <v>671</v>
@@ -9411,12 +9417,12 @@
         <v>672</v>
       </c>
       <c r="B436" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B437" t="s">
         <v>674</v>
@@ -9491,12 +9497,12 @@
         <v>691</v>
       </c>
       <c r="B446" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="447" spans="1:2">
       <c r="A447" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B447" t="s">
         <v>693</v>
@@ -9547,12 +9553,12 @@
         <v>704</v>
       </c>
       <c r="B453" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B454" t="s">
         <v>706</v>
@@ -9627,36 +9633,36 @@
         <v>723</v>
       </c>
       <c r="B463" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="464" spans="1:2">
       <c r="A464" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B464" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="465" spans="1:2">
       <c r="A465" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B465" t="s">
-        <v>485</v>
+        <v>726</v>
       </c>
     </row>
     <row r="466" spans="1:2">
       <c r="A466" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B466" t="s">
-        <v>726</v>
+        <v>487</v>
       </c>
     </row>
     <row r="467" spans="1:2">
       <c r="A467" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B467" t="s">
         <v>728</v>
@@ -9675,12 +9681,12 @@
         <v>731</v>
       </c>
       <c r="B469" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B470" t="s">
         <v>733</v>
@@ -9691,36 +9697,36 @@
         <v>734</v>
       </c>
       <c r="B471" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B472" t="s">
-        <v>485</v>
+        <v>736</v>
       </c>
     </row>
     <row r="473" spans="1:2">
       <c r="A473" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B473" t="s">
-        <v>736</v>
+        <v>487</v>
       </c>
     </row>
     <row r="474" spans="1:2">
       <c r="A474" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B474" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="475" spans="1:2">
       <c r="A475" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B475" t="s">
         <v>739</v>
@@ -9731,12 +9737,12 @@
         <v>740</v>
       </c>
       <c r="B476" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B477" t="s">
         <v>742</v>
@@ -9747,20 +9753,20 @@
         <v>743</v>
       </c>
       <c r="B478" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B479" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B480" t="s">
         <v>746</v>
@@ -9771,12 +9777,12 @@
         <v>747</v>
       </c>
       <c r="B481" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B482" t="s">
         <v>749</v>
@@ -9795,44 +9801,44 @@
         <v>752</v>
       </c>
       <c r="B484" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B485" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="486" spans="1:2">
       <c r="A486" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B486" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B487" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B488" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="489" spans="1:2">
       <c r="A489" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B489" t="s">
         <v>758</v>
@@ -9995,20 +10001,20 @@
         <v>797</v>
       </c>
       <c r="B509" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="510" spans="1:2">
       <c r="A510" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B510" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="511" spans="1:2">
       <c r="A511" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B511" t="s">
         <v>800</v>
@@ -10019,12 +10025,12 @@
         <v>801</v>
       </c>
       <c r="B512" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="A513" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B513" t="s">
         <v>803</v>
@@ -10035,12 +10041,12 @@
         <v>804</v>
       </c>
       <c r="B514" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="A515" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B515" t="s">
         <v>806</v>
@@ -10059,28 +10065,28 @@
         <v>809</v>
       </c>
       <c r="B517" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B518" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="519" spans="1:2">
       <c r="A519" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B519" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="520" spans="1:2">
       <c r="A520" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B520" t="s">
         <v>813</v>
@@ -10171,12 +10177,12 @@
         <v>834</v>
       </c>
       <c r="B531" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="532" spans="1:2">
       <c r="A532" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B532" t="s">
         <v>836</v>
@@ -10195,28 +10201,28 @@
         <v>839</v>
       </c>
       <c r="B534" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B535" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="536" spans="1:2">
       <c r="A536" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B536" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="537" spans="1:2">
       <c r="A537" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B537" t="s">
         <v>843</v>
@@ -10227,52 +10233,52 @@
         <v>844</v>
       </c>
       <c r="B538" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B539" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B540" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B541" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="542" spans="1:2">
       <c r="A542" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B542" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B543" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B544" t="s">
         <v>851</v>
@@ -10283,12 +10289,12 @@
         <v>852</v>
       </c>
       <c r="B545" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B546" t="s">
         <v>854</v>
@@ -10307,60 +10313,60 @@
         <v>857</v>
       </c>
       <c r="B548" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B549" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B550" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B551" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="552" spans="1:2">
       <c r="A552" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B552" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B553" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B554" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B555" t="s">
         <v>865</v>
@@ -10419,28 +10425,28 @@
         <v>878</v>
       </c>
       <c r="B562" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="563" spans="1:2">
       <c r="A563" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B563" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="564" spans="1:2">
       <c r="A564" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B564" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="565" spans="1:2">
       <c r="A565" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B565" t="s">
         <v>882</v>
@@ -10459,12 +10465,12 @@
         <v>885</v>
       </c>
       <c r="B567" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B568" t="s">
         <v>887</v>
@@ -10483,12 +10489,12 @@
         <v>890</v>
       </c>
       <c r="B570" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="571" spans="1:2">
       <c r="A571" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B571" t="s">
         <v>892</v>
@@ -10515,44 +10521,44 @@
         <v>897</v>
       </c>
       <c r="B574" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="575" spans="1:2">
       <c r="A575" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B575" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="576" spans="1:2">
       <c r="A576" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B576" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="577" spans="1:2">
       <c r="A577" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B577" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B578" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B579" t="s">
         <v>903</v>
@@ -10571,12 +10577,12 @@
         <v>906</v>
       </c>
       <c r="B581" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B582" t="s">
         <v>908</v>
@@ -10603,12 +10609,12 @@
         <v>913</v>
       </c>
       <c r="B585" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="586" spans="1:2">
       <c r="A586" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B586" t="s">
         <v>915</v>
@@ -10619,12 +10625,12 @@
         <v>916</v>
       </c>
       <c r="B587" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B588" t="s">
         <v>918</v>
@@ -10667,12 +10673,12 @@
         <v>927</v>
       </c>
       <c r="B593" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B594" t="s">
         <v>929</v>
@@ -10683,20 +10689,20 @@
         <v>930</v>
       </c>
       <c r="B595" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B596" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="597" spans="1:2">
       <c r="A597" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B597" t="s">
         <v>933</v>
@@ -10739,20 +10745,20 @@
         <v>942</v>
       </c>
       <c r="B602" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B603" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B604" t="s">
         <v>945</v>
@@ -10763,20 +10769,20 @@
         <v>946</v>
       </c>
       <c r="B605" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="606" spans="1:2">
       <c r="A606" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B606" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="607" spans="1:2">
       <c r="A607" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B607" t="s">
         <v>949</v>
@@ -10787,12 +10793,12 @@
         <v>950</v>
       </c>
       <c r="B608" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="609" spans="1:2">
       <c r="A609" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B609" t="s">
         <v>952</v>
@@ -10811,20 +10817,20 @@
         <v>955</v>
       </c>
       <c r="B611" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B612" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B613" t="s">
         <v>958</v>
@@ -10843,20 +10849,20 @@
         <v>961</v>
       </c>
       <c r="B615" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B616" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B617" t="s">
         <v>964</v>
@@ -10891,20 +10897,20 @@
         <v>971</v>
       </c>
       <c r="B621" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B622" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B623" t="s">
         <v>974</v>
@@ -10915,20 +10921,20 @@
         <v>975</v>
       </c>
       <c r="B624" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B625" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="626" spans="1:2">
       <c r="A626" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B626" t="s">
         <v>978</v>
@@ -10955,92 +10961,92 @@
         <v>983</v>
       </c>
       <c r="B629" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="630" spans="1:2">
       <c r="A630" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B630" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B631" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B632" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B633" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B634" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="635" spans="1:2">
       <c r="A635" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B635" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B636" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B637" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B638" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B639" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B640" t="s">
         <v>995</v>
@@ -11051,36 +11057,36 @@
         <v>996</v>
       </c>
       <c r="B641" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B642" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B643" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B644" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B645" t="s">
         <v>1001</v>
@@ -11115,12 +11121,12 @@
         <v>1008</v>
       </c>
       <c r="B649" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B650" t="s">
         <v>1010</v>
@@ -11131,12 +11137,12 @@
         <v>1011</v>
       </c>
       <c r="B651" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B652" t="s">
         <v>1013</v>
@@ -11147,12 +11153,12 @@
         <v>1014</v>
       </c>
       <c r="B653" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B654" t="s">
         <v>1016</v>
@@ -11171,12 +11177,12 @@
         <v>1019</v>
       </c>
       <c r="B656" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="657" spans="1:2">
       <c r="A657" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B657" t="s">
         <v>1021</v>
@@ -11235,36 +11241,36 @@
         <v>1034</v>
       </c>
       <c r="B664" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="665" spans="1:2">
       <c r="A665" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B665" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="666" spans="1:2">
       <c r="A666" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B666" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="667" spans="1:2">
       <c r="A667" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B667" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="668" spans="1:2">
       <c r="A668" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B668" t="s">
         <v>1039</v>
@@ -11283,28 +11289,28 @@
         <v>1042</v>
       </c>
       <c r="B670" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="671" spans="1:2">
       <c r="A671" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B671" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="672" spans="1:2">
       <c r="A672" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B672" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="673" spans="1:2">
       <c r="A673" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B673" t="s">
         <v>1046</v>
@@ -11315,44 +11321,44 @@
         <v>1047</v>
       </c>
       <c r="B674" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B675" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="676" spans="1:2">
       <c r="A676" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B676" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B677" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="678" spans="1:2">
       <c r="A678" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B678" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="679" spans="1:2">
       <c r="A679" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B679" t="s">
         <v>1053</v>
@@ -11371,28 +11377,28 @@
         <v>1056</v>
       </c>
       <c r="B681" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="682" spans="1:2">
       <c r="A682" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B682" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="683" spans="1:2">
       <c r="A683" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B683" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="684" spans="1:2">
       <c r="A684" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B684" t="s">
         <v>1060</v>
@@ -11475,12 +11481,12 @@
         <v>1079</v>
       </c>
       <c r="B694" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="695" spans="1:2">
       <c r="A695" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B695" t="s">
         <v>1081</v>
@@ -11499,12 +11505,12 @@
         <v>1084</v>
       </c>
       <c r="B697" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="698" spans="1:2">
       <c r="A698" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B698" t="s">
         <v>1086</v>
@@ -11523,12 +11529,12 @@
         <v>1089</v>
       </c>
       <c r="B700" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="701" spans="1:2">
       <c r="A701" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B701" t="s">
         <v>1091</v>
@@ -11539,20 +11545,20 @@
         <v>1092</v>
       </c>
       <c r="B702" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="703" spans="1:2">
       <c r="A703" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B703" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B704" t="s">
         <v>1095</v>
@@ -11563,60 +11569,60 @@
         <v>1096</v>
       </c>
       <c r="B705" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="706" spans="1:2">
       <c r="A706" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B706" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="707" spans="1:2">
       <c r="A707" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B707" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="708" spans="1:2">
       <c r="A708" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B708" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B709" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B710" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B711" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B712" t="s">
         <v>1104</v>
@@ -11627,12 +11633,12 @@
         <v>1105</v>
       </c>
       <c r="B713" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B714" t="s">
         <v>1107</v>
@@ -11643,20 +11649,20 @@
         <v>1108</v>
       </c>
       <c r="B715" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B716" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B717" t="s">
         <v>1111</v>
@@ -11747,12 +11753,12 @@
         <v>1132</v>
       </c>
       <c r="B728" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B729" t="s">
         <v>1134</v>
@@ -11771,12 +11777,12 @@
         <v>1137</v>
       </c>
       <c r="B731" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B732" t="s">
         <v>1139</v>
@@ -11795,28 +11801,28 @@
         <v>1142</v>
       </c>
       <c r="B734" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="735" spans="1:2">
       <c r="A735" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B735" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="736" spans="1:2">
       <c r="A736" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B736" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="737" spans="1:2">
       <c r="A737" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B737" t="s">
         <v>1146</v>
@@ -11827,44 +11833,44 @@
         <v>1147</v>
       </c>
       <c r="B738" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B739" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="740" spans="1:2">
       <c r="A740" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B740" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="741" spans="1:2">
       <c r="A741" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B741" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="742" spans="1:2">
       <c r="A742" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B742" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B743" t="s">
         <v>1153</v>
@@ -11883,36 +11889,36 @@
         <v>1156</v>
       </c>
       <c r="B745" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="746" spans="1:2">
       <c r="A746" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B746" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B747" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B748" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B749" t="s">
         <v>1161</v>
@@ -11971,12 +11977,12 @@
         <v>1174</v>
       </c>
       <c r="B756" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B757" t="s">
         <v>1176</v>
@@ -12003,12 +12009,12 @@
         <v>1181</v>
       </c>
       <c r="B760" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="761" spans="1:2">
       <c r="A761" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B761" t="s">
         <v>1183</v>
@@ -12019,20 +12025,20 @@
         <v>1184</v>
       </c>
       <c r="B762" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="763" spans="1:2">
       <c r="A763" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B763" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B764" t="s">
         <v>1187</v>
@@ -12072,15 +12078,15 @@
     </row>
     <row r="769" spans="1:2">
       <c r="A769" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B769" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B770" t="s">
         <v>1197</v>
@@ -12107,28 +12113,28 @@
         <v>1202</v>
       </c>
       <c r="B773" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="774" spans="1:2">
       <c r="A774" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B774" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="775" spans="1:2">
       <c r="A775" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B775" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="776" spans="1:2">
       <c r="A776" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B776" t="s">
         <v>1206</v>
@@ -12139,20 +12145,20 @@
         <v>1207</v>
       </c>
       <c r="B777" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="778" spans="1:2">
       <c r="A778" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B778" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="779" spans="1:2">
       <c r="A779" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B779" t="s">
         <v>1210</v>
@@ -12187,28 +12193,28 @@
         <v>1217</v>
       </c>
       <c r="B783" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B784" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="785" spans="1:2">
       <c r="A785" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B785" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B786" t="s">
         <v>1221</v>
@@ -12227,12 +12233,12 @@
         <v>1224</v>
       </c>
       <c r="B788" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="789" spans="1:2">
       <c r="A789" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B789" t="s">
         <v>1226</v>
@@ -12243,60 +12249,60 @@
         <v>1227</v>
       </c>
       <c r="B790" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="791" spans="1:2">
       <c r="A791" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B791" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B792" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B793" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B794" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B795" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B796" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B797" t="s">
         <v>1235</v>
@@ -12307,12 +12313,12 @@
         <v>1236</v>
       </c>
       <c r="B798" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B799" t="s">
         <v>1238</v>
@@ -12379,36 +12385,36 @@
         <v>1253</v>
       </c>
       <c r="B807" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B808" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B809" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B810" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B811" t="s">
         <v>1258</v>
@@ -12443,12 +12449,12 @@
         <v>1265</v>
       </c>
       <c r="B815" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B816" t="s">
         <v>1267</v>
@@ -12483,12 +12489,12 @@
         <v>1274</v>
       </c>
       <c r="B820" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B821" t="s">
         <v>1276</v>
@@ -12499,12 +12505,12 @@
         <v>1277</v>
       </c>
       <c r="B822" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B823" t="s">
         <v>1279</v>
@@ -12515,12 +12521,12 @@
         <v>1280</v>
       </c>
       <c r="B824" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B825" t="s">
         <v>1282</v>
@@ -12531,12 +12537,12 @@
         <v>1283</v>
       </c>
       <c r="B826" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B827" t="s">
         <v>1285</v>
@@ -12547,23 +12553,23 @@
         <v>1286</v>
       </c>
       <c r="B828" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B829" t="s">
-        <v>714</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B830" t="s">
-        <v>1289</v>
+        <v>716</v>
       </c>
     </row>
     <row r="831" spans="1:2">
@@ -12579,36 +12585,36 @@
         <v>1292</v>
       </c>
       <c r="B832" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B833" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B834" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B835" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B836" t="s">
         <v>1297</v>
@@ -12643,12 +12649,12 @@
         <v>1304</v>
       </c>
       <c r="B840" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B841" t="s">
         <v>1306</v>
@@ -12667,36 +12673,36 @@
         <v>1309</v>
       </c>
       <c r="B843" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B844" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B845" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B846" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B847" t="s">
         <v>1314</v>
@@ -12803,60 +12809,60 @@
         <v>1339</v>
       </c>
       <c r="B860" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B861" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B862" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B863" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B864" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B865" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="866" spans="1:2">
       <c r="A866" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B866" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B867" t="s">
         <v>1347</v>
@@ -12867,28 +12873,28 @@
         <v>1348</v>
       </c>
       <c r="B868" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B869" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B870" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B871" t="s">
         <v>1352</v>
@@ -12907,12 +12913,12 @@
         <v>1355</v>
       </c>
       <c r="B873" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B874" t="s">
         <v>1357</v>
@@ -12939,15 +12945,15 @@
         <v>1362</v>
       </c>
       <c r="B877" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B878" t="s">
         <v>1363</v>
-      </c>
-      <c r="B878" t="s">
-        <v>1364</v>
       </c>
     </row>
     <row r="879" spans="1:2">
@@ -12955,20 +12961,20 @@
         <v>1365</v>
       </c>
       <c r="B879" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B880" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B881" t="s">
         <v>1368</v>
@@ -12995,12 +13001,12 @@
         <v>1373</v>
       </c>
       <c r="B884" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B885" t="s">
         <v>1375</v>
@@ -13019,12 +13025,12 @@
         <v>1378</v>
       </c>
       <c r="B887" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B888" t="s">
         <v>1380</v>
@@ -13035,28 +13041,28 @@
         <v>1381</v>
       </c>
       <c r="B889" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B890" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="B891" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="B892" t="s">
         <v>1385</v>
@@ -13067,20 +13073,20 @@
         <v>1386</v>
       </c>
       <c r="B893" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="B894" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B895" t="s">
         <v>1389</v>
@@ -13107,20 +13113,20 @@
         <v>1394</v>
       </c>
       <c r="B898" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="B899" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B900" t="s">
         <v>1397</v>
@@ -13163,60 +13169,60 @@
         <v>1406</v>
       </c>
       <c r="B905" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="B906" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B907" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="B908" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B909" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="B910" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B911" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="B912" t="s">
         <v>1414</v>
@@ -13251,20 +13257,20 @@
         <v>1421</v>
       </c>
       <c r="B916" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B917" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B918" t="s">
         <v>1424</v>
@@ -13307,20 +13313,20 @@
         <v>1433</v>
       </c>
       <c r="B923" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B924" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B925" t="s">
         <v>1436</v>
@@ -13355,12 +13361,12 @@
         <v>1443</v>
       </c>
       <c r="B929" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B930" t="s">
         <v>1445</v>
@@ -13379,20 +13385,20 @@
         <v>1448</v>
       </c>
       <c r="B932" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="B933" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B934" t="s">
         <v>1451</v>
@@ -13403,12 +13409,12 @@
         <v>1452</v>
       </c>
       <c r="B935" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="B936" t="s">
         <v>1454</v>
@@ -13435,12 +13441,12 @@
         <v>1459</v>
       </c>
       <c r="B939" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B940" t="s">
         <v>1461</v>
@@ -13459,36 +13465,36 @@
         <v>1464</v>
       </c>
       <c r="B942" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="B943" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B944" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B945" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B946" t="s">
         <v>1469</v>
@@ -13499,52 +13505,52 @@
         <v>1470</v>
       </c>
       <c r="B947" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B948" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B949" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B950" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B951" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B952" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B953" t="s">
         <v>1477</v>
@@ -13579,20 +13585,20 @@
         <v>1484</v>
       </c>
       <c r="B957" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B958" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B959" t="s">
         <v>1487</v>
@@ -13643,36 +13649,36 @@
         <v>1498</v>
       </c>
       <c r="B965" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B966" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B967" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B968" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B969" t="s">
         <v>1503</v>
@@ -13691,12 +13697,12 @@
         <v>1506</v>
       </c>
       <c r="B971" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B972" t="s">
         <v>1508</v>
@@ -13763,20 +13769,20 @@
         <v>1523</v>
       </c>
       <c r="B980" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="B981" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B982" t="s">
         <v>1526</v>
@@ -13795,28 +13801,28 @@
         <v>1529</v>
       </c>
       <c r="B984" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B985" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B986" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B987" t="s">
         <v>1533</v>
@@ -13859,12 +13865,12 @@
         <v>1542</v>
       </c>
       <c r="B992" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B993" t="s">
         <v>1544</v>
@@ -13875,12 +13881,12 @@
         <v>1545</v>
       </c>
       <c r="B994" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B995" t="s">
         <v>1547</v>
@@ -13899,28 +13905,28 @@
         <v>1550</v>
       </c>
       <c r="B997" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B998" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B999" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B1000" t="s">
         <v>1554</v>
@@ -13931,12 +13937,12 @@
         <v>1555</v>
       </c>
       <c r="B1001" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B1002" t="s">
         <v>1557</v>
@@ -13955,36 +13961,36 @@
         <v>1560</v>
       </c>
       <c r="B1004" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B1005" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B1006" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B1007" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B1008" t="s">
         <v>1565</v>
@@ -13995,36 +14001,36 @@
         <v>1566</v>
       </c>
       <c r="B1009" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B1010" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B1011" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B1012" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B1013" t="s">
         <v>1571</v>
@@ -14043,36 +14049,36 @@
         <v>1574</v>
       </c>
       <c r="B1015" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B1016" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="B1017" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B1018" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B1019" t="s">
         <v>1579</v>
@@ -14091,12 +14097,12 @@
         <v>1582</v>
       </c>
       <c r="B1021" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B1022" t="s">
         <v>1584</v>
@@ -14123,12 +14129,12 @@
         <v>1589</v>
       </c>
       <c r="B1025" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B1026" t="s">
         <v>1591</v>
@@ -14139,20 +14145,20 @@
         <v>1592</v>
       </c>
       <c r="B1027" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B1028" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B1029" t="s">
         <v>1595</v>
@@ -14163,52 +14169,52 @@
         <v>1596</v>
       </c>
       <c r="B1030" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B1031" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1032" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B1033" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B1034" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B1035" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B1036" t="s">
         <v>1603</v>
@@ -14227,12 +14233,12 @@
         <v>1606</v>
       </c>
       <c r="B1038" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B1039" t="s">
         <v>1608</v>
@@ -14259,20 +14265,20 @@
         <v>1613</v>
       </c>
       <c r="B1042" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B1043" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B1044" t="s">
         <v>1616</v>
@@ -14299,20 +14305,20 @@
         <v>1621</v>
       </c>
       <c r="B1047" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="B1048" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B1049" t="s">
         <v>1624</v>
@@ -14323,20 +14329,20 @@
         <v>1625</v>
       </c>
       <c r="B1050" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="B1051" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B1052" t="s">
         <v>1628</v>
@@ -14515,12 +14521,12 @@
         <v>1671</v>
       </c>
       <c r="B1074" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B1075" t="s">
         <v>1673</v>
@@ -14531,28 +14537,28 @@
         <v>1674</v>
       </c>
       <c r="B1076" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B1077" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B1078" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B1079" t="s">
         <v>1678</v>
@@ -14563,12 +14569,12 @@
         <v>1679</v>
       </c>
       <c r="B1080" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B1081" t="s">
         <v>1681</v>
@@ -14579,28 +14585,28 @@
         <v>1682</v>
       </c>
       <c r="B1082" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="B1083" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B1084" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B1085" t="s">
         <v>1686</v>
@@ -14611,20 +14617,20 @@
         <v>1687</v>
       </c>
       <c r="B1086" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B1087" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B1088" t="s">
         <v>1690</v>
@@ -14659,20 +14665,20 @@
         <v>1697</v>
       </c>
       <c r="B1092" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B1093" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B1094" t="s">
         <v>1700</v>
@@ -14715,12 +14721,12 @@
         <v>1709</v>
       </c>
       <c r="B1099" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B1100" t="s">
         <v>1711</v>
@@ -14747,12 +14753,12 @@
         <v>1716</v>
       </c>
       <c r="B1103" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B1104" t="s">
         <v>1718</v>
@@ -14763,20 +14769,20 @@
         <v>1719</v>
       </c>
       <c r="B1105" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="B1106" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="B1107" t="s">
         <v>1722</v>
@@ -14787,12 +14793,12 @@
         <v>1723</v>
       </c>
       <c r="B1108" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="B1109" t="s">
         <v>1725</v>
@@ -14819,20 +14825,20 @@
         <v>1730</v>
       </c>
       <c r="B1112" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="B1113" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="B1114" t="s">
         <v>1733</v>
@@ -14987,44 +14993,44 @@
         <v>1770</v>
       </c>
       <c r="B1133" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="B1134" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="B1135" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="B1136" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="B1137" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="B1138" t="s">
         <v>1776</v>
@@ -15043,36 +15049,36 @@
         <v>1779</v>
       </c>
       <c r="B1140" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="B1141" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="B1142" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="B1143" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="B1144" t="s">
         <v>1784</v>
@@ -15083,12 +15089,12 @@
         <v>1785</v>
       </c>
       <c r="B1145" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B1146" t="s">
         <v>1787</v>
@@ -15115,12 +15121,12 @@
         <v>1792</v>
       </c>
       <c r="B1149" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="B1150" t="s">
         <v>1794</v>
@@ -15131,12 +15137,12 @@
         <v>1795</v>
       </c>
       <c r="B1151" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B1152" t="s">
         <v>1797</v>
@@ -15147,12 +15153,12 @@
         <v>1798</v>
       </c>
       <c r="B1153" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="B1154" t="s">
         <v>1800</v>
@@ -15187,44 +15193,44 @@
         <v>1807</v>
       </c>
       <c r="B1158" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1159" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B1160" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="B1161" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B1162" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="B1163" t="s">
         <v>1813</v>
@@ -15235,28 +15241,28 @@
         <v>1814</v>
       </c>
       <c r="B1164" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B1165" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="B1166" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="B1167" t="s">
         <v>1818</v>
@@ -15267,36 +15273,36 @@
         <v>1819</v>
       </c>
       <c r="B1168" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="B1169" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="B1170" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="B1171" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="B1172" t="s">
         <v>1824</v>
@@ -15315,12 +15321,12 @@
         <v>1827</v>
       </c>
       <c r="B1174" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B1175" t="s">
         <v>1829</v>
@@ -15331,20 +15337,20 @@
         <v>1830</v>
       </c>
       <c r="B1176" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="B1177" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="B1178" t="s">
         <v>1833</v>
@@ -15371,36 +15377,36 @@
         <v>1838</v>
       </c>
       <c r="B1181" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="B1182" t="s">
-        <v>716</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="B1183" t="s">
-        <v>1840</v>
+        <v>718</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="B1184" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="B1185" t="s">
         <v>1843</v>
@@ -15411,20 +15417,20 @@
         <v>1844</v>
       </c>
       <c r="B1186" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="B1187" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="B1188" t="s">
         <v>1847</v>
@@ -15446,8 +15452,16 @@
         <v>1851</v>
       </c>
     </row>
+    <row r="1191" spans="1:2">
+      <c r="A1191" t="s">
+        <v>1852</v>
+      </c>
+      <c r="B1191" t="s">
+        <v>1853</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1190"/>
+  <autoFilter ref="A1:B1191"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/es/headTags.xlsx
+++ b/lang/es/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1192</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1856">
   <si>
     <t>en</t>
   </si>
@@ -4049,6 +4049,12 @@
   </si>
   <si>
     <t>Pop Team Epic</t>
+  </si>
+  <si>
+    <t>Popee the Performer</t>
+  </si>
+  <si>
+    <t>Popee, el artista</t>
   </si>
   <si>
     <t>POPGOES</t>
@@ -5925,7 +5931,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1191"/>
+  <dimension ref="A1:B1192"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -12841,36 +12847,36 @@
         <v>1344</v>
       </c>
       <c r="B864" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B865" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="866" spans="1:2">
       <c r="A866" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B866" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B867" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B868" t="s">
         <v>1349</v>
@@ -12881,28 +12887,28 @@
         <v>1350</v>
       </c>
       <c r="B869" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B870" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B871" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B872" t="s">
         <v>1354</v>
@@ -12921,12 +12927,12 @@
         <v>1357</v>
       </c>
       <c r="B874" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B875" t="s">
         <v>1359</v>
@@ -12953,15 +12959,15 @@
         <v>1364</v>
       </c>
       <c r="B878" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B879" t="s">
         <v>1365</v>
-      </c>
-      <c r="B879" t="s">
-        <v>1366</v>
       </c>
     </row>
     <row r="880" spans="1:2">
@@ -12969,20 +12975,20 @@
         <v>1367</v>
       </c>
       <c r="B880" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B881" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B882" t="s">
         <v>1370</v>
@@ -13009,12 +13015,12 @@
         <v>1375</v>
       </c>
       <c r="B885" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B886" t="s">
         <v>1377</v>
@@ -13033,12 +13039,12 @@
         <v>1380</v>
       </c>
       <c r="B888" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="B889" t="s">
         <v>1382</v>
@@ -13049,28 +13055,28 @@
         <v>1383</v>
       </c>
       <c r="B890" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="B891" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="B892" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="B893" t="s">
         <v>1387</v>
@@ -13081,20 +13087,20 @@
         <v>1388</v>
       </c>
       <c r="B894" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="B895" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="B896" t="s">
         <v>1391</v>
@@ -13121,20 +13127,20 @@
         <v>1396</v>
       </c>
       <c r="B899" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B900" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="B901" t="s">
         <v>1399</v>
@@ -13177,60 +13183,60 @@
         <v>1408</v>
       </c>
       <c r="B906" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="B907" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B908" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="B909" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B910" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="B911" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="B912" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B913" t="s">
         <v>1416</v>
@@ -13265,20 +13271,20 @@
         <v>1423</v>
       </c>
       <c r="B917" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B918" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="B919" t="s">
         <v>1426</v>
@@ -13321,20 +13327,20 @@
         <v>1435</v>
       </c>
       <c r="B924" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B925" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="B926" t="s">
         <v>1438</v>
@@ -13369,12 +13375,12 @@
         <v>1445</v>
       </c>
       <c r="B930" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B931" t="s">
         <v>1447</v>
@@ -13393,20 +13399,20 @@
         <v>1450</v>
       </c>
       <c r="B933" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B934" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="B935" t="s">
         <v>1453</v>
@@ -13417,12 +13423,12 @@
         <v>1454</v>
       </c>
       <c r="B936" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B937" t="s">
         <v>1456</v>
@@ -13449,12 +13455,12 @@
         <v>1461</v>
       </c>
       <c r="B940" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B941" t="s">
         <v>1463</v>
@@ -13473,36 +13479,36 @@
         <v>1466</v>
       </c>
       <c r="B943" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B944" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B945" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B946" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B947" t="s">
         <v>1471</v>
@@ -13513,52 +13519,52 @@
         <v>1472</v>
       </c>
       <c r="B948" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B949" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B950" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B951" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B952" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B953" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B954" t="s">
         <v>1479</v>
@@ -13593,20 +13599,20 @@
         <v>1486</v>
       </c>
       <c r="B958" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B959" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B960" t="s">
         <v>1489</v>
@@ -13657,36 +13663,36 @@
         <v>1500</v>
       </c>
       <c r="B966" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B967" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B968" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B969" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B970" t="s">
         <v>1505</v>
@@ -13705,12 +13711,12 @@
         <v>1508</v>
       </c>
       <c r="B972" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="B973" t="s">
         <v>1510</v>
@@ -13777,20 +13783,20 @@
         <v>1525</v>
       </c>
       <c r="B981" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="B982" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B983" t="s">
         <v>1528</v>
@@ -13809,28 +13815,28 @@
         <v>1531</v>
       </c>
       <c r="B985" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B986" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="B987" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="B988" t="s">
         <v>1535</v>
@@ -13873,12 +13879,12 @@
         <v>1544</v>
       </c>
       <c r="B993" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B994" t="s">
         <v>1546</v>
@@ -13889,12 +13895,12 @@
         <v>1547</v>
       </c>
       <c r="B995" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B996" t="s">
         <v>1549</v>
@@ -13913,28 +13919,28 @@
         <v>1552</v>
       </c>
       <c r="B998" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B999" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B1000" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B1001" t="s">
         <v>1556</v>
@@ -13945,12 +13951,12 @@
         <v>1557</v>
       </c>
       <c r="B1002" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B1003" t="s">
         <v>1559</v>
@@ -13969,36 +13975,36 @@
         <v>1562</v>
       </c>
       <c r="B1005" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B1006" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B1007" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B1008" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B1009" t="s">
         <v>1567</v>
@@ -14009,36 +14015,36 @@
         <v>1568</v>
       </c>
       <c r="B1010" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B1011" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B1012" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B1013" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B1014" t="s">
         <v>1573</v>
@@ -14057,36 +14063,36 @@
         <v>1576</v>
       </c>
       <c r="B1016" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B1017" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B1018" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="B1019" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B1020" t="s">
         <v>1581</v>
@@ -14105,12 +14111,12 @@
         <v>1584</v>
       </c>
       <c r="B1022" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B1023" t="s">
         <v>1586</v>
@@ -14137,12 +14143,12 @@
         <v>1591</v>
       </c>
       <c r="B1026" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B1027" t="s">
         <v>1593</v>
@@ -14153,20 +14159,20 @@
         <v>1594</v>
       </c>
       <c r="B1028" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="B1029" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B1030" t="s">
         <v>1597</v>
@@ -14177,52 +14183,52 @@
         <v>1598</v>
       </c>
       <c r="B1031" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B1032" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B1033" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B1034" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B1035" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="B1036" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B1037" t="s">
         <v>1605</v>
@@ -14241,12 +14247,12 @@
         <v>1608</v>
       </c>
       <c r="B1039" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B1040" t="s">
         <v>1610</v>
@@ -14273,20 +14279,20 @@
         <v>1615</v>
       </c>
       <c r="B1043" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B1044" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B1045" t="s">
         <v>1618</v>
@@ -14313,20 +14319,20 @@
         <v>1623</v>
       </c>
       <c r="B1048" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B1049" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B1050" t="s">
         <v>1626</v>
@@ -14337,20 +14343,20 @@
         <v>1627</v>
       </c>
       <c r="B1051" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B1052" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B1053" t="s">
         <v>1630</v>
@@ -14529,12 +14535,12 @@
         <v>1673</v>
       </c>
       <c r="B1075" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B1076" t="s">
         <v>1675</v>
@@ -14545,28 +14551,28 @@
         <v>1676</v>
       </c>
       <c r="B1077" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B1078" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B1079" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B1080" t="s">
         <v>1680</v>
@@ -14577,12 +14583,12 @@
         <v>1681</v>
       </c>
       <c r="B1081" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="B1082" t="s">
         <v>1683</v>
@@ -14593,28 +14599,28 @@
         <v>1684</v>
       </c>
       <c r="B1083" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B1084" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B1085" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B1086" t="s">
         <v>1688</v>
@@ -14625,20 +14631,20 @@
         <v>1689</v>
       </c>
       <c r="B1087" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B1088" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B1089" t="s">
         <v>1692</v>
@@ -14673,20 +14679,20 @@
         <v>1699</v>
       </c>
       <c r="B1093" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B1094" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B1095" t="s">
         <v>1702</v>
@@ -14729,12 +14735,12 @@
         <v>1711</v>
       </c>
       <c r="B1100" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B1101" t="s">
         <v>1713</v>
@@ -14761,12 +14767,12 @@
         <v>1718</v>
       </c>
       <c r="B1104" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="B1105" t="s">
         <v>1720</v>
@@ -14777,20 +14783,20 @@
         <v>1721</v>
       </c>
       <c r="B1106" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="B1107" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="B1108" t="s">
         <v>1724</v>
@@ -14801,12 +14807,12 @@
         <v>1725</v>
       </c>
       <c r="B1109" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="B1110" t="s">
         <v>1727</v>
@@ -14833,20 +14839,20 @@
         <v>1732</v>
       </c>
       <c r="B1113" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B1114" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="B1115" t="s">
         <v>1735</v>
@@ -15001,44 +15007,44 @@
         <v>1772</v>
       </c>
       <c r="B1134" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="B1135" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="B1136" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="B1137" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="B1138" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="B1139" t="s">
         <v>1778</v>
@@ -15057,36 +15063,36 @@
         <v>1781</v>
       </c>
       <c r="B1141" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="B1142" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="B1143" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="B1144" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="B1145" t="s">
         <v>1786</v>
@@ -15097,12 +15103,12 @@
         <v>1787</v>
       </c>
       <c r="B1146" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="B1147" t="s">
         <v>1789</v>
@@ -15129,12 +15135,12 @@
         <v>1794</v>
       </c>
       <c r="B1150" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="B1151" t="s">
         <v>1796</v>
@@ -15145,12 +15151,12 @@
         <v>1797</v>
       </c>
       <c r="B1152" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="B1153" t="s">
         <v>1799</v>
@@ -15161,12 +15167,12 @@
         <v>1800</v>
       </c>
       <c r="B1154" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="B1155" t="s">
         <v>1802</v>
@@ -15201,44 +15207,44 @@
         <v>1809</v>
       </c>
       <c r="B1159" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="B1160" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B1161" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="B1162" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="B1163" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="B1164" t="s">
         <v>1815</v>
@@ -15249,28 +15255,28 @@
         <v>1816</v>
       </c>
       <c r="B1165" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="B1166" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B1167" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B1168" t="s">
         <v>1820</v>
@@ -15281,36 +15287,36 @@
         <v>1821</v>
       </c>
       <c r="B1169" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="B1170" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="B1171" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1172" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="B1173" t="s">
         <v>1826</v>
@@ -15329,12 +15335,12 @@
         <v>1829</v>
       </c>
       <c r="B1175" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="B1176" t="s">
         <v>1831</v>
@@ -15345,20 +15351,20 @@
         <v>1832</v>
       </c>
       <c r="B1177" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="B1178" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B1179" t="s">
         <v>1835</v>
@@ -15385,36 +15391,36 @@
         <v>1840</v>
       </c>
       <c r="B1182" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="B1183" t="s">
-        <v>718</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="B1184" t="s">
-        <v>1842</v>
+        <v>718</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="B1185" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="B1186" t="s">
         <v>1845</v>
@@ -15425,20 +15431,20 @@
         <v>1846</v>
       </c>
       <c r="B1187" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="B1188" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="B1189" t="s">
         <v>1849</v>
@@ -15460,8 +15466,16 @@
         <v>1853</v>
       </c>
     </row>
+    <row r="1192" spans="1:2">
+      <c r="A1192" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B1192" t="s">
+        <v>1855</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1191"/>
+  <autoFilter ref="A1:B1192"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/es/headTags.xlsx
+++ b/lang/es/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1193</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1856">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1857">
   <si>
     <t>en</t>
   </si>
@@ -5054,6 +5054,9 @@
   </si>
   <si>
     <t>Tinker's Construct</t>
+  </si>
+  <si>
+    <t>Tiny Takeover</t>
   </si>
   <si>
     <t>Titanfall</t>
@@ -5931,7 +5934,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1192"/>
+  <dimension ref="A1:B1193"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14583,12 +14586,12 @@
         <v>1681</v>
       </c>
       <c r="B1081" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="B1082" t="s">
         <v>1683</v>
@@ -14599,12 +14602,12 @@
         <v>1684</v>
       </c>
       <c r="B1083" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="B1084" t="s">
         <v>1686</v>
@@ -14631,12 +14634,12 @@
         <v>1689</v>
       </c>
       <c r="B1087" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="B1088" t="s">
         <v>1691</v>
@@ -14655,36 +14658,36 @@
         <v>1693</v>
       </c>
       <c r="B1090" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B1091" t="s">
         <v>1695</v>
-      </c>
-      <c r="B1091" t="s">
-        <v>1696</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B1092" t="s">
         <v>1697</v>
-      </c>
-      <c r="B1092" t="s">
-        <v>1698</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B1093" t="s">
         <v>1699</v>
-      </c>
-      <c r="B1093" t="s">
-        <v>1700</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="B1094" t="s">
         <v>1701</v>
@@ -14703,44 +14706,44 @@
         <v>1703</v>
       </c>
       <c r="B1096" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B1097" t="s">
         <v>1705</v>
-      </c>
-      <c r="B1097" t="s">
-        <v>1706</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B1098" t="s">
         <v>1707</v>
-      </c>
-      <c r="B1098" t="s">
-        <v>1708</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B1099" t="s">
         <v>1709</v>
-      </c>
-      <c r="B1099" t="s">
-        <v>1710</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B1100" t="s">
         <v>1711</v>
-      </c>
-      <c r="B1100" t="s">
-        <v>1712</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="B1101" t="s">
         <v>1713</v>
@@ -14751,28 +14754,28 @@
         <v>1714</v>
       </c>
       <c r="B1102" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B1103" t="s">
         <v>1716</v>
-      </c>
-      <c r="B1103" t="s">
-        <v>1717</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B1104" t="s">
         <v>1718</v>
-      </c>
-      <c r="B1104" t="s">
-        <v>1719</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="B1105" t="s">
         <v>1720</v>
@@ -14783,12 +14786,12 @@
         <v>1721</v>
       </c>
       <c r="B1106" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="B1107" t="s">
         <v>1723</v>
@@ -14807,12 +14810,12 @@
         <v>1725</v>
       </c>
       <c r="B1109" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="B1110" t="s">
         <v>1727</v>
@@ -14823,28 +14826,28 @@
         <v>1728</v>
       </c>
       <c r="B1111" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B1112" t="s">
         <v>1730</v>
-      </c>
-      <c r="B1112" t="s">
-        <v>1731</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B1113" t="s">
         <v>1732</v>
-      </c>
-      <c r="B1113" t="s">
-        <v>1733</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="B1114" t="s">
         <v>1734</v>
@@ -14863,156 +14866,156 @@
         <v>1736</v>
       </c>
       <c r="B1116" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B1117" t="s">
         <v>1738</v>
-      </c>
-      <c r="B1117" t="s">
-        <v>1739</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
+        <v>1739</v>
+      </c>
+      <c r="B1118" t="s">
         <v>1740</v>
-      </c>
-      <c r="B1118" t="s">
-        <v>1741</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B1119" t="s">
         <v>1742</v>
-      </c>
-      <c r="B1119" t="s">
-        <v>1743</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B1120" t="s">
         <v>1744</v>
-      </c>
-      <c r="B1120" t="s">
-        <v>1745</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1121" t="s">
         <v>1746</v>
-      </c>
-      <c r="B1121" t="s">
-        <v>1747</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1122" t="s">
         <v>1748</v>
-      </c>
-      <c r="B1122" t="s">
-        <v>1749</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
+        <v>1749</v>
+      </c>
+      <c r="B1123" t="s">
         <v>1750</v>
-      </c>
-      <c r="B1123" t="s">
-        <v>1751</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
+        <v>1751</v>
+      </c>
+      <c r="B1124" t="s">
         <v>1752</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B1125" t="s">
         <v>1754</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>1755</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B1126" t="s">
         <v>1756</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>1757</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B1127" t="s">
         <v>1758</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>1759</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B1128" t="s">
         <v>1760</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>1761</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B1129" t="s">
         <v>1762</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>1763</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B1130" t="s">
         <v>1764</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>1765</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B1131" t="s">
         <v>1766</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>1767</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B1132" t="s">
         <v>1768</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>1769</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B1133" t="s">
         <v>1770</v>
-      </c>
-      <c r="B1133" t="s">
-        <v>1771</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B1134" t="s">
         <v>1772</v>
-      </c>
-      <c r="B1134" t="s">
-        <v>1773</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="B1135" t="s">
         <v>1774</v>
@@ -15055,20 +15058,20 @@
         <v>1779</v>
       </c>
       <c r="B1140" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B1141" t="s">
         <v>1781</v>
-      </c>
-      <c r="B1141" t="s">
-        <v>1782</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="B1142" t="s">
         <v>1783</v>
@@ -15103,12 +15106,12 @@
         <v>1787</v>
       </c>
       <c r="B1146" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B1147" t="s">
         <v>1789</v>
@@ -15119,28 +15122,28 @@
         <v>1790</v>
       </c>
       <c r="B1148" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B1149" t="s">
         <v>1792</v>
-      </c>
-      <c r="B1149" t="s">
-        <v>1793</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B1150" t="s">
         <v>1794</v>
-      </c>
-      <c r="B1150" t="s">
-        <v>1795</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="B1151" t="s">
         <v>1796</v>
@@ -15151,12 +15154,12 @@
         <v>1797</v>
       </c>
       <c r="B1152" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="B1153" t="s">
         <v>1799</v>
@@ -15167,12 +15170,12 @@
         <v>1800</v>
       </c>
       <c r="B1154" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="B1155" t="s">
         <v>1802</v>
@@ -15183,36 +15186,36 @@
         <v>1803</v>
       </c>
       <c r="B1156" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B1157" t="s">
         <v>1805</v>
-      </c>
-      <c r="B1157" t="s">
-        <v>1806</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B1158" t="s">
         <v>1807</v>
-      </c>
-      <c r="B1158" t="s">
-        <v>1808</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B1159" t="s">
         <v>1809</v>
-      </c>
-      <c r="B1159" t="s">
-        <v>1810</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="B1160" t="s">
         <v>1811</v>
@@ -15255,12 +15258,12 @@
         <v>1816</v>
       </c>
       <c r="B1165" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="B1166" t="s">
         <v>1818</v>
@@ -15287,12 +15290,12 @@
         <v>1821</v>
       </c>
       <c r="B1169" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="B1170" t="s">
         <v>1823</v>
@@ -15327,20 +15330,20 @@
         <v>1827</v>
       </c>
       <c r="B1174" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B1175" t="s">
         <v>1829</v>
-      </c>
-      <c r="B1175" t="s">
-        <v>1830</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="B1176" t="s">
         <v>1831</v>
@@ -15351,12 +15354,12 @@
         <v>1832</v>
       </c>
       <c r="B1177" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="B1178" t="s">
         <v>1834</v>
@@ -15375,28 +15378,28 @@
         <v>1836</v>
       </c>
       <c r="B1180" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B1181" t="s">
         <v>1838</v>
-      </c>
-      <c r="B1181" t="s">
-        <v>1839</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B1182" t="s">
         <v>1840</v>
-      </c>
-      <c r="B1182" t="s">
-        <v>1841</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="B1183" t="s">
         <v>1842</v>
@@ -15407,7 +15410,7 @@
         <v>1843</v>
       </c>
       <c r="B1184" t="s">
-        <v>718</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
@@ -15415,7 +15418,7 @@
         <v>1844</v>
       </c>
       <c r="B1185" t="s">
-        <v>1844</v>
+        <v>718</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
@@ -15431,12 +15434,12 @@
         <v>1846</v>
       </c>
       <c r="B1187" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="B1188" t="s">
         <v>1848</v>
@@ -15455,27 +15458,35 @@
         <v>1850</v>
       </c>
       <c r="B1190" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B1191" t="s">
         <v>1852</v>
-      </c>
-      <c r="B1191" t="s">
-        <v>1853</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B1192" t="s">
         <v>1854</v>
       </c>
-      <c r="B1192" t="s">
+    </row>
+    <row r="1193" spans="1:2">
+      <c r="A1193" t="s">
         <v>1855</v>
       </c>
+      <c r="B1193" t="s">
+        <v>1856</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1192"/>
+  <autoFilter ref="A1:B1193"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/es/headTags.xlsx
+++ b/lang/es/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1197</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1857">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1864">
   <si>
     <t>en</t>
   </si>
@@ -2731,6 +2731,9 @@
     <t>Hypixel</t>
   </si>
   <si>
+    <t>Hypixel (Abiphone)</t>
+  </si>
+  <si>
     <t>Hypixel (Attribute Shard)</t>
   </si>
   <si>
@@ -2752,6 +2755,12 @@
     <t>Hypixel (Engranaje)</t>
   </si>
   <si>
+    <t>Hypixel (Gemstone)</t>
+  </si>
+  <si>
+    <t>Hypixel (Piedra preciosa)</t>
+  </si>
+  <si>
     <t>Hypixel (Minion)</t>
   </si>
   <si>
@@ -2767,6 +2776,12 @@
     <t>Hypixel (NPC)</t>
   </si>
   <si>
+    <t>Hypixel (Pet Items)</t>
+  </si>
+  <si>
+    <t>Hypixel (Artículos para mascotas)</t>
+  </si>
+  <si>
     <t>Hypixel (Pets)</t>
   </si>
   <si>
@@ -2774,6 +2789,12 @@
   </si>
   <si>
     <t>Hypixel (Reforge Stone)</t>
+  </si>
+  <si>
+    <t>Hypixel (Runes)</t>
+  </si>
+  <si>
+    <t>Hypixel (Runas)</t>
   </si>
   <si>
     <t>Hypixel (Sacks)</t>
@@ -5934,7 +5955,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1193"/>
+  <dimension ref="A1:B1197"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -10578,20 +10599,20 @@
         <v>904</v>
       </c>
       <c r="B580" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
+        <v>905</v>
+      </c>
+      <c r="B581" t="s">
         <v>906</v>
-      </c>
-      <c r="B581" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B582" t="s">
         <v>908</v>
@@ -10602,28 +10623,28 @@
         <v>909</v>
       </c>
       <c r="B583" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
+        <v>910</v>
+      </c>
+      <c r="B584" t="s">
         <v>911</v>
-      </c>
-      <c r="B584" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
+        <v>912</v>
+      </c>
+      <c r="B585" t="s">
         <v>913</v>
-      </c>
-      <c r="B585" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="586" spans="1:2">
       <c r="A586" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B586" t="s">
         <v>915</v>
@@ -10666,28 +10687,28 @@
         <v>923</v>
       </c>
       <c r="B591" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="592" spans="1:2">
       <c r="A592" t="s">
+        <v>924</v>
+      </c>
+      <c r="B592" t="s">
         <v>925</v>
-      </c>
-      <c r="B592" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="593" spans="1:2">
       <c r="A593" t="s">
+        <v>926</v>
+      </c>
+      <c r="B593" t="s">
         <v>927</v>
-      </c>
-      <c r="B593" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B594" t="s">
         <v>929</v>
@@ -10706,36 +10727,36 @@
         <v>932</v>
       </c>
       <c r="B596" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="597" spans="1:2">
       <c r="A597" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B597" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
     </row>
     <row r="598" spans="1:2">
       <c r="A598" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B598" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="599" spans="1:2">
       <c r="A599" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B599" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B600" t="s">
         <v>939</v>
@@ -10746,20 +10767,20 @@
         <v>940</v>
       </c>
       <c r="B601" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
+        <v>941</v>
+      </c>
+      <c r="B602" t="s">
         <v>942</v>
-      </c>
-      <c r="B602" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B603" t="s">
         <v>944</v>
@@ -10770,60 +10791,60 @@
         <v>945</v>
       </c>
       <c r="B604" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B605" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="606" spans="1:2">
       <c r="A606" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B606" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
     </row>
     <row r="607" spans="1:2">
       <c r="A607" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="B607" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
     </row>
     <row r="608" spans="1:2">
       <c r="A608" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B608" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="609" spans="1:2">
       <c r="A609" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B609" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B610" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B611" t="s">
         <v>956</v>
@@ -10834,68 +10855,68 @@
         <v>957</v>
       </c>
       <c r="B612" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B613" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="614" spans="1:2">
       <c r="A614" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B614" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B615" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B616" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B617" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="618" spans="1:2">
       <c r="A618" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B618" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="619" spans="1:2">
       <c r="A619" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B619" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="620" spans="1:2">
       <c r="A620" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B620" t="s">
         <v>970</v>
@@ -10906,12 +10927,12 @@
         <v>971</v>
       </c>
       <c r="B621" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B622" t="s">
         <v>973</v>
@@ -10922,52 +10943,52 @@
         <v>974</v>
       </c>
       <c r="B623" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B624" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B625" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
     </row>
     <row r="626" spans="1:2">
       <c r="A626" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="B626" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
     </row>
     <row r="627" spans="1:2">
       <c r="A627" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B627" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B628" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B629" t="s">
         <v>984</v>
@@ -10986,140 +11007,140 @@
         <v>986</v>
       </c>
       <c r="B631" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B632" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B633" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="B634" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
     </row>
     <row r="635" spans="1:2">
       <c r="A635" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="B635" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="B636" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="B637" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="B638" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="B639" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="B640" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="B641" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="B642" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B643" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="B644" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B645" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="B646" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="B647" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B648" t="s">
         <v>1007</v>
@@ -11130,12 +11151,12 @@
         <v>1008</v>
       </c>
       <c r="B649" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B650" t="s">
         <v>1010</v>
@@ -11154,36 +11175,36 @@
         <v>1013</v>
       </c>
       <c r="B652" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B653" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B654" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="655" spans="1:2">
       <c r="A655" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B655" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="656" spans="1:2">
       <c r="A656" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B656" t="s">
         <v>1020</v>
@@ -11194,12 +11215,12 @@
         <v>1021</v>
       </c>
       <c r="B657" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B658" t="s">
         <v>1023</v>
@@ -11226,36 +11247,36 @@
         <v>1028</v>
       </c>
       <c r="B661" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="662" spans="1:2">
       <c r="A662" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B662" t="s">
         <v>1030</v>
-      </c>
-      <c r="B662" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="663" spans="1:2">
       <c r="A663" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B663" t="s">
         <v>1032</v>
-      </c>
-      <c r="B663" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="664" spans="1:2">
       <c r="A664" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B664" t="s">
         <v>1034</v>
-      </c>
-      <c r="B664" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="665" spans="1:2">
       <c r="A665" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B665" t="s">
         <v>1036</v>
@@ -11266,172 +11287,172 @@
         <v>1037</v>
       </c>
       <c r="B666" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="667" spans="1:2">
       <c r="A667" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B667" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="668" spans="1:2">
       <c r="A668" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="B668" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="669" spans="1:2">
       <c r="A669" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="B669" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="670" spans="1:2">
       <c r="A670" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="B670" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="671" spans="1:2">
       <c r="A671" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B671" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="672" spans="1:2">
       <c r="A672" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B672" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="673" spans="1:2">
       <c r="A673" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B673" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="B674" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B675" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="676" spans="1:2">
       <c r="A676" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="B676" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="B677" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="678" spans="1:2">
       <c r="A678" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B678" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="679" spans="1:2">
       <c r="A679" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="B679" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="680" spans="1:2">
       <c r="A680" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="B680" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="681" spans="1:2">
       <c r="A681" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B681" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="682" spans="1:2">
       <c r="A682" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B682" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="683" spans="1:2">
       <c r="A683" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B683" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="684" spans="1:2">
       <c r="A684" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B684" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="B685" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="B686" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B687" t="s">
         <v>1066</v>
@@ -11442,60 +11463,60 @@
         <v>1067</v>
       </c>
       <c r="B688" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="689" spans="1:2">
       <c r="A689" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B689" t="s">
         <v>1069</v>
-      </c>
-      <c r="B689" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B690" t="s">
         <v>1071</v>
-      </c>
-      <c r="B690" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B691" t="s">
         <v>1073</v>
-      </c>
-      <c r="B691" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B692" t="s">
         <v>1075</v>
-      </c>
-      <c r="B692" t="s">
-        <v>1076</v>
       </c>
     </row>
     <row r="693" spans="1:2">
       <c r="A693" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B693" t="s">
         <v>1077</v>
-      </c>
-      <c r="B693" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="694" spans="1:2">
       <c r="A694" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B694" t="s">
         <v>1079</v>
-      </c>
-      <c r="B694" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="695" spans="1:2">
       <c r="A695" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B695" t="s">
         <v>1081</v>
@@ -11522,12 +11543,12 @@
         <v>1086</v>
       </c>
       <c r="B698" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="699" spans="1:2">
       <c r="A699" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B699" t="s">
         <v>1088</v>
@@ -11546,12 +11567,12 @@
         <v>1091</v>
       </c>
       <c r="B701" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="702" spans="1:2">
       <c r="A702" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B702" t="s">
         <v>1093</v>
@@ -11562,140 +11583,140 @@
         <v>1094</v>
       </c>
       <c r="B703" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B704" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="705" spans="1:2">
       <c r="A705" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="B705" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="706" spans="1:2">
       <c r="A706" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B706" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="707" spans="1:2">
       <c r="A707" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="B707" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="708" spans="1:2">
       <c r="A708" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="B708" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="B709" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="B710" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="B711" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="B712" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="B713" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B714" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="B715" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B716" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B717" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="B718" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B719" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B720" t="s">
         <v>1117</v>
@@ -11706,68 +11727,68 @@
         <v>1118</v>
       </c>
       <c r="B721" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="722" spans="1:2">
       <c r="A722" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B722" t="s">
         <v>1120</v>
-      </c>
-      <c r="B722" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="723" spans="1:2">
       <c r="A723" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B723" t="s">
         <v>1122</v>
-      </c>
-      <c r="B723" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="724" spans="1:2">
       <c r="A724" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B724" t="s">
         <v>1124</v>
-      </c>
-      <c r="B724" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B725" t="s">
         <v>1126</v>
-      </c>
-      <c r="B725" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B726" t="s">
         <v>1128</v>
-      </c>
-      <c r="B726" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="727" spans="1:2">
       <c r="A727" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B727" t="s">
         <v>1130</v>
-      </c>
-      <c r="B727" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="728" spans="1:2">
       <c r="A728" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B728" t="s">
         <v>1132</v>
-      </c>
-      <c r="B728" t="s">
-        <v>1133</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B729" t="s">
         <v>1134</v>
@@ -11794,12 +11815,12 @@
         <v>1139</v>
       </c>
       <c r="B732" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B733" t="s">
         <v>1141</v>
@@ -11818,140 +11839,140 @@
         <v>1144</v>
       </c>
       <c r="B735" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="736" spans="1:2">
       <c r="A736" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B736" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="737" spans="1:2">
       <c r="A737" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B737" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="738" spans="1:2">
       <c r="A738" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="B738" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="B739" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="740" spans="1:2">
       <c r="A740" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="B740" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="741" spans="1:2">
       <c r="A741" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="B741" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="742" spans="1:2">
       <c r="A742" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="B742" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="B743" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="744" spans="1:2">
       <c r="A744" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="B744" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="745" spans="1:2">
       <c r="A745" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B745" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="746" spans="1:2">
       <c r="A746" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B746" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B747" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B748" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="B749" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="B750" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="B751" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="752" spans="1:2">
       <c r="A752" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B752" t="s">
         <v>1167</v>
@@ -11962,36 +11983,36 @@
         <v>1168</v>
       </c>
       <c r="B753" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="754" spans="1:2">
       <c r="A754" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B754" t="s">
         <v>1170</v>
-      </c>
-      <c r="B754" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B755" t="s">
         <v>1172</v>
-      </c>
-      <c r="B755" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B756" t="s">
         <v>1174</v>
-      </c>
-      <c r="B756" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B757" t="s">
         <v>1176</v>
@@ -12042,36 +12063,36 @@
         <v>1186</v>
       </c>
       <c r="B763" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B764" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="765" spans="1:2">
       <c r="A765" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="B765" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="766" spans="1:2">
       <c r="A766" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B766" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="767" spans="1:2">
       <c r="A767" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B767" t="s">
         <v>1193</v>
@@ -12082,15 +12103,15 @@
         <v>1194</v>
       </c>
       <c r="B768" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="769" spans="1:2">
       <c r="A769" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B769" t="s">
         <v>1196</v>
-      </c>
-      <c r="B769" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="770" spans="1:2">
@@ -12098,31 +12119,31 @@
         <v>1197</v>
       </c>
       <c r="B770" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B771" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B772" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="773" spans="1:2">
       <c r="A773" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B773" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="774" spans="1:2">
@@ -12138,60 +12159,60 @@
         <v>1205</v>
       </c>
       <c r="B775" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="776" spans="1:2">
       <c r="A776" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B776" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="777" spans="1:2">
       <c r="A777" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="B777" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="778" spans="1:2">
       <c r="A778" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="B778" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="779" spans="1:2">
       <c r="A779" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="B779" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="780" spans="1:2">
       <c r="A780" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="B780" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="781" spans="1:2">
       <c r="A781" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B781" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="782" spans="1:2">
       <c r="A782" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B782" t="s">
         <v>1216</v>
@@ -12202,12 +12223,12 @@
         <v>1217</v>
       </c>
       <c r="B783" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="B784" t="s">
         <v>1219</v>
@@ -12218,44 +12239,44 @@
         <v>1220</v>
       </c>
       <c r="B785" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B786" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="787" spans="1:2">
       <c r="A787" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="B787" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="788" spans="1:2">
       <c r="A788" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="B788" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="789" spans="1:2">
       <c r="A789" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B789" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="790" spans="1:2">
       <c r="A790" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B790" t="s">
         <v>1228</v>
@@ -12266,84 +12287,84 @@
         <v>1229</v>
       </c>
       <c r="B791" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B792" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="B793" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="B794" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="B795" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="B796" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="B797" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="B798" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="B799" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="B800" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B801" t="s">
         <v>1242</v>
@@ -12362,44 +12383,44 @@
         <v>1245</v>
       </c>
       <c r="B803" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B804" t="s">
         <v>1247</v>
-      </c>
-      <c r="B804" t="s">
-        <v>1248</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B805" t="s">
         <v>1249</v>
-      </c>
-      <c r="B805" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B806" t="s">
         <v>1251</v>
-      </c>
-      <c r="B806" t="s">
-        <v>1252</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B807" t="s">
         <v>1253</v>
-      </c>
-      <c r="B807" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B808" t="s">
         <v>1255</v>
@@ -12410,44 +12431,44 @@
         <v>1256</v>
       </c>
       <c r="B809" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B810" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="B811" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="812" spans="1:2">
       <c r="A812" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="B812" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="813" spans="1:2">
       <c r="A813" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="B813" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="814" spans="1:2">
       <c r="A814" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B814" t="s">
         <v>1264</v>
@@ -12458,12 +12479,12 @@
         <v>1265</v>
       </c>
       <c r="B815" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="B816" t="s">
         <v>1267</v>
@@ -12498,12 +12519,12 @@
         <v>1274</v>
       </c>
       <c r="B820" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B821" t="s">
         <v>1276</v>
@@ -12522,132 +12543,132 @@
         <v>1279</v>
       </c>
       <c r="B823" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="824" spans="1:2">
       <c r="A824" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B824" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B825" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="826" spans="1:2">
       <c r="A826" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B826" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="B827" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="828" spans="1:2">
       <c r="A828" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B828" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B829" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B830" t="s">
-        <v>716</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="B831" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="832" spans="1:2">
       <c r="A832" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B832" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B833" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B834" t="s">
-        <v>1295</v>
+        <v>716</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B835" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="B836" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="B837" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="B838" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B839" t="s">
         <v>1303</v>
@@ -12658,12 +12679,12 @@
         <v>1304</v>
       </c>
       <c r="B840" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="B841" t="s">
         <v>1306</v>
@@ -12690,52 +12711,52 @@
         <v>1311</v>
       </c>
       <c r="B844" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B845" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B846" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="B847" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="B848" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="B849" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B850" t="s">
         <v>1320</v>
@@ -12746,84 +12767,84 @@
         <v>1321</v>
       </c>
       <c r="B851" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B852" t="s">
         <v>1323</v>
-      </c>
-      <c r="B852" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B853" t="s">
         <v>1325</v>
-      </c>
-      <c r="B853" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B854" t="s">
         <v>1327</v>
-      </c>
-      <c r="B854" t="s">
-        <v>1328</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B855" t="s">
         <v>1329</v>
-      </c>
-      <c r="B855" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B856" t="s">
         <v>1331</v>
-      </c>
-      <c r="B856" t="s">
-        <v>1332</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B857" t="s">
         <v>1333</v>
-      </c>
-      <c r="B857" t="s">
-        <v>1334</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B858" t="s">
         <v>1335</v>
-      </c>
-      <c r="B858" t="s">
-        <v>1336</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B859" t="s">
         <v>1337</v>
-      </c>
-      <c r="B859" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="860" spans="1:2">
       <c r="A860" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B860" t="s">
         <v>1339</v>
-      </c>
-      <c r="B860" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B861" t="s">
         <v>1341</v>
@@ -12834,116 +12855,116 @@
         <v>1342</v>
       </c>
       <c r="B862" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B863" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="B864" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="B865" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="866" spans="1:2">
       <c r="A866" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="B866" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="B867" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="B868" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="B869" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="B870" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="B871" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="B872" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="B873" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="B874" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B875" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B876" t="s">
         <v>1361</v>
@@ -12970,7 +12991,7 @@
         <v>1366</v>
       </c>
       <c r="B879" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="880" spans="1:2">
@@ -12986,20 +13007,20 @@
         <v>1369</v>
       </c>
       <c r="B881" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B882" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="B883" t="s">
         <v>1372</v>
@@ -13007,15 +13028,15 @@
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B884" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="B885" t="s">
         <v>1376</v>
@@ -13050,12 +13071,12 @@
         <v>1382</v>
       </c>
       <c r="B889" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="B890" t="s">
         <v>1384</v>
@@ -13066,68 +13087,68 @@
         <v>1385</v>
       </c>
       <c r="B891" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="B892" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="B893" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="B894" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="B895" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="B896" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B897" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B898" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B899" t="s">
         <v>1397</v>
@@ -13146,28 +13167,28 @@
         <v>1399</v>
       </c>
       <c r="B901" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="B902" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B903" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B904" t="s">
         <v>1405</v>
@@ -13178,20 +13199,20 @@
         <v>1406</v>
       </c>
       <c r="B905" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B906" t="s">
         <v>1408</v>
-      </c>
-      <c r="B906" t="s">
-        <v>1409</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="B907" t="s">
         <v>1410</v>
@@ -13202,68 +13223,68 @@
         <v>1411</v>
       </c>
       <c r="B908" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B909" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="B910" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
       <c r="B911" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
       <c r="B912" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="B913" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1417</v>
+        <v>1420</v>
       </c>
       <c r="B914" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="B915" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B916" t="s">
         <v>1422</v>
@@ -13274,12 +13295,12 @@
         <v>1423</v>
       </c>
       <c r="B917" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="B918" t="s">
         <v>1425</v>
@@ -13290,28 +13311,28 @@
         <v>1426</v>
       </c>
       <c r="B919" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B920" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B921" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B922" t="s">
         <v>1432</v>
@@ -13322,20 +13343,20 @@
         <v>1433</v>
       </c>
       <c r="B923" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B924" t="s">
         <v>1435</v>
-      </c>
-      <c r="B924" t="s">
-        <v>1436</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B925" t="s">
         <v>1437</v>
@@ -13346,28 +13367,28 @@
         <v>1438</v>
       </c>
       <c r="B926" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B927" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B928" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B929" t="s">
         <v>1444</v>
@@ -13378,12 +13399,12 @@
         <v>1445</v>
       </c>
       <c r="B930" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B931" t="s">
         <v>1447</v>
@@ -13410,44 +13431,44 @@
         <v>1452</v>
       </c>
       <c r="B934" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="B935" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="B936" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B937" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="B938" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B939" t="s">
         <v>1460</v>
@@ -13490,108 +13511,108 @@
         <v>1468</v>
       </c>
       <c r="B944" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B945" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B946" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="B947" t="s">
-        <v>1471</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
-        <v>1472</v>
+        <v>1475</v>
       </c>
       <c r="B948" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="B949" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="B950" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="B951" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="B952" t="s">
-        <v>1477</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1478</v>
+        <v>1481</v>
       </c>
       <c r="B953" t="s">
-        <v>1478</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="B954" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1480</v>
+        <v>1483</v>
       </c>
       <c r="B955" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="B956" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B957" t="s">
         <v>1485</v>
@@ -13602,12 +13623,12 @@
         <v>1486</v>
       </c>
       <c r="B958" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="B959" t="s">
         <v>1488</v>
@@ -13618,28 +13639,28 @@
         <v>1489</v>
       </c>
       <c r="B960" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B961" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B962" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B963" t="s">
         <v>1495</v>
@@ -13650,28 +13671,28 @@
         <v>1496</v>
       </c>
       <c r="B964" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B965" t="s">
         <v>1498</v>
-      </c>
-      <c r="B965" t="s">
-        <v>1499</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B966" t="s">
         <v>1500</v>
-      </c>
-      <c r="B966" t="s">
-        <v>1501</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="B967" t="s">
         <v>1502</v>
@@ -13682,52 +13703,52 @@
         <v>1503</v>
       </c>
       <c r="B968" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B969" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="B970" t="s">
-        <v>1505</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B971" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="B972" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="B973" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B974" t="s">
         <v>1512</v>
@@ -13754,44 +13775,44 @@
         <v>1517</v>
       </c>
       <c r="B977" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B978" t="s">
         <v>1519</v>
-      </c>
-      <c r="B978" t="s">
-        <v>1520</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B979" t="s">
         <v>1521</v>
-      </c>
-      <c r="B979" t="s">
-        <v>1522</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B980" t="s">
         <v>1523</v>
-      </c>
-      <c r="B980" t="s">
-        <v>1524</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B981" t="s">
         <v>1525</v>
-      </c>
-      <c r="B981" t="s">
-        <v>1526</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B982" t="s">
         <v>1527</v>
@@ -13802,68 +13823,68 @@
         <v>1528</v>
       </c>
       <c r="B983" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B984" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B985" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="B986" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="B987" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B988" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="B989" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="B990" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B991" t="s">
         <v>1541</v>
@@ -13874,20 +13895,20 @@
         <v>1542</v>
       </c>
       <c r="B992" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B993" t="s">
         <v>1544</v>
-      </c>
-      <c r="B993" t="s">
-        <v>1545</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="B994" t="s">
         <v>1546</v>
@@ -13906,20 +13927,20 @@
         <v>1549</v>
       </c>
       <c r="B996" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B997" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B998" t="s">
         <v>1553</v>
@@ -13930,52 +13951,52 @@
         <v>1554</v>
       </c>
       <c r="B999" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B1000" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B1001" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="B1002" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="B1003" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="B1004" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B1005" t="s">
         <v>1563</v>
@@ -13986,148 +14007,148 @@
         <v>1564</v>
       </c>
       <c r="B1006" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B1007" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B1008" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="B1009" t="s">
-        <v>1567</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1568</v>
+        <v>1571</v>
       </c>
       <c r="B1010" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="B1011" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="B1012" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="B1013" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="B1014" t="s">
-        <v>1573</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1574</v>
+        <v>1577</v>
       </c>
       <c r="B1015" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="B1016" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B1017" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="B1018" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B1019" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="B1020" t="s">
-        <v>1581</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1582</v>
+        <v>1585</v>
       </c>
       <c r="B1021" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="B1022" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B1023" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B1024" t="s">
         <v>1588</v>
@@ -14170,100 +14191,100 @@
         <v>1596</v>
       </c>
       <c r="B1029" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B1030" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="B1031" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B1032" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="B1033" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="B1034" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="B1035" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1604</v>
+        <v>1607</v>
       </c>
       <c r="B1036" t="s">
-        <v>1604</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1605</v>
+        <v>1608</v>
       </c>
       <c r="B1037" t="s">
-        <v>1605</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1606</v>
+        <v>1609</v>
       </c>
       <c r="B1038" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="B1039" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B1040" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B1041" t="s">
         <v>1612</v>
@@ -14298,28 +14319,28 @@
         <v>1618</v>
       </c>
       <c r="B1045" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B1046" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B1047" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B1048" t="s">
         <v>1624</v>
@@ -14338,52 +14359,52 @@
         <v>1626</v>
       </c>
       <c r="B1050" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B1051" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B1052" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="B1053" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="B1054" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B1055" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B1056" t="s">
         <v>1636</v>
@@ -14394,156 +14415,156 @@
         <v>1637</v>
       </c>
       <c r="B1057" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B1058" t="s">
         <v>1639</v>
-      </c>
-      <c r="B1058" t="s">
-        <v>1640</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B1059" t="s">
         <v>1641</v>
-      </c>
-      <c r="B1059" t="s">
-        <v>1642</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B1060" t="s">
         <v>1643</v>
-      </c>
-      <c r="B1060" t="s">
-        <v>1644</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B1061" t="s">
         <v>1645</v>
-      </c>
-      <c r="B1061" t="s">
-        <v>1646</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B1062" t="s">
         <v>1647</v>
-      </c>
-      <c r="B1062" t="s">
-        <v>1648</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B1063" t="s">
         <v>1649</v>
-      </c>
-      <c r="B1063" t="s">
-        <v>1650</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B1064" t="s">
         <v>1651</v>
-      </c>
-      <c r="B1064" t="s">
-        <v>1652</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B1065" t="s">
         <v>1653</v>
-      </c>
-      <c r="B1065" t="s">
-        <v>1654</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B1066" t="s">
         <v>1655</v>
-      </c>
-      <c r="B1066" t="s">
-        <v>1656</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B1067" t="s">
         <v>1657</v>
-      </c>
-      <c r="B1067" t="s">
-        <v>1658</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B1068" t="s">
         <v>1659</v>
-      </c>
-      <c r="B1068" t="s">
-        <v>1660</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B1069" t="s">
         <v>1661</v>
-      </c>
-      <c r="B1069" t="s">
-        <v>1662</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B1070" t="s">
         <v>1663</v>
-      </c>
-      <c r="B1070" t="s">
-        <v>1664</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B1071" t="s">
         <v>1665</v>
-      </c>
-      <c r="B1071" t="s">
-        <v>1666</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B1072" t="s">
         <v>1667</v>
-      </c>
-      <c r="B1072" t="s">
-        <v>1668</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B1073" t="s">
         <v>1669</v>
-      </c>
-      <c r="B1073" t="s">
-        <v>1670</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B1074" t="s">
         <v>1671</v>
-      </c>
-      <c r="B1074" t="s">
-        <v>1672</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B1075" t="s">
         <v>1673</v>
-      </c>
-      <c r="B1075" t="s">
-        <v>1674</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="B1076" t="s">
         <v>1675</v>
@@ -14562,124 +14583,124 @@
         <v>1678</v>
       </c>
       <c r="B1078" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B1079" t="s">
-        <v>1679</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1680</v>
+        <v>1682</v>
       </c>
       <c r="B1080" t="s">
-        <v>1680</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1681</v>
+        <v>1683</v>
       </c>
       <c r="B1081" t="s">
-        <v>1681</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1682</v>
+        <v>1685</v>
       </c>
       <c r="B1082" t="s">
-        <v>1683</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="B1083" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="B1084" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B1085" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B1086" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="B1087" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="B1088" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="B1089" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="B1090" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1694</v>
+        <v>1696</v>
       </c>
       <c r="B1091" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B1092" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B1093" t="s">
         <v>1699</v>
@@ -14690,12 +14711,12 @@
         <v>1700</v>
       </c>
       <c r="B1094" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="B1095" t="s">
         <v>1702</v>
@@ -14706,28 +14727,28 @@
         <v>1703</v>
       </c>
       <c r="B1096" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B1097" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B1098" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B1099" t="s">
         <v>1709</v>
@@ -14738,20 +14759,20 @@
         <v>1710</v>
       </c>
       <c r="B1100" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B1101" t="s">
         <v>1712</v>
-      </c>
-      <c r="B1101" t="s">
-        <v>1713</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="B1102" t="s">
         <v>1714</v>
@@ -14802,44 +14823,44 @@
         <v>1724</v>
       </c>
       <c r="B1108" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B1109" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="B1110" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="B1111" t="s">
-        <v>1728</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="B1112" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="B1113" t="s">
         <v>1732</v>
@@ -14866,28 +14887,28 @@
         <v>1736</v>
       </c>
       <c r="B1116" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="B1117" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="B1118" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="B1119" t="s">
         <v>1742</v>
@@ -14898,132 +14919,132 @@
         <v>1743</v>
       </c>
       <c r="B1120" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
+        <v>1744</v>
+      </c>
+      <c r="B1121" t="s">
         <v>1745</v>
-      </c>
-      <c r="B1121" t="s">
-        <v>1746</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B1122" t="s">
         <v>1747</v>
-      </c>
-      <c r="B1122" t="s">
-        <v>1748</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B1123" t="s">
         <v>1749</v>
-      </c>
-      <c r="B1123" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B1124" t="s">
         <v>1751</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>1752</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B1125" t="s">
         <v>1753</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>1754</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B1126" t="s">
         <v>1755</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>1756</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B1127" t="s">
         <v>1757</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>1758</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B1128" t="s">
         <v>1759</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>1760</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B1129" t="s">
         <v>1761</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>1762</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B1130" t="s">
         <v>1763</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>1764</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B1131" t="s">
         <v>1765</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>1766</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>1766</v>
+      </c>
+      <c r="B1132" t="s">
         <v>1767</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>1768</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B1133" t="s">
         <v>1769</v>
-      </c>
-      <c r="B1133" t="s">
-        <v>1770</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B1134" t="s">
         <v>1771</v>
-      </c>
-      <c r="B1134" t="s">
-        <v>1772</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B1135" t="s">
         <v>1773</v>
-      </c>
-      <c r="B1135" t="s">
-        <v>1774</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="B1136" t="s">
         <v>1775</v>
@@ -15034,108 +15055,108 @@
         <v>1776</v>
       </c>
       <c r="B1137" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="B1138" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
-        <v>1778</v>
+        <v>1780</v>
       </c>
       <c r="B1139" t="s">
-        <v>1778</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
-        <v>1779</v>
+        <v>1782</v>
       </c>
       <c r="B1140" t="s">
-        <v>1779</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>1780</v>
+        <v>1783</v>
       </c>
       <c r="B1141" t="s">
-        <v>1781</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="B1142" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="B1143" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="B1144" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B1145" t="s">
-        <v>1786</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>1787</v>
+        <v>1789</v>
       </c>
       <c r="B1146" t="s">
-        <v>1787</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1788</v>
+        <v>1791</v>
       </c>
       <c r="B1147" t="s">
-        <v>1789</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="B1148" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1791</v>
+        <v>1793</v>
       </c>
       <c r="B1149" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="B1150" t="s">
         <v>1794</v>
@@ -15170,36 +15191,36 @@
         <v>1800</v>
       </c>
       <c r="B1154" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="B1155" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="B1156" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="B1157" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="B1158" t="s">
         <v>1807</v>
@@ -15218,12 +15239,12 @@
         <v>1810</v>
       </c>
       <c r="B1160" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="B1161" t="s">
         <v>1812</v>
@@ -15234,132 +15255,132 @@
         <v>1813</v>
       </c>
       <c r="B1162" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="B1163" t="s">
-        <v>1814</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>1815</v>
+        <v>1817</v>
       </c>
       <c r="B1164" t="s">
-        <v>1815</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>1816</v>
+        <v>1819</v>
       </c>
       <c r="B1165" t="s">
-        <v>1816</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1817</v>
+        <v>1820</v>
       </c>
       <c r="B1166" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="B1167" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="B1168" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="B1169" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="B1170" t="s">
-        <v>1823</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="B1171" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="B1172" t="s">
-        <v>1825</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
       <c r="B1173" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="B1174" t="s">
-        <v>1827</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1828</v>
+        <v>1831</v>
       </c>
       <c r="B1175" t="s">
-        <v>1829</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1830</v>
+        <v>1832</v>
       </c>
       <c r="B1176" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="B1177" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="B1178" t="s">
         <v>1834</v>
@@ -15370,36 +15391,36 @@
         <v>1835</v>
       </c>
       <c r="B1179" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B1180" t="s">
-        <v>1836</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
       <c r="B1181" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="B1182" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="B1183" t="s">
         <v>1842</v>
@@ -15418,75 +15439,107 @@
         <v>1844</v>
       </c>
       <c r="B1185" t="s">
-        <v>718</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="B1186" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
       <c r="B1187" t="s">
-        <v>1846</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1847</v>
+        <v>1850</v>
       </c>
       <c r="B1188" t="s">
-        <v>1848</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="B1189" t="s">
-        <v>1849</v>
+        <v>718</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>1850</v>
+        <v>1852</v>
       </c>
       <c r="B1190" t="s">
-        <v>1850</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>1851</v>
+        <v>1853</v>
       </c>
       <c r="B1191" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B1192" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="B1193" t="s">
         <v>1856</v>
       </c>
     </row>
+    <row r="1194" spans="1:2">
+      <c r="A1194" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B1194" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:2">
+      <c r="A1195" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B1195" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:2">
+      <c r="A1196" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B1196" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:2">
+      <c r="A1197" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B1197" t="s">
+        <v>1863</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1193"/>
+  <autoFilter ref="A1:B1197"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/es/headTags.xlsx
+++ b/lang/es/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1198</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1864">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1866">
   <si>
     <t>en</t>
   </si>
@@ -4130,6 +4130,12 @@
   </si>
   <si>
     <t>Profesor Layton</t>
+  </si>
+  <si>
+    <t>Project Zomboid</t>
+  </si>
+  <si>
+    <t>Proyecto Zomboid</t>
   </si>
   <si>
     <t>Pumpkin</t>
@@ -5955,7 +5961,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1197"/>
+  <dimension ref="A1:B1198"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13023,15 +13029,15 @@
         <v>1373</v>
       </c>
       <c r="B883" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B884" t="s">
         <v>1374</v>
-      </c>
-      <c r="B884" t="s">
-        <v>1375</v>
       </c>
     </row>
     <row r="885" spans="1:2">
@@ -13039,20 +13045,20 @@
         <v>1376</v>
       </c>
       <c r="B885" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B886" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B887" t="s">
         <v>1379</v>
@@ -13079,12 +13085,12 @@
         <v>1384</v>
       </c>
       <c r="B890" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="B891" t="s">
         <v>1386</v>
@@ -13103,12 +13109,12 @@
         <v>1389</v>
       </c>
       <c r="B893" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="B894" t="s">
         <v>1391</v>
@@ -13119,28 +13125,28 @@
         <v>1392</v>
       </c>
       <c r="B895" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="B896" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B897" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="B898" t="s">
         <v>1396</v>
@@ -13151,20 +13157,20 @@
         <v>1397</v>
       </c>
       <c r="B899" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="B900" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="B901" t="s">
         <v>1400</v>
@@ -13191,20 +13197,20 @@
         <v>1405</v>
       </c>
       <c r="B904" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B905" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="B906" t="s">
         <v>1408</v>
@@ -13247,60 +13253,60 @@
         <v>1417</v>
       </c>
       <c r="B911" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B912" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B913" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B914" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B915" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B916" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B917" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B918" t="s">
         <v>1425</v>
@@ -13335,20 +13341,20 @@
         <v>1432</v>
       </c>
       <c r="B922" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B923" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B924" t="s">
         <v>1435</v>
@@ -13391,20 +13397,20 @@
         <v>1444</v>
       </c>
       <c r="B929" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="B930" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B931" t="s">
         <v>1447</v>
@@ -13439,12 +13445,12 @@
         <v>1454</v>
       </c>
       <c r="B935" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B936" t="s">
         <v>1456</v>
@@ -13463,20 +13469,20 @@
         <v>1459</v>
       </c>
       <c r="B938" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B939" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B940" t="s">
         <v>1462</v>
@@ -13487,12 +13493,12 @@
         <v>1463</v>
       </c>
       <c r="B941" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="B942" t="s">
         <v>1465</v>
@@ -13519,12 +13525,12 @@
         <v>1470</v>
       </c>
       <c r="B945" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B946" t="s">
         <v>1472</v>
@@ -13543,36 +13549,36 @@
         <v>1475</v>
       </c>
       <c r="B948" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B949" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B950" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B951" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="B952" t="s">
         <v>1480</v>
@@ -13583,52 +13589,52 @@
         <v>1481</v>
       </c>
       <c r="B953" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B954" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B955" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B956" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B957" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B958" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B959" t="s">
         <v>1488</v>
@@ -13663,20 +13669,20 @@
         <v>1495</v>
       </c>
       <c r="B963" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B964" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B965" t="s">
         <v>1498</v>
@@ -13727,36 +13733,36 @@
         <v>1509</v>
       </c>
       <c r="B971" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="B972" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B973" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="B974" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B975" t="s">
         <v>1514</v>
@@ -13775,12 +13781,12 @@
         <v>1517</v>
       </c>
       <c r="B977" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="B978" t="s">
         <v>1519</v>
@@ -13847,20 +13853,20 @@
         <v>1534</v>
       </c>
       <c r="B986" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B987" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="B988" t="s">
         <v>1537</v>
@@ -13879,28 +13885,28 @@
         <v>1540</v>
       </c>
       <c r="B990" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B991" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B992" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B993" t="s">
         <v>1544</v>
@@ -13943,12 +13949,12 @@
         <v>1553</v>
       </c>
       <c r="B998" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B999" t="s">
         <v>1555</v>
@@ -13959,12 +13965,12 @@
         <v>1556</v>
       </c>
       <c r="B1000" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B1001" t="s">
         <v>1558</v>
@@ -13983,28 +13989,28 @@
         <v>1561</v>
       </c>
       <c r="B1003" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B1004" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B1005" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B1006" t="s">
         <v>1565</v>
@@ -14015,12 +14021,12 @@
         <v>1566</v>
       </c>
       <c r="B1007" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B1008" t="s">
         <v>1568</v>
@@ -14039,36 +14045,36 @@
         <v>1571</v>
       </c>
       <c r="B1010" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B1011" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B1012" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B1013" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B1014" t="s">
         <v>1576</v>
@@ -14079,36 +14085,36 @@
         <v>1577</v>
       </c>
       <c r="B1015" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B1016" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="B1017" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B1018" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B1019" t="s">
         <v>1582</v>
@@ -14127,36 +14133,36 @@
         <v>1585</v>
       </c>
       <c r="B1021" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B1022" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B1023" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B1024" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B1025" t="s">
         <v>1590</v>
@@ -14175,12 +14181,12 @@
         <v>1593</v>
       </c>
       <c r="B1027" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B1028" t="s">
         <v>1595</v>
@@ -14207,12 +14213,12 @@
         <v>1600</v>
       </c>
       <c r="B1031" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B1032" t="s">
         <v>1602</v>
@@ -14223,20 +14229,20 @@
         <v>1603</v>
       </c>
       <c r="B1033" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B1034" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="B1035" t="s">
         <v>1606</v>
@@ -14247,52 +14253,52 @@
         <v>1607</v>
       </c>
       <c r="B1036" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B1037" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B1038" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B1039" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B1040" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B1041" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B1042" t="s">
         <v>1614</v>
@@ -14311,12 +14317,12 @@
         <v>1617</v>
       </c>
       <c r="B1044" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B1045" t="s">
         <v>1619</v>
@@ -14343,20 +14349,20 @@
         <v>1624</v>
       </c>
       <c r="B1048" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B1049" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="B1050" t="s">
         <v>1627</v>
@@ -14383,20 +14389,20 @@
         <v>1632</v>
       </c>
       <c r="B1053" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B1054" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B1055" t="s">
         <v>1635</v>
@@ -14407,20 +14413,20 @@
         <v>1636</v>
       </c>
       <c r="B1056" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B1057" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="B1058" t="s">
         <v>1639</v>
@@ -14599,12 +14605,12 @@
         <v>1682</v>
       </c>
       <c r="B1080" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="B1081" t="s">
         <v>1684</v>
@@ -14615,36 +14621,36 @@
         <v>1685</v>
       </c>
       <c r="B1082" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B1083" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B1084" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B1085" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B1086" t="s">
         <v>1690</v>
@@ -14655,12 +14661,12 @@
         <v>1691</v>
       </c>
       <c r="B1087" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B1088" t="s">
         <v>1693</v>
@@ -14671,28 +14677,28 @@
         <v>1694</v>
       </c>
       <c r="B1089" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B1090" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B1091" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B1092" t="s">
         <v>1698</v>
@@ -14703,20 +14709,20 @@
         <v>1699</v>
       </c>
       <c r="B1093" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B1094" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B1095" t="s">
         <v>1702</v>
@@ -14751,20 +14757,20 @@
         <v>1709</v>
       </c>
       <c r="B1099" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B1100" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B1101" t="s">
         <v>1712</v>
@@ -14807,12 +14813,12 @@
         <v>1721</v>
       </c>
       <c r="B1106" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="B1107" t="s">
         <v>1723</v>
@@ -14839,12 +14845,12 @@
         <v>1728</v>
       </c>
       <c r="B1110" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="B1111" t="s">
         <v>1730</v>
@@ -14855,20 +14861,20 @@
         <v>1731</v>
       </c>
       <c r="B1112" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="B1113" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B1114" t="s">
         <v>1734</v>
@@ -14879,12 +14885,12 @@
         <v>1735</v>
       </c>
       <c r="B1115" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="B1116" t="s">
         <v>1737</v>
@@ -14911,20 +14917,20 @@
         <v>1742</v>
       </c>
       <c r="B1119" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="B1120" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="B1121" t="s">
         <v>1745</v>
@@ -15079,44 +15085,44 @@
         <v>1782</v>
       </c>
       <c r="B1140" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="B1141" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="B1142" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="B1143" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B1144" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="B1145" t="s">
         <v>1788</v>
@@ -15135,36 +15141,36 @@
         <v>1791</v>
       </c>
       <c r="B1147" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B1148" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="B1149" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B1150" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="B1151" t="s">
         <v>1796</v>
@@ -15175,12 +15181,12 @@
         <v>1797</v>
       </c>
       <c r="B1152" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="B1153" t="s">
         <v>1799</v>
@@ -15207,12 +15213,12 @@
         <v>1804</v>
       </c>
       <c r="B1156" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="B1157" t="s">
         <v>1806</v>
@@ -15223,12 +15229,12 @@
         <v>1807</v>
       </c>
       <c r="B1158" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1159" t="s">
         <v>1809</v>
@@ -15239,12 +15245,12 @@
         <v>1810</v>
       </c>
       <c r="B1160" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B1161" t="s">
         <v>1812</v>
@@ -15279,44 +15285,44 @@
         <v>1819</v>
       </c>
       <c r="B1165" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="B1166" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="B1167" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="B1168" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="B1169" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1170" t="s">
         <v>1825</v>
@@ -15327,28 +15333,28 @@
         <v>1826</v>
       </c>
       <c r="B1171" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="B1172" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B1173" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B1174" t="s">
         <v>1830</v>
@@ -15359,36 +15365,36 @@
         <v>1831</v>
       </c>
       <c r="B1175" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="B1176" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="B1177" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B1178" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1179" t="s">
         <v>1836</v>
@@ -15407,12 +15413,12 @@
         <v>1839</v>
       </c>
       <c r="B1181" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="B1182" t="s">
         <v>1841</v>
@@ -15423,20 +15429,20 @@
         <v>1842</v>
       </c>
       <c r="B1183" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="B1184" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="B1185" t="s">
         <v>1845</v>
@@ -15463,36 +15469,36 @@
         <v>1850</v>
       </c>
       <c r="B1188" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="B1189" t="s">
-        <v>718</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="B1190" t="s">
-        <v>1852</v>
+        <v>718</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B1191" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B1192" t="s">
         <v>1855</v>
@@ -15503,20 +15509,20 @@
         <v>1856</v>
       </c>
       <c r="B1193" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="B1194" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
       <c r="A1195" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B1195" t="s">
         <v>1859</v>
@@ -15538,8 +15544,16 @@
         <v>1863</v>
       </c>
     </row>
+    <row r="1198" spans="1:2">
+      <c r="A1198" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B1198" t="s">
+        <v>1865</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1197"/>
+  <autoFilter ref="A1:B1198"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/es/headTags.xlsx
+++ b/lang/es/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1199</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1866">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1867">
   <si>
     <t>en</t>
   </si>
@@ -332,6 +332,9 @@
   </si>
   <si>
     <t>Baka y Test</t>
+  </si>
+  <si>
+    <t>Bakugan</t>
   </si>
   <si>
     <t>Baldi's Basics</t>
@@ -5961,7 +5964,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1198"/>
+  <dimension ref="A1:B1199"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -6517,20 +6520,20 @@
         <v>105</v>
       </c>
       <c r="B69" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
+        <v>106</v>
+      </c>
+      <c r="B70" t="s">
         <v>107</v>
-      </c>
-      <c r="B70" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B71" t="s">
         <v>109</v>
@@ -6549,12 +6552,12 @@
         <v>111</v>
       </c>
       <c r="B73" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B74" t="s">
         <v>113</v>
@@ -6565,36 +6568,36 @@
         <v>114</v>
       </c>
       <c r="B75" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
+        <v>115</v>
+      </c>
+      <c r="B76" t="s">
         <v>116</v>
-      </c>
-      <c r="B76" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
+        <v>117</v>
+      </c>
+      <c r="B77" t="s">
         <v>118</v>
-      </c>
-      <c r="B77" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
+        <v>119</v>
+      </c>
+      <c r="B78" t="s">
         <v>120</v>
-      </c>
-      <c r="B78" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B79" t="s">
         <v>122</v>
@@ -6605,12 +6608,12 @@
         <v>123</v>
       </c>
       <c r="B80" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B81" t="s">
         <v>125</v>
@@ -6621,28 +6624,28 @@
         <v>126</v>
       </c>
       <c r="B82" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
+        <v>127</v>
+      </c>
+      <c r="B83" t="s">
         <v>128</v>
-      </c>
-      <c r="B83" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
+        <v>129</v>
+      </c>
+      <c r="B84" t="s">
         <v>130</v>
-      </c>
-      <c r="B84" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B85" t="s">
         <v>132</v>
@@ -6653,36 +6656,36 @@
         <v>133</v>
       </c>
       <c r="B86" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
+        <v>134</v>
+      </c>
+      <c r="B87" t="s">
         <v>135</v>
-      </c>
-      <c r="B87" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
+        <v>136</v>
+      </c>
+      <c r="B88" t="s">
         <v>137</v>
-      </c>
-      <c r="B88" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
+        <v>138</v>
+      </c>
+      <c r="B89" t="s">
         <v>139</v>
-      </c>
-      <c r="B89" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B90" t="s">
         <v>141</v>
@@ -6701,12 +6704,12 @@
         <v>143</v>
       </c>
       <c r="B92" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B93" t="s">
         <v>145</v>
@@ -6797,12 +6800,12 @@
         <v>156</v>
       </c>
       <c r="B104" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B105" t="s">
         <v>158</v>
@@ -6829,12 +6832,12 @@
         <v>161</v>
       </c>
       <c r="B108" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B109" t="s">
         <v>163</v>
@@ -6869,76 +6872,76 @@
         <v>167</v>
       </c>
       <c r="B113" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
+        <v>168</v>
+      </c>
+      <c r="B114" t="s">
         <v>169</v>
-      </c>
-      <c r="B114" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
+        <v>170</v>
+      </c>
+      <c r="B115" t="s">
         <v>171</v>
-      </c>
-      <c r="B115" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
+        <v>172</v>
+      </c>
+      <c r="B116" t="s">
         <v>173</v>
-      </c>
-      <c r="B116" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
+        <v>174</v>
+      </c>
+      <c r="B117" t="s">
         <v>175</v>
-      </c>
-      <c r="B117" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
+        <v>176</v>
+      </c>
+      <c r="B118" t="s">
         <v>177</v>
-      </c>
-      <c r="B118" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
+        <v>178</v>
+      </c>
+      <c r="B119" t="s">
         <v>179</v>
-      </c>
-      <c r="B119" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
+        <v>180</v>
+      </c>
+      <c r="B120" t="s">
         <v>181</v>
-      </c>
-      <c r="B120" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
+        <v>182</v>
+      </c>
+      <c r="B121" t="s">
         <v>183</v>
-      </c>
-      <c r="B121" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B122" t="s">
         <v>185</v>
@@ -6973,12 +6976,12 @@
         <v>189</v>
       </c>
       <c r="B126" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B127" t="s">
         <v>191</v>
@@ -6989,12 +6992,12 @@
         <v>192</v>
       </c>
       <c r="B128" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B129" t="s">
         <v>194</v>
@@ -7037,20 +7040,20 @@
         <v>199</v>
       </c>
       <c r="B134" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
+        <v>200</v>
+      </c>
+      <c r="B135" t="s">
         <v>201</v>
-      </c>
-      <c r="B135" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B136" t="s">
         <v>203</v>
@@ -7069,20 +7072,20 @@
         <v>205</v>
       </c>
       <c r="B138" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
+        <v>206</v>
+      </c>
+      <c r="B139" t="s">
         <v>207</v>
-      </c>
-      <c r="B139" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B140" t="s">
         <v>209</v>
@@ -7093,60 +7096,60 @@
         <v>210</v>
       </c>
       <c r="B141" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
+        <v>211</v>
+      </c>
+      <c r="B142" t="s">
         <v>212</v>
-      </c>
-      <c r="B142" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
+        <v>213</v>
+      </c>
+      <c r="B143" t="s">
         <v>214</v>
-      </c>
-      <c r="B143" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
+        <v>215</v>
+      </c>
+      <c r="B144" t="s">
         <v>216</v>
-      </c>
-      <c r="B144" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
+        <v>217</v>
+      </c>
+      <c r="B145" t="s">
         <v>218</v>
-      </c>
-      <c r="B145" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
+        <v>219</v>
+      </c>
+      <c r="B146" t="s">
         <v>220</v>
-      </c>
-      <c r="B146" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
+        <v>221</v>
+      </c>
+      <c r="B147" t="s">
         <v>222</v>
-      </c>
-      <c r="B147" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B148" t="s">
         <v>224</v>
@@ -7189,20 +7192,20 @@
         <v>229</v>
       </c>
       <c r="B153" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
+        <v>230</v>
+      </c>
+      <c r="B154" t="s">
         <v>231</v>
-      </c>
-      <c r="B154" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B155" t="s">
         <v>233</v>
@@ -7221,20 +7224,20 @@
         <v>235</v>
       </c>
       <c r="B157" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
+        <v>236</v>
+      </c>
+      <c r="B158" t="s">
         <v>237</v>
-      </c>
-      <c r="B158" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B159" t="s">
         <v>239</v>
@@ -7245,92 +7248,92 @@
         <v>240</v>
       </c>
       <c r="B160" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
+        <v>241</v>
+      </c>
+      <c r="B161" t="s">
         <v>242</v>
-      </c>
-      <c r="B161" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
+        <v>243</v>
+      </c>
+      <c r="B162" t="s">
         <v>244</v>
-      </c>
-      <c r="B162" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
+        <v>245</v>
+      </c>
+      <c r="B163" t="s">
         <v>246</v>
-      </c>
-      <c r="B163" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
+        <v>247</v>
+      </c>
+      <c r="B164" t="s">
         <v>248</v>
-      </c>
-      <c r="B164" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
+        <v>249</v>
+      </c>
+      <c r="B165" t="s">
         <v>250</v>
-      </c>
-      <c r="B165" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
+        <v>251</v>
+      </c>
+      <c r="B166" t="s">
         <v>252</v>
-      </c>
-      <c r="B166" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
+        <v>253</v>
+      </c>
+      <c r="B167" t="s">
         <v>254</v>
-      </c>
-      <c r="B167" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
+        <v>255</v>
+      </c>
+      <c r="B168" t="s">
         <v>256</v>
-      </c>
-      <c r="B168" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
+        <v>257</v>
+      </c>
+      <c r="B169" t="s">
         <v>258</v>
-      </c>
-      <c r="B169" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
+        <v>259</v>
+      </c>
+      <c r="B170" t="s">
         <v>260</v>
-      </c>
-      <c r="B170" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B171" t="s">
         <v>262</v>
@@ -7349,28 +7352,28 @@
         <v>264</v>
       </c>
       <c r="B173" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
+        <v>265</v>
+      </c>
+      <c r="B174" t="s">
         <v>266</v>
-      </c>
-      <c r="B174" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
+        <v>267</v>
+      </c>
+      <c r="B175" t="s">
         <v>268</v>
-      </c>
-      <c r="B175" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B176" t="s">
         <v>270</v>
@@ -7389,20 +7392,20 @@
         <v>272</v>
       </c>
       <c r="B178" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
+        <v>273</v>
+      </c>
+      <c r="B179" t="s">
         <v>274</v>
-      </c>
-      <c r="B179" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B180" t="s">
         <v>276</v>
@@ -7421,15 +7424,15 @@
         <v>278</v>
       </c>
       <c r="B182" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
+        <v>279</v>
+      </c>
+      <c r="B183" t="s">
         <v>280</v>
-      </c>
-      <c r="B183" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -7437,7 +7440,7 @@
         <v>281</v>
       </c>
       <c r="B184" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -7453,12 +7456,12 @@
         <v>283</v>
       </c>
       <c r="B186" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B187" t="s">
         <v>285</v>
@@ -7469,92 +7472,92 @@
         <v>286</v>
       </c>
       <c r="B188" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" t="s">
+        <v>287</v>
+      </c>
+      <c r="B189" t="s">
         <v>288</v>
-      </c>
-      <c r="B189" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
+        <v>289</v>
+      </c>
+      <c r="B190" t="s">
         <v>290</v>
-      </c>
-      <c r="B190" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
+        <v>291</v>
+      </c>
+      <c r="B191" t="s">
         <v>292</v>
-      </c>
-      <c r="B191" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" t="s">
+        <v>293</v>
+      </c>
+      <c r="B192" t="s">
         <v>294</v>
-      </c>
-      <c r="B192" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" t="s">
+        <v>295</v>
+      </c>
+      <c r="B193" t="s">
         <v>296</v>
-      </c>
-      <c r="B193" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
+        <v>297</v>
+      </c>
+      <c r="B194" t="s">
         <v>298</v>
-      </c>
-      <c r="B194" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" t="s">
+        <v>299</v>
+      </c>
+      <c r="B195" t="s">
         <v>300</v>
-      </c>
-      <c r="B195" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" t="s">
+        <v>301</v>
+      </c>
+      <c r="B196" t="s">
         <v>302</v>
-      </c>
-      <c r="B196" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
+        <v>303</v>
+      </c>
+      <c r="B197" t="s">
         <v>304</v>
-      </c>
-      <c r="B197" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" t="s">
+        <v>305</v>
+      </c>
+      <c r="B198" t="s">
         <v>306</v>
-      </c>
-      <c r="B198" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B199" t="s">
         <v>308</v>
@@ -7565,36 +7568,36 @@
         <v>309</v>
       </c>
       <c r="B200" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" t="s">
+        <v>310</v>
+      </c>
+      <c r="B201" t="s">
         <v>311</v>
-      </c>
-      <c r="B201" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
+        <v>312</v>
+      </c>
+      <c r="B202" t="s">
         <v>313</v>
-      </c>
-      <c r="B202" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" t="s">
+        <v>314</v>
+      </c>
+      <c r="B203" t="s">
         <v>315</v>
-      </c>
-      <c r="B203" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B204" t="s">
         <v>317</v>
@@ -7621,12 +7624,12 @@
         <v>320</v>
       </c>
       <c r="B207" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B208" t="s">
         <v>322</v>
@@ -7653,12 +7656,12 @@
         <v>325</v>
       </c>
       <c r="B211" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B212" t="s">
         <v>327</v>
@@ -7669,20 +7672,20 @@
         <v>328</v>
       </c>
       <c r="B213" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
+        <v>329</v>
+      </c>
+      <c r="B214" t="s">
         <v>330</v>
-      </c>
-      <c r="B214" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B215" t="s">
         <v>332</v>
@@ -7693,20 +7696,20 @@
         <v>333</v>
       </c>
       <c r="B216" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
+        <v>334</v>
+      </c>
+      <c r="B217" t="s">
         <v>335</v>
-      </c>
-      <c r="B217" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B218" t="s">
         <v>337</v>
@@ -7757,12 +7760,12 @@
         <v>343</v>
       </c>
       <c r="B224" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B225" t="s">
         <v>345</v>
@@ -7797,20 +7800,20 @@
         <v>349</v>
       </c>
       <c r="B229" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
+        <v>350</v>
+      </c>
+      <c r="B230" t="s">
         <v>351</v>
-      </c>
-      <c r="B230" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B231" t="s">
         <v>353</v>
@@ -7861,44 +7864,44 @@
         <v>359</v>
       </c>
       <c r="B237" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
+        <v>360</v>
+      </c>
+      <c r="B238" t="s">
         <v>361</v>
-      </c>
-      <c r="B238" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
+        <v>362</v>
+      </c>
+      <c r="B239" t="s">
         <v>363</v>
-      </c>
-      <c r="B239" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" t="s">
+        <v>364</v>
+      </c>
+      <c r="B240" t="s">
         <v>365</v>
-      </c>
-      <c r="B240" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
+        <v>366</v>
+      </c>
+      <c r="B241" t="s">
         <v>367</v>
-      </c>
-      <c r="B241" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="242" spans="1:2">
       <c r="A242" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B242" t="s">
         <v>369</v>
@@ -7909,12 +7912,12 @@
         <v>370</v>
       </c>
       <c r="B243" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B244" t="s">
         <v>372</v>
@@ -7925,52 +7928,52 @@
         <v>373</v>
       </c>
       <c r="B245" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
+        <v>374</v>
+      </c>
+      <c r="B246" t="s">
         <v>375</v>
-      </c>
-      <c r="B246" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="247" spans="1:2">
       <c r="A247" t="s">
+        <v>376</v>
+      </c>
+      <c r="B247" t="s">
         <v>377</v>
-      </c>
-      <c r="B247" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="248" spans="1:2">
       <c r="A248" t="s">
+        <v>378</v>
+      </c>
+      <c r="B248" t="s">
         <v>379</v>
-      </c>
-      <c r="B248" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="249" spans="1:2">
       <c r="A249" t="s">
+        <v>380</v>
+      </c>
+      <c r="B249" t="s">
         <v>381</v>
-      </c>
-      <c r="B249" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
+        <v>382</v>
+      </c>
+      <c r="B250" t="s">
         <v>383</v>
-      </c>
-      <c r="B250" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B251" t="s">
         <v>385</v>
@@ -7981,12 +7984,12 @@
         <v>386</v>
       </c>
       <c r="B252" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B253" t="s">
         <v>388</v>
@@ -8005,12 +8008,12 @@
         <v>390</v>
       </c>
       <c r="B255" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B256" t="s">
         <v>392</v>
@@ -8045,44 +8048,44 @@
         <v>396</v>
       </c>
       <c r="B260" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="261" spans="1:2">
       <c r="A261" t="s">
+        <v>397</v>
+      </c>
+      <c r="B261" t="s">
         <v>398</v>
-      </c>
-      <c r="B261" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="262" spans="1:2">
       <c r="A262" t="s">
+        <v>399</v>
+      </c>
+      <c r="B262" t="s">
         <v>400</v>
-      </c>
-      <c r="B262" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="263" spans="1:2">
       <c r="A263" t="s">
+        <v>401</v>
+      </c>
+      <c r="B263" t="s">
         <v>402</v>
-      </c>
-      <c r="B263" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="264" spans="1:2">
       <c r="A264" t="s">
+        <v>403</v>
+      </c>
+      <c r="B264" t="s">
         <v>404</v>
-      </c>
-      <c r="B264" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="265" spans="1:2">
       <c r="A265" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B265" t="s">
         <v>406</v>
@@ -8101,20 +8104,20 @@
         <v>408</v>
       </c>
       <c r="B267" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
+        <v>409</v>
+      </c>
+      <c r="B268" t="s">
         <v>410</v>
-      </c>
-      <c r="B268" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B269" t="s">
         <v>412</v>
@@ -8141,12 +8144,12 @@
         <v>415</v>
       </c>
       <c r="B272" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B273" t="s">
         <v>417</v>
@@ -8189,28 +8192,28 @@
         <v>422</v>
       </c>
       <c r="B278" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="279" spans="1:2">
       <c r="A279" t="s">
+        <v>423</v>
+      </c>
+      <c r="B279" t="s">
         <v>424</v>
-      </c>
-      <c r="B279" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="280" spans="1:2">
       <c r="A280" t="s">
+        <v>425</v>
+      </c>
+      <c r="B280" t="s">
         <v>426</v>
-      </c>
-      <c r="B280" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="281" spans="1:2">
       <c r="A281" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B281" t="s">
         <v>428</v>
@@ -8245,12 +8248,12 @@
         <v>432</v>
       </c>
       <c r="B285" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B286" t="s">
         <v>434</v>
@@ -8261,12 +8264,12 @@
         <v>435</v>
       </c>
       <c r="B287" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B288" t="s">
         <v>437</v>
@@ -8277,12 +8280,12 @@
         <v>438</v>
       </c>
       <c r="B289" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="290" spans="1:2">
       <c r="A290" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B290" t="s">
         <v>440</v>
@@ -8293,15 +8296,15 @@
         <v>441</v>
       </c>
       <c r="B291" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" t="s">
+        <v>442</v>
+      </c>
+      <c r="B292" t="s">
         <v>443</v>
-      </c>
-      <c r="B292" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -8309,20 +8312,20 @@
         <v>444</v>
       </c>
       <c r="B293" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="294" spans="1:2">
       <c r="A294" t="s">
+        <v>445</v>
+      </c>
+      <c r="B294" t="s">
         <v>446</v>
-      </c>
-      <c r="B294" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="295" spans="1:2">
       <c r="A295" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B295" t="s">
         <v>448</v>
@@ -8341,36 +8344,36 @@
         <v>450</v>
       </c>
       <c r="B297" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
+        <v>451</v>
+      </c>
+      <c r="B298" t="s">
         <v>452</v>
-      </c>
-      <c r="B298" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
+        <v>453</v>
+      </c>
+      <c r="B299" t="s">
         <v>454</v>
-      </c>
-      <c r="B299" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="300" spans="1:2">
       <c r="A300" t="s">
+        <v>455</v>
+      </c>
+      <c r="B300" t="s">
         <v>456</v>
-      </c>
-      <c r="B300" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="301" spans="1:2">
       <c r="A301" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B301" t="s">
         <v>458</v>
@@ -8381,12 +8384,12 @@
         <v>459</v>
       </c>
       <c r="B302" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B303" t="s">
         <v>461</v>
@@ -8397,44 +8400,44 @@
         <v>462</v>
       </c>
       <c r="B304" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="305" spans="1:2">
       <c r="A305" t="s">
+        <v>463</v>
+      </c>
+      <c r="B305" t="s">
         <v>464</v>
-      </c>
-      <c r="B305" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
+        <v>465</v>
+      </c>
+      <c r="B306" t="s">
         <v>466</v>
-      </c>
-      <c r="B306" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="307" spans="1:2">
       <c r="A307" t="s">
+        <v>467</v>
+      </c>
+      <c r="B307" t="s">
         <v>468</v>
-      </c>
-      <c r="B307" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="308" spans="1:2">
       <c r="A308" t="s">
+        <v>469</v>
+      </c>
+      <c r="B308" t="s">
         <v>470</v>
-      </c>
-      <c r="B308" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="309" spans="1:2">
       <c r="A309" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B309" t="s">
         <v>472</v>
@@ -8453,20 +8456,20 @@
         <v>474</v>
       </c>
       <c r="B311" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
+        <v>475</v>
+      </c>
+      <c r="B312" t="s">
         <v>476</v>
-      </c>
-      <c r="B312" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B313" t="s">
         <v>478</v>
@@ -8485,36 +8488,36 @@
         <v>480</v>
       </c>
       <c r="B315" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
+        <v>481</v>
+      </c>
+      <c r="B316" t="s">
         <v>482</v>
-      </c>
-      <c r="B316" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="317" spans="1:2">
       <c r="A317" t="s">
+        <v>483</v>
+      </c>
+      <c r="B317" t="s">
         <v>484</v>
-      </c>
-      <c r="B317" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="318" spans="1:2">
       <c r="A318" t="s">
+        <v>485</v>
+      </c>
+      <c r="B318" t="s">
         <v>486</v>
-      </c>
-      <c r="B318" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B319" t="s">
         <v>488</v>
@@ -8589,12 +8592,12 @@
         <v>497</v>
       </c>
       <c r="B328" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B329" t="s">
         <v>499</v>
@@ -8621,12 +8624,12 @@
         <v>502</v>
       </c>
       <c r="B332" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B333" t="s">
         <v>504</v>
@@ -8637,52 +8640,52 @@
         <v>505</v>
       </c>
       <c r="B334" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
+        <v>506</v>
+      </c>
+      <c r="B335" t="s">
         <v>507</v>
-      </c>
-      <c r="B335" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="336" spans="1:2">
       <c r="A336" t="s">
+        <v>508</v>
+      </c>
+      <c r="B336" t="s">
         <v>509</v>
-      </c>
-      <c r="B336" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="337" spans="1:2">
       <c r="A337" t="s">
+        <v>510</v>
+      </c>
+      <c r="B337" t="s">
         <v>511</v>
-      </c>
-      <c r="B337" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="338" spans="1:2">
       <c r="A338" t="s">
+        <v>512</v>
+      </c>
+      <c r="B338" t="s">
         <v>513</v>
-      </c>
-      <c r="B338" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="339" spans="1:2">
       <c r="A339" t="s">
+        <v>514</v>
+      </c>
+      <c r="B339" t="s">
         <v>515</v>
-      </c>
-      <c r="B339" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="A340" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B340" t="s">
         <v>517</v>
@@ -8693,156 +8696,156 @@
         <v>518</v>
       </c>
       <c r="B341" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="342" spans="1:2">
       <c r="A342" t="s">
+        <v>519</v>
+      </c>
+      <c r="B342" t="s">
         <v>520</v>
-      </c>
-      <c r="B342" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
+        <v>521</v>
+      </c>
+      <c r="B343" t="s">
         <v>522</v>
-      </c>
-      <c r="B343" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="344" spans="1:2">
       <c r="A344" t="s">
+        <v>523</v>
+      </c>
+      <c r="B344" t="s">
         <v>524</v>
-      </c>
-      <c r="B344" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="345" spans="1:2">
       <c r="A345" t="s">
+        <v>525</v>
+      </c>
+      <c r="B345" t="s">
         <v>526</v>
-      </c>
-      <c r="B345" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="346" spans="1:2">
       <c r="A346" t="s">
+        <v>527</v>
+      </c>
+      <c r="B346" t="s">
         <v>528</v>
-      </c>
-      <c r="B346" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="347" spans="1:2">
       <c r="A347" t="s">
+        <v>529</v>
+      </c>
+      <c r="B347" t="s">
         <v>530</v>
-      </c>
-      <c r="B347" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="348" spans="1:2">
       <c r="A348" t="s">
+        <v>531</v>
+      </c>
+      <c r="B348" t="s">
         <v>532</v>
-      </c>
-      <c r="B348" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="349" spans="1:2">
       <c r="A349" t="s">
+        <v>533</v>
+      </c>
+      <c r="B349" t="s">
         <v>534</v>
-      </c>
-      <c r="B349" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="350" spans="1:2">
       <c r="A350" t="s">
+        <v>535</v>
+      </c>
+      <c r="B350" t="s">
         <v>536</v>
-      </c>
-      <c r="B350" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="351" spans="1:2">
       <c r="A351" t="s">
+        <v>537</v>
+      </c>
+      <c r="B351" t="s">
         <v>538</v>
-      </c>
-      <c r="B351" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="352" spans="1:2">
       <c r="A352" t="s">
+        <v>539</v>
+      </c>
+      <c r="B352" t="s">
         <v>540</v>
-      </c>
-      <c r="B352" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="353" spans="1:2">
       <c r="A353" t="s">
+        <v>541</v>
+      </c>
+      <c r="B353" t="s">
         <v>542</v>
-      </c>
-      <c r="B353" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="354" spans="1:2">
       <c r="A354" t="s">
+        <v>543</v>
+      </c>
+      <c r="B354" t="s">
         <v>544</v>
-      </c>
-      <c r="B354" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="355" spans="1:2">
       <c r="A355" t="s">
+        <v>545</v>
+      </c>
+      <c r="B355" t="s">
         <v>546</v>
-      </c>
-      <c r="B355" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="356" spans="1:2">
       <c r="A356" t="s">
+        <v>547</v>
+      </c>
+      <c r="B356" t="s">
         <v>548</v>
-      </c>
-      <c r="B356" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="357" spans="1:2">
       <c r="A357" t="s">
+        <v>549</v>
+      </c>
+      <c r="B357" t="s">
         <v>550</v>
-      </c>
-      <c r="B357" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="358" spans="1:2">
       <c r="A358" t="s">
+        <v>551</v>
+      </c>
+      <c r="B358" t="s">
         <v>552</v>
-      </c>
-      <c r="B358" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="359" spans="1:2">
       <c r="A359" t="s">
+        <v>553</v>
+      </c>
+      <c r="B359" t="s">
         <v>554</v>
-      </c>
-      <c r="B359" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B360" t="s">
         <v>556</v>
@@ -8853,28 +8856,28 @@
         <v>557</v>
       </c>
       <c r="B361" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="362" spans="1:2">
       <c r="A362" t="s">
+        <v>558</v>
+      </c>
+      <c r="B362" t="s">
         <v>559</v>
-      </c>
-      <c r="B362" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="363" spans="1:2">
       <c r="A363" t="s">
+        <v>560</v>
+      </c>
+      <c r="B363" t="s">
         <v>561</v>
-      </c>
-      <c r="B363" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="364" spans="1:2">
       <c r="A364" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B364" t="s">
         <v>563</v>
@@ -8885,55 +8888,55 @@
         <v>564</v>
       </c>
       <c r="B365" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="366" spans="1:2">
       <c r="A366" t="s">
+        <v>565</v>
+      </c>
+      <c r="B366" t="s">
         <v>566</v>
-      </c>
-      <c r="B366" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" t="s">
+        <v>567</v>
+      </c>
+      <c r="B367" t="s">
         <v>568</v>
-      </c>
-      <c r="B367" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="368" spans="1:2">
       <c r="A368" t="s">
+        <v>569</v>
+      </c>
+      <c r="B368" t="s">
         <v>570</v>
-      </c>
-      <c r="B368" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="369" spans="1:2">
       <c r="A369" t="s">
+        <v>571</v>
+      </c>
+      <c r="B369" t="s">
         <v>572</v>
-      </c>
-      <c r="B369" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="370" spans="1:2">
       <c r="A370" t="s">
+        <v>573</v>
+      </c>
+      <c r="B370" t="s">
         <v>574</v>
-      </c>
-      <c r="B370" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="371" spans="1:2">
       <c r="A371" t="s">
+        <v>575</v>
+      </c>
+      <c r="B371" t="s">
         <v>576</v>
-      </c>
-      <c r="B371" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -8941,20 +8944,20 @@
         <v>577</v>
       </c>
       <c r="B372" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="373" spans="1:2">
       <c r="A373" t="s">
+        <v>578</v>
+      </c>
+      <c r="B373" t="s">
         <v>579</v>
-      </c>
-      <c r="B373" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="374" spans="1:2">
       <c r="A374" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B374" t="s">
         <v>581</v>
@@ -8973,12 +8976,12 @@
         <v>583</v>
       </c>
       <c r="B376" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="377" spans="1:2">
       <c r="A377" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B377" t="s">
         <v>585</v>
@@ -8989,31 +8992,31 @@
         <v>586</v>
       </c>
       <c r="B378" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="379" spans="1:2">
       <c r="A379" t="s">
+        <v>587</v>
+      </c>
+      <c r="B379" t="s">
         <v>588</v>
-      </c>
-      <c r="B379" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="380" spans="1:2">
       <c r="A380" t="s">
+        <v>589</v>
+      </c>
+      <c r="B380" t="s">
         <v>590</v>
-      </c>
-      <c r="B380" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="381" spans="1:2">
       <c r="A381" t="s">
+        <v>591</v>
+      </c>
+      <c r="B381" t="s">
         <v>592</v>
-      </c>
-      <c r="B381" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -9021,7 +9024,7 @@
         <v>593</v>
       </c>
       <c r="B382" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -9029,7 +9032,7 @@
         <v>594</v>
       </c>
       <c r="B383" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -9037,20 +9040,20 @@
         <v>595</v>
       </c>
       <c r="B384" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="385" spans="1:2">
       <c r="A385" t="s">
+        <v>596</v>
+      </c>
+      <c r="B385" t="s">
         <v>597</v>
-      </c>
-      <c r="B385" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="386" spans="1:2">
       <c r="A386" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B386" t="s">
         <v>599</v>
@@ -9061,12 +9064,12 @@
         <v>600</v>
       </c>
       <c r="B387" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="388" spans="1:2">
       <c r="A388" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B388" t="s">
         <v>602</v>
@@ -9077,20 +9080,20 @@
         <v>603</v>
       </c>
       <c r="B389" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="390" spans="1:2">
       <c r="A390" t="s">
+        <v>604</v>
+      </c>
+      <c r="B390" t="s">
         <v>605</v>
-      </c>
-      <c r="B390" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="391" spans="1:2">
       <c r="A391" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B391" t="s">
         <v>607</v>
@@ -9205,23 +9208,23 @@
         <v>621</v>
       </c>
       <c r="B405" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="406" spans="1:2">
       <c r="A406" t="s">
+        <v>622</v>
+      </c>
+      <c r="B406" t="s">
         <v>623</v>
-      </c>
-      <c r="B406" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="407" spans="1:2">
       <c r="A407" t="s">
+        <v>624</v>
+      </c>
+      <c r="B407" t="s">
         <v>625</v>
-      </c>
-      <c r="B407" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -9234,31 +9237,31 @@
     </row>
     <row r="409" spans="1:2">
       <c r="A409" t="s">
+        <v>627</v>
+      </c>
+      <c r="B409" t="s">
         <v>628</v>
-      </c>
-      <c r="B409" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="410" spans="1:2">
       <c r="A410" t="s">
+        <v>629</v>
+      </c>
+      <c r="B410" t="s">
         <v>630</v>
-      </c>
-      <c r="B410" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="411" spans="1:2">
       <c r="A411" t="s">
+        <v>631</v>
+      </c>
+      <c r="B411" t="s">
         <v>632</v>
-      </c>
-      <c r="B411" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="412" spans="1:2">
       <c r="A412" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B412" t="s">
         <v>634</v>
@@ -9277,12 +9280,12 @@
         <v>636</v>
       </c>
       <c r="B414" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="415" spans="1:2">
       <c r="A415" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B415" t="s">
         <v>638</v>
@@ -9301,12 +9304,12 @@
         <v>640</v>
       </c>
       <c r="B417" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="418" spans="1:2">
       <c r="A418" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B418" t="s">
         <v>642</v>
@@ -9325,100 +9328,100 @@
         <v>644</v>
       </c>
       <c r="B420" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="421" spans="1:2">
       <c r="A421" t="s">
+        <v>645</v>
+      </c>
+      <c r="B421" t="s">
         <v>646</v>
-      </c>
-      <c r="B421" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="422" spans="1:2">
       <c r="A422" t="s">
+        <v>647</v>
+      </c>
+      <c r="B422" t="s">
         <v>648</v>
-      </c>
-      <c r="B422" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="423" spans="1:2">
       <c r="A423" t="s">
+        <v>649</v>
+      </c>
+      <c r="B423" t="s">
         <v>650</v>
-      </c>
-      <c r="B423" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="424" spans="1:2">
       <c r="A424" t="s">
+        <v>651</v>
+      </c>
+      <c r="B424" t="s">
         <v>652</v>
-      </c>
-      <c r="B424" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="425" spans="1:2">
       <c r="A425" t="s">
+        <v>653</v>
+      </c>
+      <c r="B425" t="s">
         <v>654</v>
-      </c>
-      <c r="B425" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="426" spans="1:2">
       <c r="A426" t="s">
+        <v>655</v>
+      </c>
+      <c r="B426" t="s">
         <v>656</v>
-      </c>
-      <c r="B426" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="427" spans="1:2">
       <c r="A427" t="s">
+        <v>657</v>
+      </c>
+      <c r="B427" t="s">
         <v>658</v>
-      </c>
-      <c r="B427" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="428" spans="1:2">
       <c r="A428" t="s">
+        <v>659</v>
+      </c>
+      <c r="B428" t="s">
         <v>660</v>
-      </c>
-      <c r="B428" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="429" spans="1:2">
       <c r="A429" t="s">
+        <v>661</v>
+      </c>
+      <c r="B429" t="s">
         <v>662</v>
-      </c>
-      <c r="B429" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="430" spans="1:2">
       <c r="A430" t="s">
+        <v>663</v>
+      </c>
+      <c r="B430" t="s">
         <v>664</v>
-      </c>
-      <c r="B430" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="431" spans="1:2">
       <c r="A431" t="s">
+        <v>665</v>
+      </c>
+      <c r="B431" t="s">
         <v>666</v>
-      </c>
-      <c r="B431" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="432" spans="1:2">
       <c r="A432" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B432" t="s">
         <v>668</v>
@@ -9453,12 +9456,12 @@
         <v>672</v>
       </c>
       <c r="B436" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B437" t="s">
         <v>674</v>
@@ -9469,76 +9472,76 @@
         <v>675</v>
       </c>
       <c r="B438" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="439" spans="1:2">
       <c r="A439" t="s">
+        <v>676</v>
+      </c>
+      <c r="B439" t="s">
         <v>677</v>
-      </c>
-      <c r="B439" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="440" spans="1:2">
       <c r="A440" t="s">
+        <v>678</v>
+      </c>
+      <c r="B440" t="s">
         <v>679</v>
-      </c>
-      <c r="B440" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="441" spans="1:2">
       <c r="A441" t="s">
+        <v>680</v>
+      </c>
+      <c r="B441" t="s">
         <v>681</v>
-      </c>
-      <c r="B441" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="442" spans="1:2">
       <c r="A442" t="s">
+        <v>682</v>
+      </c>
+      <c r="B442" t="s">
         <v>683</v>
-      </c>
-      <c r="B442" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="443" spans="1:2">
       <c r="A443" t="s">
+        <v>684</v>
+      </c>
+      <c r="B443" t="s">
         <v>685</v>
-      </c>
-      <c r="B443" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="444" spans="1:2">
       <c r="A444" t="s">
+        <v>686</v>
+      </c>
+      <c r="B444" t="s">
         <v>687</v>
-      </c>
-      <c r="B444" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="445" spans="1:2">
       <c r="A445" t="s">
+        <v>688</v>
+      </c>
+      <c r="B445" t="s">
         <v>689</v>
-      </c>
-      <c r="B445" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="446" spans="1:2">
       <c r="A446" t="s">
+        <v>690</v>
+      </c>
+      <c r="B446" t="s">
         <v>691</v>
-      </c>
-      <c r="B446" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="447" spans="1:2">
       <c r="A447" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B447" t="s">
         <v>693</v>
@@ -9549,52 +9552,52 @@
         <v>694</v>
       </c>
       <c r="B448" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="449" spans="1:2">
       <c r="A449" t="s">
+        <v>695</v>
+      </c>
+      <c r="B449" t="s">
         <v>696</v>
-      </c>
-      <c r="B449" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="450" spans="1:2">
       <c r="A450" t="s">
+        <v>697</v>
+      </c>
+      <c r="B450" t="s">
         <v>698</v>
-      </c>
-      <c r="B450" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="451" spans="1:2">
       <c r="A451" t="s">
+        <v>699</v>
+      </c>
+      <c r="B451" t="s">
         <v>700</v>
-      </c>
-      <c r="B451" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="452" spans="1:2">
       <c r="A452" t="s">
+        <v>701</v>
+      </c>
+      <c r="B452" t="s">
         <v>702</v>
-      </c>
-      <c r="B452" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="453" spans="1:2">
       <c r="A453" t="s">
+        <v>703</v>
+      </c>
+      <c r="B453" t="s">
         <v>704</v>
-      </c>
-      <c r="B453" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B454" t="s">
         <v>706</v>
@@ -9605,76 +9608,76 @@
         <v>707</v>
       </c>
       <c r="B455" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="456" spans="1:2">
       <c r="A456" t="s">
+        <v>708</v>
+      </c>
+      <c r="B456" t="s">
         <v>709</v>
-      </c>
-      <c r="B456" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="457" spans="1:2">
       <c r="A457" t="s">
+        <v>710</v>
+      </c>
+      <c r="B457" t="s">
         <v>711</v>
-      </c>
-      <c r="B457" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="458" spans="1:2">
       <c r="A458" t="s">
+        <v>712</v>
+      </c>
+      <c r="B458" t="s">
         <v>713</v>
-      </c>
-      <c r="B458" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="459" spans="1:2">
       <c r="A459" t="s">
+        <v>714</v>
+      </c>
+      <c r="B459" t="s">
         <v>715</v>
-      </c>
-      <c r="B459" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="460" spans="1:2">
       <c r="A460" t="s">
+        <v>716</v>
+      </c>
+      <c r="B460" t="s">
         <v>717</v>
-      </c>
-      <c r="B460" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="461" spans="1:2">
       <c r="A461" t="s">
+        <v>718</v>
+      </c>
+      <c r="B461" t="s">
         <v>719</v>
-      </c>
-      <c r="B461" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="462" spans="1:2">
       <c r="A462" t="s">
+        <v>720</v>
+      </c>
+      <c r="B462" t="s">
         <v>721</v>
-      </c>
-      <c r="B462" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="463" spans="1:2">
       <c r="A463" t="s">
+        <v>722</v>
+      </c>
+      <c r="B463" t="s">
         <v>723</v>
-      </c>
-      <c r="B463" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="464" spans="1:2">
       <c r="A464" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B464" t="s">
         <v>725</v>
@@ -9693,7 +9696,7 @@
         <v>727</v>
       </c>
       <c r="B466" t="s">
-        <v>487</v>
+        <v>727</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -9701,7 +9704,7 @@
         <v>728</v>
       </c>
       <c r="B467" t="s">
-        <v>728</v>
+        <v>488</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -9709,20 +9712,20 @@
         <v>729</v>
       </c>
       <c r="B468" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
+        <v>730</v>
+      </c>
+      <c r="B469" t="s">
         <v>731</v>
-      </c>
-      <c r="B469" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B470" t="s">
         <v>733</v>
@@ -9733,12 +9736,12 @@
         <v>734</v>
       </c>
       <c r="B471" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B472" t="s">
         <v>736</v>
@@ -9749,7 +9752,7 @@
         <v>737</v>
       </c>
       <c r="B473" t="s">
-        <v>487</v>
+        <v>737</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -9757,7 +9760,7 @@
         <v>738</v>
       </c>
       <c r="B474" t="s">
-        <v>738</v>
+        <v>488</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -9773,12 +9776,12 @@
         <v>740</v>
       </c>
       <c r="B476" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B477" t="s">
         <v>742</v>
@@ -9789,12 +9792,12 @@
         <v>743</v>
       </c>
       <c r="B478" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B479" t="s">
         <v>745</v>
@@ -9813,12 +9816,12 @@
         <v>747</v>
       </c>
       <c r="B481" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B482" t="s">
         <v>749</v>
@@ -9829,20 +9832,20 @@
         <v>750</v>
       </c>
       <c r="B483" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" t="s">
+        <v>751</v>
+      </c>
+      <c r="B484" t="s">
         <v>752</v>
-      </c>
-      <c r="B484" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B485" t="s">
         <v>754</v>
@@ -9885,164 +9888,164 @@
         <v>759</v>
       </c>
       <c r="B490" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" t="s">
+        <v>760</v>
+      </c>
+      <c r="B491" t="s">
         <v>761</v>
-      </c>
-      <c r="B491" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
+        <v>762</v>
+      </c>
+      <c r="B492" t="s">
         <v>763</v>
-      </c>
-      <c r="B492" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
+        <v>764</v>
+      </c>
+      <c r="B493" t="s">
         <v>765</v>
-      </c>
-      <c r="B493" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="494" spans="1:2">
       <c r="A494" t="s">
+        <v>766</v>
+      </c>
+      <c r="B494" t="s">
         <v>767</v>
-      </c>
-      <c r="B494" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="495" spans="1:2">
       <c r="A495" t="s">
+        <v>768</v>
+      </c>
+      <c r="B495" t="s">
         <v>769</v>
-      </c>
-      <c r="B495" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="496" spans="1:2">
       <c r="A496" t="s">
+        <v>770</v>
+      </c>
+      <c r="B496" t="s">
         <v>771</v>
-      </c>
-      <c r="B496" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="497" spans="1:2">
       <c r="A497" t="s">
+        <v>772</v>
+      </c>
+      <c r="B497" t="s">
         <v>773</v>
-      </c>
-      <c r="B497" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="498" spans="1:2">
       <c r="A498" t="s">
+        <v>774</v>
+      </c>
+      <c r="B498" t="s">
         <v>775</v>
-      </c>
-      <c r="B498" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="499" spans="1:2">
       <c r="A499" t="s">
+        <v>776</v>
+      </c>
+      <c r="B499" t="s">
         <v>777</v>
-      </c>
-      <c r="B499" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="500" spans="1:2">
       <c r="A500" t="s">
+        <v>778</v>
+      </c>
+      <c r="B500" t="s">
         <v>779</v>
-      </c>
-      <c r="B500" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="501" spans="1:2">
       <c r="A501" t="s">
+        <v>780</v>
+      </c>
+      <c r="B501" t="s">
         <v>781</v>
-      </c>
-      <c r="B501" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="502" spans="1:2">
       <c r="A502" t="s">
+        <v>782</v>
+      </c>
+      <c r="B502" t="s">
         <v>783</v>
-      </c>
-      <c r="B502" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="503" spans="1:2">
       <c r="A503" t="s">
+        <v>784</v>
+      </c>
+      <c r="B503" t="s">
         <v>785</v>
-      </c>
-      <c r="B503" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="504" spans="1:2">
       <c r="A504" t="s">
+        <v>786</v>
+      </c>
+      <c r="B504" t="s">
         <v>787</v>
-      </c>
-      <c r="B504" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="505" spans="1:2">
       <c r="A505" t="s">
+        <v>788</v>
+      </c>
+      <c r="B505" t="s">
         <v>789</v>
-      </c>
-      <c r="B505" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="506" spans="1:2">
       <c r="A506" t="s">
+        <v>790</v>
+      </c>
+      <c r="B506" t="s">
         <v>791</v>
-      </c>
-      <c r="B506" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="507" spans="1:2">
       <c r="A507" t="s">
+        <v>792</v>
+      </c>
+      <c r="B507" t="s">
         <v>793</v>
-      </c>
-      <c r="B507" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="508" spans="1:2">
       <c r="A508" t="s">
+        <v>794</v>
+      </c>
+      <c r="B508" t="s">
         <v>795</v>
-      </c>
-      <c r="B508" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="509" spans="1:2">
       <c r="A509" t="s">
+        <v>796</v>
+      </c>
+      <c r="B509" t="s">
         <v>797</v>
-      </c>
-      <c r="B509" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="510" spans="1:2">
       <c r="A510" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B510" t="s">
         <v>799</v>
@@ -10061,12 +10064,12 @@
         <v>801</v>
       </c>
       <c r="B512" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="A513" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B513" t="s">
         <v>803</v>
@@ -10077,12 +10080,12 @@
         <v>804</v>
       </c>
       <c r="B514" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="A515" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B515" t="s">
         <v>806</v>
@@ -10093,20 +10096,20 @@
         <v>807</v>
       </c>
       <c r="B516" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="517" spans="1:2">
       <c r="A517" t="s">
+        <v>808</v>
+      </c>
+      <c r="B517" t="s">
         <v>809</v>
-      </c>
-      <c r="B517" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B518" t="s">
         <v>811</v>
@@ -10133,92 +10136,92 @@
         <v>814</v>
       </c>
       <c r="B521" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="522" spans="1:2">
       <c r="A522" t="s">
+        <v>815</v>
+      </c>
+      <c r="B522" t="s">
         <v>816</v>
-      </c>
-      <c r="B522" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="523" spans="1:2">
       <c r="A523" t="s">
+        <v>817</v>
+      </c>
+      <c r="B523" t="s">
         <v>818</v>
-      </c>
-      <c r="B523" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="A524" t="s">
+        <v>819</v>
+      </c>
+      <c r="B524" t="s">
         <v>820</v>
-      </c>
-      <c r="B524" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="525" spans="1:2">
       <c r="A525" t="s">
+        <v>821</v>
+      </c>
+      <c r="B525" t="s">
         <v>822</v>
-      </c>
-      <c r="B525" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="526" spans="1:2">
       <c r="A526" t="s">
+        <v>823</v>
+      </c>
+      <c r="B526" t="s">
         <v>824</v>
-      </c>
-      <c r="B526" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="527" spans="1:2">
       <c r="A527" t="s">
+        <v>825</v>
+      </c>
+      <c r="B527" t="s">
         <v>826</v>
-      </c>
-      <c r="B527" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="528" spans="1:2">
       <c r="A528" t="s">
+        <v>827</v>
+      </c>
+      <c r="B528" t="s">
         <v>828</v>
-      </c>
-      <c r="B528" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="529" spans="1:2">
       <c r="A529" t="s">
+        <v>829</v>
+      </c>
+      <c r="B529" t="s">
         <v>830</v>
-      </c>
-      <c r="B529" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="530" spans="1:2">
       <c r="A530" t="s">
+        <v>831</v>
+      </c>
+      <c r="B530" t="s">
         <v>832</v>
-      </c>
-      <c r="B530" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="531" spans="1:2">
       <c r="A531" t="s">
+        <v>833</v>
+      </c>
+      <c r="B531" t="s">
         <v>834</v>
-      </c>
-      <c r="B531" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="532" spans="1:2">
       <c r="A532" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B532" t="s">
         <v>836</v>
@@ -10229,20 +10232,20 @@
         <v>837</v>
       </c>
       <c r="B533" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="534" spans="1:2">
       <c r="A534" t="s">
+        <v>838</v>
+      </c>
+      <c r="B534" t="s">
         <v>839</v>
-      </c>
-      <c r="B534" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B535" t="s">
         <v>841</v>
@@ -10269,12 +10272,12 @@
         <v>844</v>
       </c>
       <c r="B538" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B539" t="s">
         <v>846</v>
@@ -10325,12 +10328,12 @@
         <v>852</v>
       </c>
       <c r="B545" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B546" t="s">
         <v>854</v>
@@ -10341,20 +10344,20 @@
         <v>855</v>
       </c>
       <c r="B547" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="548" spans="1:2">
       <c r="A548" t="s">
+        <v>856</v>
+      </c>
+      <c r="B548" t="s">
         <v>857</v>
-      </c>
-      <c r="B548" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B549" t="s">
         <v>859</v>
@@ -10413,60 +10416,60 @@
         <v>866</v>
       </c>
       <c r="B556" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
+        <v>867</v>
+      </c>
+      <c r="B557" t="s">
         <v>868</v>
-      </c>
-      <c r="B557" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
+        <v>869</v>
+      </c>
+      <c r="B558" t="s">
         <v>870</v>
-      </c>
-      <c r="B558" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
+        <v>871</v>
+      </c>
+      <c r="B559" t="s">
         <v>872</v>
-      </c>
-      <c r="B559" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
+        <v>873</v>
+      </c>
+      <c r="B560" t="s">
         <v>874</v>
-      </c>
-      <c r="B560" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="561" spans="1:2">
       <c r="A561" t="s">
+        <v>875</v>
+      </c>
+      <c r="B561" t="s">
         <v>876</v>
-      </c>
-      <c r="B561" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="562" spans="1:2">
       <c r="A562" t="s">
+        <v>877</v>
+      </c>
+      <c r="B562" t="s">
         <v>878</v>
-      </c>
-      <c r="B562" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="563" spans="1:2">
       <c r="A563" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B563" t="s">
         <v>880</v>
@@ -10493,20 +10496,20 @@
         <v>883</v>
       </c>
       <c r="B566" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
+        <v>884</v>
+      </c>
+      <c r="B567" t="s">
         <v>885</v>
-      </c>
-      <c r="B567" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B568" t="s">
         <v>887</v>
@@ -10517,20 +10520,20 @@
         <v>888</v>
       </c>
       <c r="B569" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="570" spans="1:2">
       <c r="A570" t="s">
+        <v>889</v>
+      </c>
+      <c r="B570" t="s">
         <v>890</v>
-      </c>
-      <c r="B570" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="571" spans="1:2">
       <c r="A571" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B571" t="s">
         <v>892</v>
@@ -10541,28 +10544,28 @@
         <v>893</v>
       </c>
       <c r="B572" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="573" spans="1:2">
       <c r="A573" t="s">
+        <v>894</v>
+      </c>
+      <c r="B573" t="s">
         <v>895</v>
-      </c>
-      <c r="B573" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="574" spans="1:2">
       <c r="A574" t="s">
+        <v>896</v>
+      </c>
+      <c r="B574" t="s">
         <v>897</v>
-      </c>
-      <c r="B574" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="575" spans="1:2">
       <c r="A575" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B575" t="s">
         <v>899</v>
@@ -10613,20 +10616,20 @@
         <v>905</v>
       </c>
       <c r="B581" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
+        <v>906</v>
+      </c>
+      <c r="B582" t="s">
         <v>907</v>
-      </c>
-      <c r="B582" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B583" t="s">
         <v>909</v>
@@ -10637,36 +10640,36 @@
         <v>910</v>
       </c>
       <c r="B584" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
+        <v>911</v>
+      </c>
+      <c r="B585" t="s">
         <v>912</v>
-      </c>
-      <c r="B585" t="s">
-        <v>913</v>
       </c>
     </row>
     <row r="586" spans="1:2">
       <c r="A586" t="s">
+        <v>913</v>
+      </c>
+      <c r="B586" t="s">
         <v>914</v>
-      </c>
-      <c r="B586" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="587" spans="1:2">
       <c r="A587" t="s">
+        <v>915</v>
+      </c>
+      <c r="B587" t="s">
         <v>916</v>
-      </c>
-      <c r="B587" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B588" t="s">
         <v>918</v>
@@ -10677,20 +10680,20 @@
         <v>919</v>
       </c>
       <c r="B589" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="590" spans="1:2">
       <c r="A590" t="s">
+        <v>920</v>
+      </c>
+      <c r="B590" t="s">
         <v>921</v>
-      </c>
-      <c r="B590" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B591" t="s">
         <v>923</v>
@@ -10701,52 +10704,52 @@
         <v>924</v>
       </c>
       <c r="B592" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="593" spans="1:2">
       <c r="A593" t="s">
+        <v>925</v>
+      </c>
+      <c r="B593" t="s">
         <v>926</v>
-      </c>
-      <c r="B593" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
+        <v>927</v>
+      </c>
+      <c r="B594" t="s">
         <v>928</v>
-      </c>
-      <c r="B594" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="595" spans="1:2">
       <c r="A595" t="s">
+        <v>929</v>
+      </c>
+      <c r="B595" t="s">
         <v>930</v>
-      </c>
-      <c r="B595" t="s">
-        <v>931</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" t="s">
+        <v>931</v>
+      </c>
+      <c r="B596" t="s">
         <v>932</v>
-      </c>
-      <c r="B596" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="597" spans="1:2">
       <c r="A597" t="s">
+        <v>933</v>
+      </c>
+      <c r="B597" t="s">
         <v>934</v>
-      </c>
-      <c r="B597" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="598" spans="1:2">
       <c r="A598" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B598" t="s">
         <v>936</v>
@@ -10757,12 +10760,12 @@
         <v>937</v>
       </c>
       <c r="B599" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B600" t="s">
         <v>939</v>
@@ -10781,44 +10784,44 @@
         <v>941</v>
       </c>
       <c r="B602" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
+        <v>942</v>
+      </c>
+      <c r="B603" t="s">
         <v>943</v>
-      </c>
-      <c r="B603" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
+        <v>944</v>
+      </c>
+      <c r="B604" t="s">
         <v>945</v>
-      </c>
-      <c r="B604" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" t="s">
+        <v>946</v>
+      </c>
+      <c r="B605" t="s">
         <v>947</v>
-      </c>
-      <c r="B605" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="606" spans="1:2">
       <c r="A606" t="s">
+        <v>948</v>
+      </c>
+      <c r="B606" t="s">
         <v>949</v>
-      </c>
-      <c r="B606" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="607" spans="1:2">
       <c r="A607" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B607" t="s">
         <v>951</v>
@@ -10837,12 +10840,12 @@
         <v>953</v>
       </c>
       <c r="B609" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B610" t="s">
         <v>955</v>
@@ -10861,12 +10864,12 @@
         <v>957</v>
       </c>
       <c r="B612" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B613" t="s">
         <v>959</v>
@@ -10877,20 +10880,20 @@
         <v>960</v>
       </c>
       <c r="B614" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
+        <v>961</v>
+      </c>
+      <c r="B615" t="s">
         <v>962</v>
-      </c>
-      <c r="B615" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B616" t="s">
         <v>964</v>
@@ -10909,20 +10912,20 @@
         <v>966</v>
       </c>
       <c r="B618" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="619" spans="1:2">
       <c r="A619" t="s">
+        <v>967</v>
+      </c>
+      <c r="B619" t="s">
         <v>968</v>
-      </c>
-      <c r="B619" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="620" spans="1:2">
       <c r="A620" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B620" t="s">
         <v>970</v>
@@ -10941,36 +10944,36 @@
         <v>972</v>
       </c>
       <c r="B622" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
+        <v>973</v>
+      </c>
+      <c r="B623" t="s">
         <v>974</v>
-      </c>
-      <c r="B623" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
+        <v>975</v>
+      </c>
+      <c r="B624" t="s">
         <v>976</v>
-      </c>
-      <c r="B624" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
+        <v>977</v>
+      </c>
+      <c r="B625" t="s">
         <v>978</v>
-      </c>
-      <c r="B625" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="626" spans="1:2">
       <c r="A626" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B626" t="s">
         <v>980</v>
@@ -10989,12 +10992,12 @@
         <v>982</v>
       </c>
       <c r="B628" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B629" t="s">
         <v>984</v>
@@ -11013,28 +11016,28 @@
         <v>986</v>
       </c>
       <c r="B631" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
+        <v>987</v>
+      </c>
+      <c r="B632" t="s">
         <v>988</v>
-      </c>
-      <c r="B632" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" t="s">
+        <v>989</v>
+      </c>
+      <c r="B633" t="s">
         <v>990</v>
-      </c>
-      <c r="B633" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B634" t="s">
         <v>992</v>
@@ -11125,12 +11128,12 @@
         <v>1003</v>
       </c>
       <c r="B645" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B646" t="s">
         <v>1005</v>
@@ -11165,36 +11168,36 @@
         <v>1009</v>
       </c>
       <c r="B650" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B651" t="s">
         <v>1011</v>
-      </c>
-      <c r="B651" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B652" t="s">
         <v>1013</v>
-      </c>
-      <c r="B652" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B653" t="s">
         <v>1015</v>
-      </c>
-      <c r="B653" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B654" t="s">
         <v>1017</v>
@@ -11205,12 +11208,12 @@
         <v>1018</v>
       </c>
       <c r="B655" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="656" spans="1:2">
       <c r="A656" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B656" t="s">
         <v>1020</v>
@@ -11221,12 +11224,12 @@
         <v>1021</v>
       </c>
       <c r="B657" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B658" t="s">
         <v>1023</v>
@@ -11237,20 +11240,20 @@
         <v>1024</v>
       </c>
       <c r="B659" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="660" spans="1:2">
       <c r="A660" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B660" t="s">
         <v>1026</v>
-      </c>
-      <c r="B660" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="661" spans="1:2">
       <c r="A661" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B661" t="s">
         <v>1028</v>
@@ -11261,60 +11264,60 @@
         <v>1029</v>
       </c>
       <c r="B662" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="663" spans="1:2">
       <c r="A663" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B663" t="s">
         <v>1031</v>
-      </c>
-      <c r="B663" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="664" spans="1:2">
       <c r="A664" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B664" t="s">
         <v>1033</v>
-      </c>
-      <c r="B664" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="665" spans="1:2">
       <c r="A665" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B665" t="s">
         <v>1035</v>
-      </c>
-      <c r="B665" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="666" spans="1:2">
       <c r="A666" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B666" t="s">
         <v>1037</v>
-      </c>
-      <c r="B666" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="667" spans="1:2">
       <c r="A667" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B667" t="s">
         <v>1039</v>
-      </c>
-      <c r="B667" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="668" spans="1:2">
       <c r="A668" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B668" t="s">
         <v>1041</v>
-      </c>
-      <c r="B668" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="669" spans="1:2">
       <c r="A669" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B669" t="s">
         <v>1043</v>
@@ -11349,20 +11352,20 @@
         <v>1047</v>
       </c>
       <c r="B673" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B674" t="s">
         <v>1049</v>
-      </c>
-      <c r="B674" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B675" t="s">
         <v>1051</v>
@@ -11389,12 +11392,12 @@
         <v>1054</v>
       </c>
       <c r="B678" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="679" spans="1:2">
       <c r="A679" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B679" t="s">
         <v>1056</v>
@@ -11437,20 +11440,20 @@
         <v>1061</v>
       </c>
       <c r="B684" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B685" t="s">
         <v>1063</v>
-      </c>
-      <c r="B685" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B686" t="s">
         <v>1065</v>
@@ -11477,84 +11480,84 @@
         <v>1068</v>
       </c>
       <c r="B689" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B690" t="s">
         <v>1070</v>
-      </c>
-      <c r="B690" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B691" t="s">
         <v>1072</v>
-      </c>
-      <c r="B691" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B692" t="s">
         <v>1074</v>
-      </c>
-      <c r="B692" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="693" spans="1:2">
       <c r="A693" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B693" t="s">
         <v>1076</v>
-      </c>
-      <c r="B693" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="694" spans="1:2">
       <c r="A694" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B694" t="s">
         <v>1078</v>
-      </c>
-      <c r="B694" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="695" spans="1:2">
       <c r="A695" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B695" t="s">
         <v>1080</v>
-      </c>
-      <c r="B695" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="696" spans="1:2">
       <c r="A696" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B696" t="s">
         <v>1082</v>
-      </c>
-      <c r="B696" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="697" spans="1:2">
       <c r="A697" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B697" t="s">
         <v>1084</v>
-      </c>
-      <c r="B697" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="698" spans="1:2">
       <c r="A698" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B698" t="s">
         <v>1086</v>
-      </c>
-      <c r="B698" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="699" spans="1:2">
       <c r="A699" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B699" t="s">
         <v>1088</v>
@@ -11565,20 +11568,20 @@
         <v>1089</v>
       </c>
       <c r="B700" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="701" spans="1:2">
       <c r="A701" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B701" t="s">
         <v>1091</v>
-      </c>
-      <c r="B701" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="702" spans="1:2">
       <c r="A702" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B702" t="s">
         <v>1093</v>
@@ -11589,20 +11592,20 @@
         <v>1094</v>
       </c>
       <c r="B703" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B704" t="s">
         <v>1096</v>
-      </c>
-      <c r="B704" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="705" spans="1:2">
       <c r="A705" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B705" t="s">
         <v>1098</v>
@@ -11613,12 +11616,12 @@
         <v>1099</v>
       </c>
       <c r="B706" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="707" spans="1:2">
       <c r="A707" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B707" t="s">
         <v>1101</v>
@@ -11637,12 +11640,12 @@
         <v>1103</v>
       </c>
       <c r="B709" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B710" t="s">
         <v>1105</v>
@@ -11701,12 +11704,12 @@
         <v>1112</v>
       </c>
       <c r="B717" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B718" t="s">
         <v>1114</v>
@@ -11717,12 +11720,12 @@
         <v>1115</v>
       </c>
       <c r="B719" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B720" t="s">
         <v>1117</v>
@@ -11741,92 +11744,92 @@
         <v>1119</v>
       </c>
       <c r="B722" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="723" spans="1:2">
       <c r="A723" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B723" t="s">
         <v>1121</v>
-      </c>
-      <c r="B723" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="724" spans="1:2">
       <c r="A724" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B724" t="s">
         <v>1123</v>
-      </c>
-      <c r="B724" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B725" t="s">
         <v>1125</v>
-      </c>
-      <c r="B725" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B726" t="s">
         <v>1127</v>
-      </c>
-      <c r="B726" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="727" spans="1:2">
       <c r="A727" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B727" t="s">
         <v>1129</v>
-      </c>
-      <c r="B727" t="s">
-        <v>1130</v>
       </c>
     </row>
     <row r="728" spans="1:2">
       <c r="A728" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B728" t="s">
         <v>1131</v>
-      </c>
-      <c r="B728" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B729" t="s">
         <v>1133</v>
-      </c>
-      <c r="B729" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="730" spans="1:2">
       <c r="A730" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B730" t="s">
         <v>1135</v>
-      </c>
-      <c r="B730" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="731" spans="1:2">
       <c r="A731" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B731" t="s">
         <v>1137</v>
-      </c>
-      <c r="B731" t="s">
-        <v>1138</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B732" t="s">
         <v>1139</v>
-      </c>
-      <c r="B732" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B733" t="s">
         <v>1141</v>
@@ -11837,20 +11840,20 @@
         <v>1142</v>
       </c>
       <c r="B734" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="735" spans="1:2">
       <c r="A735" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B735" t="s">
         <v>1144</v>
-      </c>
-      <c r="B735" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="736" spans="1:2">
       <c r="A736" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B736" t="s">
         <v>1146</v>
@@ -11861,20 +11864,20 @@
         <v>1147</v>
       </c>
       <c r="B737" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="738" spans="1:2">
       <c r="A738" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B738" t="s">
         <v>1149</v>
-      </c>
-      <c r="B738" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B739" t="s">
         <v>1151</v>
@@ -11901,12 +11904,12 @@
         <v>1154</v>
       </c>
       <c r="B742" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B743" t="s">
         <v>1156</v>
@@ -11949,20 +11952,20 @@
         <v>1161</v>
       </c>
       <c r="B748" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B749" t="s">
         <v>1163</v>
-      </c>
-      <c r="B749" t="s">
-        <v>1164</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B750" t="s">
         <v>1165</v>
@@ -11997,60 +12000,60 @@
         <v>1169</v>
       </c>
       <c r="B754" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B755" t="s">
         <v>1171</v>
-      </c>
-      <c r="B755" t="s">
-        <v>1172</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B756" t="s">
         <v>1173</v>
-      </c>
-      <c r="B756" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B757" t="s">
         <v>1175</v>
-      </c>
-      <c r="B757" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="758" spans="1:2">
       <c r="A758" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B758" t="s">
         <v>1177</v>
-      </c>
-      <c r="B758" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="759" spans="1:2">
       <c r="A759" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B759" t="s">
         <v>1179</v>
-      </c>
-      <c r="B759" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="760" spans="1:2">
       <c r="A760" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B760" t="s">
         <v>1181</v>
-      </c>
-      <c r="B760" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="761" spans="1:2">
       <c r="A761" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B761" t="s">
         <v>1183</v>
@@ -12061,28 +12064,28 @@
         <v>1184</v>
       </c>
       <c r="B762" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="763" spans="1:2">
       <c r="A763" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B763" t="s">
         <v>1186</v>
-      </c>
-      <c r="B763" t="s">
-        <v>1187</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B764" t="s">
         <v>1188</v>
-      </c>
-      <c r="B764" t="s">
-        <v>1189</v>
       </c>
     </row>
     <row r="765" spans="1:2">
       <c r="A765" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B765" t="s">
         <v>1190</v>
@@ -12093,12 +12096,12 @@
         <v>1191</v>
       </c>
       <c r="B766" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="767" spans="1:2">
       <c r="A767" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B767" t="s">
         <v>1193</v>
@@ -12117,39 +12120,39 @@
         <v>1195</v>
       </c>
       <c r="B769" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B770" t="s">
         <v>1197</v>
-      </c>
-      <c r="B770" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B771" t="s">
         <v>1199</v>
-      </c>
-      <c r="B771" t="s">
-        <v>1200</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B772" t="s">
         <v>1201</v>
-      </c>
-      <c r="B772" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="773" spans="1:2">
       <c r="A773" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B773" t="s">
         <v>1203</v>
-      </c>
-      <c r="B773" t="s">
-        <v>1204</v>
       </c>
     </row>
     <row r="774" spans="1:2">
@@ -12157,7 +12160,7 @@
         <v>1204</v>
       </c>
       <c r="B774" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="775" spans="1:2">
@@ -12165,28 +12168,28 @@
         <v>1205</v>
       </c>
       <c r="B775" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="776" spans="1:2">
       <c r="A776" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B776" t="s">
         <v>1207</v>
-      </c>
-      <c r="B776" t="s">
-        <v>1208</v>
       </c>
     </row>
     <row r="777" spans="1:2">
       <c r="A777" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B777" t="s">
         <v>1209</v>
-      </c>
-      <c r="B777" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="778" spans="1:2">
       <c r="A778" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="B778" t="s">
         <v>1211</v>
@@ -12213,12 +12216,12 @@
         <v>1214</v>
       </c>
       <c r="B781" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="782" spans="1:2">
       <c r="A782" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B782" t="s">
         <v>1216</v>
@@ -12237,36 +12240,36 @@
         <v>1218</v>
       </c>
       <c r="B784" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="785" spans="1:2">
       <c r="A785" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B785" t="s">
         <v>1220</v>
-      </c>
-      <c r="B785" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B786" t="s">
         <v>1222</v>
-      </c>
-      <c r="B786" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="787" spans="1:2">
       <c r="A787" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B787" t="s">
         <v>1224</v>
-      </c>
-      <c r="B787" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="788" spans="1:2">
       <c r="A788" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B788" t="s">
         <v>1226</v>
@@ -12293,20 +12296,20 @@
         <v>1229</v>
       </c>
       <c r="B791" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B792" t="s">
         <v>1231</v>
-      </c>
-      <c r="B792" t="s">
-        <v>1232</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="B793" t="s">
         <v>1233</v>
@@ -12317,12 +12320,12 @@
         <v>1234</v>
       </c>
       <c r="B794" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="B795" t="s">
         <v>1236</v>
@@ -12381,12 +12384,12 @@
         <v>1243</v>
       </c>
       <c r="B802" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="B803" t="s">
         <v>1245</v>
@@ -12397,68 +12400,68 @@
         <v>1246</v>
       </c>
       <c r="B804" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B805" t="s">
         <v>1248</v>
-      </c>
-      <c r="B805" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B806" t="s">
         <v>1250</v>
-      </c>
-      <c r="B806" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B807" t="s">
         <v>1252</v>
-      </c>
-      <c r="B807" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B808" t="s">
         <v>1254</v>
-      </c>
-      <c r="B808" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B809" t="s">
         <v>1256</v>
-      </c>
-      <c r="B809" t="s">
-        <v>1257</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B810" t="s">
         <v>1258</v>
-      </c>
-      <c r="B810" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B811" t="s">
         <v>1260</v>
-      </c>
-      <c r="B811" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="812" spans="1:2">
       <c r="A812" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B812" t="s">
         <v>1262</v>
@@ -12493,36 +12496,36 @@
         <v>1266</v>
       </c>
       <c r="B816" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B817" t="s">
         <v>1268</v>
-      </c>
-      <c r="B817" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B818" t="s">
         <v>1270</v>
-      </c>
-      <c r="B818" t="s">
-        <v>1271</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B819" t="s">
         <v>1272</v>
-      </c>
-      <c r="B819" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="820" spans="1:2">
       <c r="A820" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="B820" t="s">
         <v>1274</v>
@@ -12533,36 +12536,36 @@
         <v>1275</v>
       </c>
       <c r="B821" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="822" spans="1:2">
       <c r="A822" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B822" t="s">
         <v>1277</v>
-      </c>
-      <c r="B822" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B823" t="s">
         <v>1279</v>
-      </c>
-      <c r="B823" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="824" spans="1:2">
       <c r="A824" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B824" t="s">
         <v>1281</v>
-      </c>
-      <c r="B824" t="s">
-        <v>1282</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B825" t="s">
         <v>1283</v>
@@ -12573,12 +12576,12 @@
         <v>1284</v>
       </c>
       <c r="B826" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B827" t="s">
         <v>1286</v>
@@ -12589,12 +12592,12 @@
         <v>1287</v>
       </c>
       <c r="B828" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="B829" t="s">
         <v>1289</v>
@@ -12605,12 +12608,12 @@
         <v>1290</v>
       </c>
       <c r="B830" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B831" t="s">
         <v>1292</v>
@@ -12621,12 +12624,12 @@
         <v>1293</v>
       </c>
       <c r="B832" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="B833" t="s">
         <v>1295</v>
@@ -12637,7 +12640,7 @@
         <v>1296</v>
       </c>
       <c r="B834" t="s">
-        <v>716</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="835" spans="1:2">
@@ -12645,20 +12648,20 @@
         <v>1297</v>
       </c>
       <c r="B835" t="s">
-        <v>1298</v>
+        <v>717</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B836" t="s">
         <v>1299</v>
-      </c>
-      <c r="B836" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="B837" t="s">
         <v>1301</v>
@@ -12693,36 +12696,36 @@
         <v>1305</v>
       </c>
       <c r="B841" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B842" t="s">
         <v>1307</v>
-      </c>
-      <c r="B842" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B843" t="s">
         <v>1309</v>
-      </c>
-      <c r="B843" t="s">
-        <v>1310</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B844" t="s">
         <v>1311</v>
-      </c>
-      <c r="B844" t="s">
-        <v>1312</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="B845" t="s">
         <v>1313</v>
@@ -12733,20 +12736,20 @@
         <v>1314</v>
       </c>
       <c r="B846" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B847" t="s">
         <v>1316</v>
-      </c>
-      <c r="B847" t="s">
-        <v>1317</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B848" t="s">
         <v>1318</v>
@@ -12781,108 +12784,108 @@
         <v>1322</v>
       </c>
       <c r="B852" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B853" t="s">
         <v>1324</v>
-      </c>
-      <c r="B853" t="s">
-        <v>1325</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B854" t="s">
         <v>1326</v>
-      </c>
-      <c r="B854" t="s">
-        <v>1327</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B855" t="s">
         <v>1328</v>
-      </c>
-      <c r="B855" t="s">
-        <v>1329</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B856" t="s">
         <v>1330</v>
-      </c>
-      <c r="B856" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B857" t="s">
         <v>1332</v>
-      </c>
-      <c r="B857" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B858" t="s">
         <v>1334</v>
-      </c>
-      <c r="B858" t="s">
-        <v>1335</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B859" t="s">
         <v>1336</v>
-      </c>
-      <c r="B859" t="s">
-        <v>1337</v>
       </c>
     </row>
     <row r="860" spans="1:2">
       <c r="A860" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B860" t="s">
         <v>1338</v>
-      </c>
-      <c r="B860" t="s">
-        <v>1339</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B861" t="s">
         <v>1340</v>
-      </c>
-      <c r="B861" t="s">
-        <v>1341</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B862" t="s">
         <v>1342</v>
-      </c>
-      <c r="B862" t="s">
-        <v>1343</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B863" t="s">
         <v>1344</v>
-      </c>
-      <c r="B863" t="s">
-        <v>1345</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B864" t="s">
         <v>1346</v>
-      </c>
-      <c r="B864" t="s">
-        <v>1347</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="B865" t="s">
         <v>1348</v>
@@ -12909,12 +12912,12 @@
         <v>1351</v>
       </c>
       <c r="B868" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="B869" t="s">
         <v>1353</v>
@@ -12949,12 +12952,12 @@
         <v>1357</v>
       </c>
       <c r="B873" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="B874" t="s">
         <v>1359</v>
@@ -12981,20 +12984,20 @@
         <v>1362</v>
       </c>
       <c r="B877" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B878" t="s">
         <v>1364</v>
-      </c>
-      <c r="B878" t="s">
-        <v>1365</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="B879" t="s">
         <v>1366</v>
@@ -13005,39 +13008,39 @@
         <v>1367</v>
       </c>
       <c r="B880" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B881" t="s">
         <v>1369</v>
-      </c>
-      <c r="B881" t="s">
-        <v>1370</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B882" t="s">
         <v>1371</v>
-      </c>
-      <c r="B882" t="s">
-        <v>1372</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B883" t="s">
         <v>1373</v>
-      </c>
-      <c r="B883" t="s">
-        <v>1374</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B884" t="s">
         <v>1375</v>
-      </c>
-      <c r="B884" t="s">
-        <v>1374</v>
       </c>
     </row>
     <row r="885" spans="1:2">
@@ -13045,12 +13048,12 @@
         <v>1376</v>
       </c>
       <c r="B885" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="B886" t="s">
         <v>1378</v>
@@ -13069,28 +13072,28 @@
         <v>1380</v>
       </c>
       <c r="B888" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B889" t="s">
         <v>1382</v>
-      </c>
-      <c r="B889" t="s">
-        <v>1383</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B890" t="s">
         <v>1384</v>
-      </c>
-      <c r="B890" t="s">
-        <v>1385</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="B891" t="s">
         <v>1386</v>
@@ -13101,20 +13104,20 @@
         <v>1387</v>
       </c>
       <c r="B892" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B893" t="s">
         <v>1389</v>
-      </c>
-      <c r="B893" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B894" t="s">
         <v>1391</v>
@@ -13125,12 +13128,12 @@
         <v>1392</v>
       </c>
       <c r="B895" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B896" t="s">
         <v>1394</v>
@@ -13157,12 +13160,12 @@
         <v>1397</v>
       </c>
       <c r="B899" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="B900" t="s">
         <v>1399</v>
@@ -13181,28 +13184,28 @@
         <v>1401</v>
       </c>
       <c r="B902" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B903" t="s">
         <v>1403</v>
-      </c>
-      <c r="B903" t="s">
-        <v>1404</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B904" t="s">
         <v>1405</v>
-      </c>
-      <c r="B904" t="s">
-        <v>1406</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="B905" t="s">
         <v>1407</v>
@@ -13221,44 +13224,44 @@
         <v>1409</v>
       </c>
       <c r="B907" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B908" t="s">
         <v>1411</v>
-      </c>
-      <c r="B908" t="s">
-        <v>1412</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B909" t="s">
         <v>1413</v>
-      </c>
-      <c r="B909" t="s">
-        <v>1414</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B910" t="s">
         <v>1415</v>
-      </c>
-      <c r="B910" t="s">
-        <v>1416</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B911" t="s">
         <v>1417</v>
-      </c>
-      <c r="B911" t="s">
-        <v>1418</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="B912" t="s">
         <v>1419</v>
@@ -13317,36 +13320,36 @@
         <v>1426</v>
       </c>
       <c r="B919" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B920" t="s">
         <v>1428</v>
-      </c>
-      <c r="B920" t="s">
-        <v>1429</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B921" t="s">
         <v>1430</v>
-      </c>
-      <c r="B921" t="s">
-        <v>1431</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B922" t="s">
         <v>1432</v>
-      </c>
-      <c r="B922" t="s">
-        <v>1433</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B923" t="s">
         <v>1434</v>
@@ -13365,44 +13368,44 @@
         <v>1436</v>
       </c>
       <c r="B925" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B926" t="s">
         <v>1438</v>
-      </c>
-      <c r="B926" t="s">
-        <v>1439</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B927" t="s">
         <v>1440</v>
-      </c>
-      <c r="B927" t="s">
-        <v>1441</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B928" t="s">
         <v>1442</v>
-      </c>
-      <c r="B928" t="s">
-        <v>1443</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B929" t="s">
         <v>1444</v>
-      </c>
-      <c r="B929" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="B930" t="s">
         <v>1446</v>
@@ -13421,36 +13424,36 @@
         <v>1448</v>
       </c>
       <c r="B932" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B933" t="s">
         <v>1450</v>
-      </c>
-      <c r="B933" t="s">
-        <v>1451</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B934" t="s">
         <v>1452</v>
-      </c>
-      <c r="B934" t="s">
-        <v>1453</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B935" t="s">
         <v>1454</v>
-      </c>
-      <c r="B935" t="s">
-        <v>1455</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="B936" t="s">
         <v>1456</v>
@@ -13461,20 +13464,20 @@
         <v>1457</v>
       </c>
       <c r="B937" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B938" t="s">
         <v>1459</v>
-      </c>
-      <c r="B938" t="s">
-        <v>1460</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="B939" t="s">
         <v>1461</v>
@@ -13493,12 +13496,12 @@
         <v>1463</v>
       </c>
       <c r="B941" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="B942" t="s">
         <v>1465</v>
@@ -13509,28 +13512,28 @@
         <v>1466</v>
       </c>
       <c r="B943" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B944" t="s">
         <v>1468</v>
-      </c>
-      <c r="B944" t="s">
-        <v>1469</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B945" t="s">
         <v>1470</v>
-      </c>
-      <c r="B945" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="B946" t="s">
         <v>1472</v>
@@ -13541,20 +13544,20 @@
         <v>1473</v>
       </c>
       <c r="B947" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B948" t="s">
         <v>1475</v>
-      </c>
-      <c r="B948" t="s">
-        <v>1476</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="B949" t="s">
         <v>1477</v>
@@ -13589,12 +13592,12 @@
         <v>1481</v>
       </c>
       <c r="B953" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="B954" t="s">
         <v>1483</v>
@@ -13645,36 +13648,36 @@
         <v>1489</v>
       </c>
       <c r="B960" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B961" t="s">
         <v>1491</v>
-      </c>
-      <c r="B961" t="s">
-        <v>1492</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B962" t="s">
         <v>1493</v>
-      </c>
-      <c r="B962" t="s">
-        <v>1494</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B963" t="s">
         <v>1495</v>
-      </c>
-      <c r="B963" t="s">
-        <v>1496</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="B964" t="s">
         <v>1497</v>
@@ -13693,52 +13696,52 @@
         <v>1499</v>
       </c>
       <c r="B966" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B967" t="s">
         <v>1501</v>
-      </c>
-      <c r="B967" t="s">
-        <v>1502</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B968" t="s">
         <v>1503</v>
-      </c>
-      <c r="B968" t="s">
-        <v>1504</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B969" t="s">
         <v>1505</v>
-      </c>
-      <c r="B969" t="s">
-        <v>1506</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B970" t="s">
         <v>1507</v>
-      </c>
-      <c r="B970" t="s">
-        <v>1508</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B971" t="s">
         <v>1509</v>
-      </c>
-      <c r="B971" t="s">
-        <v>1510</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="B972" t="s">
         <v>1511</v>
@@ -13773,20 +13776,20 @@
         <v>1515</v>
       </c>
       <c r="B976" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B977" t="s">
         <v>1517</v>
-      </c>
-      <c r="B977" t="s">
-        <v>1518</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="B978" t="s">
         <v>1519</v>
@@ -13797,68 +13800,68 @@
         <v>1520</v>
       </c>
       <c r="B979" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B980" t="s">
         <v>1522</v>
-      </c>
-      <c r="B980" t="s">
-        <v>1523</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B981" t="s">
         <v>1524</v>
-      </c>
-      <c r="B981" t="s">
-        <v>1525</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B982" t="s">
         <v>1526</v>
-      </c>
-      <c r="B982" t="s">
-        <v>1527</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B983" t="s">
         <v>1528</v>
-      </c>
-      <c r="B983" t="s">
-        <v>1529</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B984" t="s">
         <v>1530</v>
-      </c>
-      <c r="B984" t="s">
-        <v>1531</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B985" t="s">
         <v>1532</v>
-      </c>
-      <c r="B985" t="s">
-        <v>1533</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B986" t="s">
         <v>1534</v>
-      </c>
-      <c r="B986" t="s">
-        <v>1535</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B987" t="s">
         <v>1536</v>
@@ -13877,20 +13880,20 @@
         <v>1538</v>
       </c>
       <c r="B989" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B990" t="s">
         <v>1540</v>
-      </c>
-      <c r="B990" t="s">
-        <v>1541</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="B991" t="s">
         <v>1542</v>
@@ -13917,44 +13920,44 @@
         <v>1545</v>
       </c>
       <c r="B994" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B995" t="s">
         <v>1547</v>
-      </c>
-      <c r="B995" t="s">
-        <v>1548</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B996" t="s">
         <v>1549</v>
-      </c>
-      <c r="B996" t="s">
-        <v>1550</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B997" t="s">
         <v>1551</v>
-      </c>
-      <c r="B997" t="s">
-        <v>1552</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B998" t="s">
         <v>1553</v>
-      </c>
-      <c r="B998" t="s">
-        <v>1554</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="B999" t="s">
         <v>1555</v>
@@ -13965,12 +13968,12 @@
         <v>1556</v>
       </c>
       <c r="B1000" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="B1001" t="s">
         <v>1558</v>
@@ -13981,20 +13984,20 @@
         <v>1559</v>
       </c>
       <c r="B1002" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B1003" t="s">
         <v>1561</v>
-      </c>
-      <c r="B1003" t="s">
-        <v>1562</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="B1004" t="s">
         <v>1563</v>
@@ -14021,12 +14024,12 @@
         <v>1566</v>
       </c>
       <c r="B1007" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="B1008" t="s">
         <v>1568</v>
@@ -14037,20 +14040,20 @@
         <v>1569</v>
       </c>
       <c r="B1009" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B1010" t="s">
         <v>1571</v>
-      </c>
-      <c r="B1010" t="s">
-        <v>1572</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="B1011" t="s">
         <v>1573</v>
@@ -14085,12 +14088,12 @@
         <v>1577</v>
       </c>
       <c r="B1015" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="B1016" t="s">
         <v>1579</v>
@@ -14125,20 +14128,20 @@
         <v>1583</v>
       </c>
       <c r="B1020" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B1021" t="s">
         <v>1585</v>
-      </c>
-      <c r="B1021" t="s">
-        <v>1586</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="B1022" t="s">
         <v>1587</v>
@@ -14173,20 +14176,20 @@
         <v>1591</v>
       </c>
       <c r="B1026" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B1027" t="s">
         <v>1593</v>
-      </c>
-      <c r="B1027" t="s">
-        <v>1594</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="B1028" t="s">
         <v>1595</v>
@@ -14197,28 +14200,28 @@
         <v>1596</v>
       </c>
       <c r="B1029" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B1030" t="s">
         <v>1598</v>
-      </c>
-      <c r="B1030" t="s">
-        <v>1599</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B1031" t="s">
         <v>1600</v>
-      </c>
-      <c r="B1031" t="s">
-        <v>1601</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="B1032" t="s">
         <v>1602</v>
@@ -14229,12 +14232,12 @@
         <v>1603</v>
       </c>
       <c r="B1033" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="B1034" t="s">
         <v>1605</v>
@@ -14253,12 +14256,12 @@
         <v>1607</v>
       </c>
       <c r="B1036" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="B1037" t="s">
         <v>1609</v>
@@ -14309,20 +14312,20 @@
         <v>1615</v>
       </c>
       <c r="B1043" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B1044" t="s">
         <v>1617</v>
-      </c>
-      <c r="B1044" t="s">
-        <v>1618</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="B1045" t="s">
         <v>1619</v>
@@ -14333,28 +14336,28 @@
         <v>1620</v>
       </c>
       <c r="B1046" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B1047" t="s">
         <v>1622</v>
-      </c>
-      <c r="B1047" t="s">
-        <v>1623</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B1048" t="s">
         <v>1624</v>
-      </c>
-      <c r="B1048" t="s">
-        <v>1625</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="B1049" t="s">
         <v>1626</v>
@@ -14373,28 +14376,28 @@
         <v>1628</v>
       </c>
       <c r="B1051" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B1052" t="s">
         <v>1630</v>
-      </c>
-      <c r="B1052" t="s">
-        <v>1631</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B1053" t="s">
         <v>1632</v>
-      </c>
-      <c r="B1053" t="s">
-        <v>1633</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="B1054" t="s">
         <v>1634</v>
@@ -14413,12 +14416,12 @@
         <v>1636</v>
       </c>
       <c r="B1056" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="B1057" t="s">
         <v>1638</v>
@@ -14437,180 +14440,180 @@
         <v>1640</v>
       </c>
       <c r="B1059" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B1060" t="s">
         <v>1642</v>
-      </c>
-      <c r="B1060" t="s">
-        <v>1643</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B1061" t="s">
         <v>1644</v>
-      </c>
-      <c r="B1061" t="s">
-        <v>1645</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B1062" t="s">
         <v>1646</v>
-      </c>
-      <c r="B1062" t="s">
-        <v>1647</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B1063" t="s">
         <v>1648</v>
-      </c>
-      <c r="B1063" t="s">
-        <v>1649</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B1064" t="s">
         <v>1650</v>
-      </c>
-      <c r="B1064" t="s">
-        <v>1651</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B1065" t="s">
         <v>1652</v>
-      </c>
-      <c r="B1065" t="s">
-        <v>1653</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B1066" t="s">
         <v>1654</v>
-      </c>
-      <c r="B1066" t="s">
-        <v>1655</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B1067" t="s">
         <v>1656</v>
-      </c>
-      <c r="B1067" t="s">
-        <v>1657</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B1068" t="s">
         <v>1658</v>
-      </c>
-      <c r="B1068" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B1069" t="s">
         <v>1660</v>
-      </c>
-      <c r="B1069" t="s">
-        <v>1661</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B1070" t="s">
         <v>1662</v>
-      </c>
-      <c r="B1070" t="s">
-        <v>1663</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B1071" t="s">
         <v>1664</v>
-      </c>
-      <c r="B1071" t="s">
-        <v>1665</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B1072" t="s">
         <v>1666</v>
-      </c>
-      <c r="B1072" t="s">
-        <v>1667</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B1073" t="s">
         <v>1668</v>
-      </c>
-      <c r="B1073" t="s">
-        <v>1669</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B1074" t="s">
         <v>1670</v>
-      </c>
-      <c r="B1074" t="s">
-        <v>1671</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B1075" t="s">
         <v>1672</v>
-      </c>
-      <c r="B1075" t="s">
-        <v>1673</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B1076" t="s">
         <v>1674</v>
-      </c>
-      <c r="B1076" t="s">
-        <v>1675</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B1077" t="s">
         <v>1676</v>
-      </c>
-      <c r="B1077" t="s">
-        <v>1677</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B1078" t="s">
         <v>1678</v>
-      </c>
-      <c r="B1078" t="s">
-        <v>1679</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B1079" t="s">
         <v>1680</v>
-      </c>
-      <c r="B1079" t="s">
-        <v>1681</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B1080" t="s">
         <v>1682</v>
-      </c>
-      <c r="B1080" t="s">
-        <v>1683</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="B1081" t="s">
         <v>1684</v>
@@ -14621,12 +14624,12 @@
         <v>1685</v>
       </c>
       <c r="B1082" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="B1083" t="s">
         <v>1687</v>
@@ -14661,12 +14664,12 @@
         <v>1691</v>
       </c>
       <c r="B1087" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="B1088" t="s">
         <v>1693</v>
@@ -14677,12 +14680,12 @@
         <v>1694</v>
       </c>
       <c r="B1089" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="B1090" t="s">
         <v>1696</v>
@@ -14709,12 +14712,12 @@
         <v>1699</v>
       </c>
       <c r="B1093" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="B1094" t="s">
         <v>1701</v>
@@ -14733,36 +14736,36 @@
         <v>1703</v>
       </c>
       <c r="B1096" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B1097" t="s">
         <v>1705</v>
-      </c>
-      <c r="B1097" t="s">
-        <v>1706</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B1098" t="s">
         <v>1707</v>
-      </c>
-      <c r="B1098" t="s">
-        <v>1708</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B1099" t="s">
         <v>1709</v>
-      </c>
-      <c r="B1099" t="s">
-        <v>1710</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="B1100" t="s">
         <v>1711</v>
@@ -14781,44 +14784,44 @@
         <v>1713</v>
       </c>
       <c r="B1102" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B1103" t="s">
         <v>1715</v>
-      </c>
-      <c r="B1103" t="s">
-        <v>1716</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B1104" t="s">
         <v>1717</v>
-      </c>
-      <c r="B1104" t="s">
-        <v>1718</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B1105" t="s">
         <v>1719</v>
-      </c>
-      <c r="B1105" t="s">
-        <v>1720</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B1106" t="s">
         <v>1721</v>
-      </c>
-      <c r="B1106" t="s">
-        <v>1722</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="B1107" t="s">
         <v>1723</v>
@@ -14829,28 +14832,28 @@
         <v>1724</v>
       </c>
       <c r="B1108" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B1109" t="s">
         <v>1726</v>
-      </c>
-      <c r="B1109" t="s">
-        <v>1727</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B1110" t="s">
         <v>1728</v>
-      </c>
-      <c r="B1110" t="s">
-        <v>1729</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="B1111" t="s">
         <v>1730</v>
@@ -14861,12 +14864,12 @@
         <v>1731</v>
       </c>
       <c r="B1112" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="B1113" t="s">
         <v>1733</v>
@@ -14885,12 +14888,12 @@
         <v>1735</v>
       </c>
       <c r="B1115" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="B1116" t="s">
         <v>1737</v>
@@ -14901,28 +14904,28 @@
         <v>1738</v>
       </c>
       <c r="B1117" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
+        <v>1739</v>
+      </c>
+      <c r="B1118" t="s">
         <v>1740</v>
-      </c>
-      <c r="B1118" t="s">
-        <v>1741</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B1119" t="s">
         <v>1742</v>
-      </c>
-      <c r="B1119" t="s">
-        <v>1743</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="B1120" t="s">
         <v>1744</v>
@@ -14941,156 +14944,156 @@
         <v>1746</v>
       </c>
       <c r="B1122" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1123" t="s">
         <v>1748</v>
-      </c>
-      <c r="B1123" t="s">
-        <v>1749</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
+        <v>1749</v>
+      </c>
+      <c r="B1124" t="s">
         <v>1750</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>1751</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
+        <v>1751</v>
+      </c>
+      <c r="B1125" t="s">
         <v>1752</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B1126" t="s">
         <v>1754</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>1755</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B1127" t="s">
         <v>1756</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>1757</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B1128" t="s">
         <v>1758</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>1759</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B1129" t="s">
         <v>1760</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>1761</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B1130" t="s">
         <v>1762</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>1763</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B1131" t="s">
         <v>1764</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>1765</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B1132" t="s">
         <v>1766</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>1767</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B1133" t="s">
         <v>1768</v>
-      </c>
-      <c r="B1133" t="s">
-        <v>1769</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B1134" t="s">
         <v>1770</v>
-      </c>
-      <c r="B1134" t="s">
-        <v>1771</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B1135" t="s">
         <v>1772</v>
-      </c>
-      <c r="B1135" t="s">
-        <v>1773</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B1136" t="s">
         <v>1774</v>
-      </c>
-      <c r="B1136" t="s">
-        <v>1775</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B1137" t="s">
         <v>1776</v>
-      </c>
-      <c r="B1137" t="s">
-        <v>1777</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
+        <v>1777</v>
+      </c>
+      <c r="B1138" t="s">
         <v>1778</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>1779</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B1139" t="s">
         <v>1780</v>
-      </c>
-      <c r="B1139" t="s">
-        <v>1781</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B1140" t="s">
         <v>1782</v>
-      </c>
-      <c r="B1140" t="s">
-        <v>1783</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="B1141" t="s">
         <v>1784</v>
@@ -15133,20 +15136,20 @@
         <v>1789</v>
       </c>
       <c r="B1146" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B1147" t="s">
         <v>1791</v>
-      </c>
-      <c r="B1147" t="s">
-        <v>1792</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="B1148" t="s">
         <v>1793</v>
@@ -15181,12 +15184,12 @@
         <v>1797</v>
       </c>
       <c r="B1152" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="B1153" t="s">
         <v>1799</v>
@@ -15197,28 +15200,28 @@
         <v>1800</v>
       </c>
       <c r="B1154" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B1155" t="s">
         <v>1802</v>
-      </c>
-      <c r="B1155" t="s">
-        <v>1803</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B1156" t="s">
         <v>1804</v>
-      </c>
-      <c r="B1156" t="s">
-        <v>1805</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="B1157" t="s">
         <v>1806</v>
@@ -15229,12 +15232,12 @@
         <v>1807</v>
       </c>
       <c r="B1158" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="B1159" t="s">
         <v>1809</v>
@@ -15245,12 +15248,12 @@
         <v>1810</v>
       </c>
       <c r="B1160" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="B1161" t="s">
         <v>1812</v>
@@ -15261,36 +15264,36 @@
         <v>1813</v>
       </c>
       <c r="B1162" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B1163" t="s">
         <v>1815</v>
-      </c>
-      <c r="B1163" t="s">
-        <v>1816</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B1164" t="s">
         <v>1817</v>
-      </c>
-      <c r="B1164" t="s">
-        <v>1818</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B1165" t="s">
         <v>1819</v>
-      </c>
-      <c r="B1165" t="s">
-        <v>1820</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="B1166" t="s">
         <v>1821</v>
@@ -15333,12 +15336,12 @@
         <v>1826</v>
       </c>
       <c r="B1171" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="B1172" t="s">
         <v>1828</v>
@@ -15365,12 +15368,12 @@
         <v>1831</v>
       </c>
       <c r="B1175" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="B1176" t="s">
         <v>1833</v>
@@ -15405,20 +15408,20 @@
         <v>1837</v>
       </c>
       <c r="B1180" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B1181" t="s">
         <v>1839</v>
-      </c>
-      <c r="B1181" t="s">
-        <v>1840</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="B1182" t="s">
         <v>1841</v>
@@ -15429,12 +15432,12 @@
         <v>1842</v>
       </c>
       <c r="B1183" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="B1184" t="s">
         <v>1844</v>
@@ -15453,28 +15456,28 @@
         <v>1846</v>
       </c>
       <c r="B1186" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B1187" t="s">
         <v>1848</v>
-      </c>
-      <c r="B1187" t="s">
-        <v>1849</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B1188" t="s">
         <v>1850</v>
-      </c>
-      <c r="B1188" t="s">
-        <v>1851</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="B1189" t="s">
         <v>1852</v>
@@ -15485,7 +15488,7 @@
         <v>1853</v>
       </c>
       <c r="B1190" t="s">
-        <v>718</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
@@ -15493,7 +15496,7 @@
         <v>1854</v>
       </c>
       <c r="B1191" t="s">
-        <v>1854</v>
+        <v>719</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
@@ -15509,12 +15512,12 @@
         <v>1856</v>
       </c>
       <c r="B1193" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="B1194" t="s">
         <v>1858</v>
@@ -15533,27 +15536,35 @@
         <v>1860</v>
       </c>
       <c r="B1196" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="1197" spans="1:2">
       <c r="A1197" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B1197" t="s">
         <v>1862</v>
-      </c>
-      <c r="B1197" t="s">
-        <v>1863</v>
       </c>
     </row>
     <row r="1198" spans="1:2">
       <c r="A1198" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B1198" t="s">
         <v>1864</v>
       </c>
-      <c r="B1198" t="s">
+    </row>
+    <row r="1199" spans="1:2">
+      <c r="A1199" t="s">
         <v>1865</v>
       </c>
+      <c r="B1199" t="s">
+        <v>1866</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1198"/>
+  <autoFilter ref="A1:B1199"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/es/headTags.xlsx
+++ b/lang/es/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1199</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1200</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1867">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1869">
   <si>
     <t>en</t>
   </si>
@@ -4445,6 +4445,12 @@
   </si>
   <si>
     <t>Sombras de Mordor</t>
+  </si>
+  <si>
+    <t>Shark</t>
+  </si>
+  <si>
+    <t>Tiburón</t>
   </si>
   <si>
     <t>Sheep</t>
@@ -5964,7 +5970,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1199"/>
+  <dimension ref="A1:B1200"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13568,36 +13574,36 @@
         <v>1478</v>
       </c>
       <c r="B950" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="B951" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B952" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B953" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B954" t="s">
         <v>1483</v>
@@ -13608,52 +13614,52 @@
         <v>1484</v>
       </c>
       <c r="B955" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B956" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B957" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B958" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B959" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B960" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B961" t="s">
         <v>1491</v>
@@ -13688,20 +13694,20 @@
         <v>1498</v>
       </c>
       <c r="B965" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B966" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B967" t="s">
         <v>1501</v>
@@ -13752,36 +13758,36 @@
         <v>1512</v>
       </c>
       <c r="B973" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B974" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="B975" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B976" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B977" t="s">
         <v>1517</v>
@@ -13800,12 +13806,12 @@
         <v>1520</v>
       </c>
       <c r="B979" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B980" t="s">
         <v>1522</v>
@@ -13872,20 +13878,20 @@
         <v>1537</v>
       </c>
       <c r="B988" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B989" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B990" t="s">
         <v>1540</v>
@@ -13904,28 +13910,28 @@
         <v>1543</v>
       </c>
       <c r="B992" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B993" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B994" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B995" t="s">
         <v>1547</v>
@@ -13968,12 +13974,12 @@
         <v>1556</v>
       </c>
       <c r="B1000" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B1001" t="s">
         <v>1558</v>
@@ -13984,12 +13990,12 @@
         <v>1559</v>
       </c>
       <c r="B1002" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="B1003" t="s">
         <v>1561</v>
@@ -14008,28 +14014,28 @@
         <v>1564</v>
       </c>
       <c r="B1005" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B1006" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B1007" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B1008" t="s">
         <v>1568</v>
@@ -14040,12 +14046,12 @@
         <v>1569</v>
       </c>
       <c r="B1009" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B1010" t="s">
         <v>1571</v>
@@ -14064,36 +14070,36 @@
         <v>1574</v>
       </c>
       <c r="B1012" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B1013" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="B1014" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B1015" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B1016" t="s">
         <v>1579</v>
@@ -14104,36 +14110,36 @@
         <v>1580</v>
       </c>
       <c r="B1017" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B1018" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B1019" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B1020" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B1021" t="s">
         <v>1585</v>
@@ -14152,36 +14158,36 @@
         <v>1588</v>
       </c>
       <c r="B1023" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B1024" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B1025" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B1026" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B1027" t="s">
         <v>1593</v>
@@ -14200,12 +14206,12 @@
         <v>1596</v>
       </c>
       <c r="B1029" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B1030" t="s">
         <v>1598</v>
@@ -14232,12 +14238,12 @@
         <v>1603</v>
       </c>
       <c r="B1033" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B1034" t="s">
         <v>1605</v>
@@ -14248,20 +14254,20 @@
         <v>1606</v>
       </c>
       <c r="B1035" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B1036" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B1037" t="s">
         <v>1609</v>
@@ -14272,52 +14278,52 @@
         <v>1610</v>
       </c>
       <c r="B1038" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B1039" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B1040" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B1041" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B1042" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B1043" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B1044" t="s">
         <v>1617</v>
@@ -14336,12 +14342,12 @@
         <v>1620</v>
       </c>
       <c r="B1046" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B1047" t="s">
         <v>1622</v>
@@ -14368,20 +14374,20 @@
         <v>1627</v>
       </c>
       <c r="B1050" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B1051" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B1052" t="s">
         <v>1630</v>
@@ -14408,20 +14414,20 @@
         <v>1635</v>
       </c>
       <c r="B1055" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="B1056" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B1057" t="s">
         <v>1638</v>
@@ -14432,20 +14438,20 @@
         <v>1639</v>
       </c>
       <c r="B1058" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B1059" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B1060" t="s">
         <v>1642</v>
@@ -14624,12 +14630,12 @@
         <v>1685</v>
       </c>
       <c r="B1082" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B1083" t="s">
         <v>1687</v>
@@ -14640,36 +14646,36 @@
         <v>1688</v>
       </c>
       <c r="B1084" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B1085" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B1086" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B1087" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B1088" t="s">
         <v>1693</v>
@@ -14680,12 +14686,12 @@
         <v>1694</v>
       </c>
       <c r="B1089" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B1090" t="s">
         <v>1696</v>
@@ -14696,28 +14702,28 @@
         <v>1697</v>
       </c>
       <c r="B1091" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B1092" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B1093" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B1094" t="s">
         <v>1701</v>
@@ -14728,20 +14734,20 @@
         <v>1702</v>
       </c>
       <c r="B1095" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B1096" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B1097" t="s">
         <v>1705</v>
@@ -14776,20 +14782,20 @@
         <v>1712</v>
       </c>
       <c r="B1101" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="B1102" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="B1103" t="s">
         <v>1715</v>
@@ -14832,12 +14838,12 @@
         <v>1724</v>
       </c>
       <c r="B1108" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B1109" t="s">
         <v>1726</v>
@@ -14864,12 +14870,12 @@
         <v>1731</v>
       </c>
       <c r="B1112" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="B1113" t="s">
         <v>1733</v>
@@ -14880,20 +14886,20 @@
         <v>1734</v>
       </c>
       <c r="B1114" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="B1115" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="B1116" t="s">
         <v>1737</v>
@@ -14904,12 +14910,12 @@
         <v>1738</v>
       </c>
       <c r="B1117" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="B1118" t="s">
         <v>1740</v>
@@ -14936,20 +14942,20 @@
         <v>1745</v>
       </c>
       <c r="B1121" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="B1122" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="B1123" t="s">
         <v>1748</v>
@@ -15104,44 +15110,44 @@
         <v>1785</v>
       </c>
       <c r="B1142" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B1143" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="B1144" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="B1145" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="B1146" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="B1147" t="s">
         <v>1791</v>
@@ -15160,36 +15166,36 @@
         <v>1794</v>
       </c>
       <c r="B1149" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="B1150" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B1151" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="B1152" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="B1153" t="s">
         <v>1799</v>
@@ -15200,12 +15206,12 @@
         <v>1800</v>
       </c>
       <c r="B1154" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="B1155" t="s">
         <v>1802</v>
@@ -15232,12 +15238,12 @@
         <v>1807</v>
       </c>
       <c r="B1158" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1159" t="s">
         <v>1809</v>
@@ -15248,12 +15254,12 @@
         <v>1810</v>
       </c>
       <c r="B1160" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B1161" t="s">
         <v>1812</v>
@@ -15264,12 +15270,12 @@
         <v>1813</v>
       </c>
       <c r="B1162" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="B1163" t="s">
         <v>1815</v>
@@ -15304,44 +15310,44 @@
         <v>1822</v>
       </c>
       <c r="B1167" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="B1168" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1169" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="B1170" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="B1171" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="B1172" t="s">
         <v>1828</v>
@@ -15352,28 +15358,28 @@
         <v>1829</v>
       </c>
       <c r="B1173" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="B1174" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="B1175" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="B1176" t="s">
         <v>1833</v>
@@ -15384,36 +15390,36 @@
         <v>1834</v>
       </c>
       <c r="B1177" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1178" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B1179" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="B1180" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="B1181" t="s">
         <v>1839</v>
@@ -15432,12 +15438,12 @@
         <v>1842</v>
       </c>
       <c r="B1183" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="B1184" t="s">
         <v>1844</v>
@@ -15448,20 +15454,20 @@
         <v>1845</v>
       </c>
       <c r="B1185" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="B1186" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="B1187" t="s">
         <v>1848</v>
@@ -15488,36 +15494,36 @@
         <v>1853</v>
       </c>
       <c r="B1190" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B1191" t="s">
-        <v>719</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="B1192" t="s">
-        <v>1855</v>
+        <v>719</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B1193" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="B1194" t="s">
         <v>1858</v>
@@ -15528,20 +15534,20 @@
         <v>1859</v>
       </c>
       <c r="B1195" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="1196" spans="1:2">
       <c r="A1196" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="B1196" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="1197" spans="1:2">
       <c r="A1197" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="B1197" t="s">
         <v>1862</v>
@@ -15563,8 +15569,16 @@
         <v>1866</v>
       </c>
     </row>
+    <row r="1200" spans="1:2">
+      <c r="A1200" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B1200" t="s">
+        <v>1868</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1199"/>
+  <autoFilter ref="A1:B1200"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/es/headTags.xlsx
+++ b/lang/es/headTags.xlsx
@@ -1501,6 +1501,12 @@
     <t>Fairy Tales</t>
   </si>
   <si>
+    <t>Fall Drop</t>
+  </si>
+  <si>
+    <t>Caída</t>
+  </si>
+  <si>
     <t>Fall Guys</t>
   </si>
   <si>
@@ -5570,12 +5576,6 @@
   </si>
   <si>
     <t>Etiqueta Hypixel (Mutaciones)</t>
-  </si>
-  <si>
-    <t>Fall Drop</t>
-  </si>
-  <si>
-    <t>Caída</t>
   </si>
   <si>
     <t>Summer Drop 2025</t>
@@ -8574,36 +8574,36 @@
         <v>494</v>
       </c>
       <c r="B325" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="326" spans="1:2">
       <c r="A326" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B326" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B327" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B328" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B329" t="s">
         <v>499</v>
@@ -8614,28 +8614,28 @@
         <v>500</v>
       </c>
       <c r="B330" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B331" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="332" spans="1:2">
       <c r="A332" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B332" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B333" t="s">
         <v>504</v>
@@ -8646,12 +8646,12 @@
         <v>505</v>
       </c>
       <c r="B334" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B335" t="s">
         <v>507</v>
@@ -8702,12 +8702,12 @@
         <v>518</v>
       </c>
       <c r="B341" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="342" spans="1:2">
       <c r="A342" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B342" t="s">
         <v>520</v>
@@ -8862,12 +8862,12 @@
         <v>557</v>
       </c>
       <c r="B361" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="362" spans="1:2">
       <c r="A362" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B362" t="s">
         <v>559</v>
@@ -8894,12 +8894,12 @@
         <v>564</v>
       </c>
       <c r="B365" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="366" spans="1:2">
       <c r="A366" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B366" t="s">
         <v>566</v>
@@ -8950,15 +8950,15 @@
         <v>577</v>
       </c>
       <c r="B372" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="373" spans="1:2">
       <c r="A373" t="s">
+        <v>579</v>
+      </c>
+      <c r="B373" t="s">
         <v>578</v>
-      </c>
-      <c r="B373" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -8974,20 +8974,20 @@
         <v>582</v>
       </c>
       <c r="B375" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="376" spans="1:2">
       <c r="A376" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B376" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="377" spans="1:2">
       <c r="A377" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B377" t="s">
         <v>585</v>
@@ -8998,12 +8998,12 @@
         <v>586</v>
       </c>
       <c r="B378" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="379" spans="1:2">
       <c r="A379" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B379" t="s">
         <v>588</v>
@@ -9030,31 +9030,31 @@
         <v>593</v>
       </c>
       <c r="B382" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
     </row>
     <row r="383" spans="1:2">
       <c r="A383" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B383" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="384" spans="1:2">
       <c r="A384" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B384" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="385" spans="1:2">
       <c r="A385" t="s">
+        <v>597</v>
+      </c>
+      <c r="B385" t="s">
         <v>596</v>
-      </c>
-      <c r="B385" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -9070,12 +9070,12 @@
         <v>600</v>
       </c>
       <c r="B387" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="388" spans="1:2">
       <c r="A388" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B388" t="s">
         <v>602</v>
@@ -9086,12 +9086,12 @@
         <v>603</v>
       </c>
       <c r="B389" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="390" spans="1:2">
       <c r="A390" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B390" t="s">
         <v>605</v>
@@ -9110,116 +9110,116 @@
         <v>608</v>
       </c>
       <c r="B392" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="393" spans="1:2">
       <c r="A393" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B393" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="394" spans="1:2">
       <c r="A394" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B394" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="395" spans="1:2">
       <c r="A395" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B395" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="396" spans="1:2">
       <c r="A396" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B396" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="397" spans="1:2">
       <c r="A397" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B397" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="398" spans="1:2">
       <c r="A398" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B398" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="399" spans="1:2">
       <c r="A399" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B399" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="400" spans="1:2">
       <c r="A400" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B400" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="401" spans="1:2">
       <c r="A401" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B401" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="402" spans="1:2">
       <c r="A402" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B402" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="403" spans="1:2">
       <c r="A403" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B403" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="404" spans="1:2">
       <c r="A404" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B404" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="405" spans="1:2">
       <c r="A405" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B405" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="406" spans="1:2">
       <c r="A406" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B406" t="s">
         <v>623</v>
@@ -9243,10 +9243,10 @@
     </row>
     <row r="409" spans="1:2">
       <c r="A409" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B409" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -9278,20 +9278,20 @@
         <v>635</v>
       </c>
       <c r="B413" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="414" spans="1:2">
       <c r="A414" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B414" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="415" spans="1:2">
       <c r="A415" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B415" t="s">
         <v>638</v>
@@ -9302,20 +9302,20 @@
         <v>639</v>
       </c>
       <c r="B416" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="417" spans="1:2">
       <c r="A417" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B417" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="418" spans="1:2">
       <c r="A418" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B418" t="s">
         <v>642</v>
@@ -9326,20 +9326,20 @@
         <v>643</v>
       </c>
       <c r="B419" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="420" spans="1:2">
       <c r="A420" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B420" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="421" spans="1:2">
       <c r="A421" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B421" t="s">
         <v>646</v>
@@ -9438,36 +9438,36 @@
         <v>669</v>
       </c>
       <c r="B433" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="434" spans="1:2">
       <c r="A434" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B434" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="435" spans="1:2">
       <c r="A435" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B435" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="436" spans="1:2">
       <c r="A436" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B436" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B437" t="s">
         <v>674</v>
@@ -9478,12 +9478,12 @@
         <v>675</v>
       </c>
       <c r="B438" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="439" spans="1:2">
       <c r="A439" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B439" t="s">
         <v>677</v>
@@ -9558,12 +9558,12 @@
         <v>694</v>
       </c>
       <c r="B448" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="449" spans="1:2">
       <c r="A449" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B449" t="s">
         <v>696</v>
@@ -9614,12 +9614,12 @@
         <v>707</v>
       </c>
       <c r="B455" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="456" spans="1:2">
       <c r="A456" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B456" t="s">
         <v>709</v>
@@ -9694,36 +9694,36 @@
         <v>726</v>
       </c>
       <c r="B465" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="466" spans="1:2">
       <c r="A466" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B466" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="467" spans="1:2">
       <c r="A467" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B467" t="s">
-        <v>488</v>
+        <v>729</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B468" t="s">
-        <v>729</v>
+        <v>488</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B469" t="s">
         <v>731</v>
@@ -9742,12 +9742,12 @@
         <v>734</v>
       </c>
       <c r="B471" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B472" t="s">
         <v>736</v>
@@ -9758,36 +9758,36 @@
         <v>737</v>
       </c>
       <c r="B473" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="474" spans="1:2">
       <c r="A474" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B474" t="s">
-        <v>488</v>
+        <v>739</v>
       </c>
     </row>
     <row r="475" spans="1:2">
       <c r="A475" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B475" t="s">
-        <v>739</v>
+        <v>488</v>
       </c>
     </row>
     <row r="476" spans="1:2">
       <c r="A476" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B476" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B477" t="s">
         <v>742</v>
@@ -9798,12 +9798,12 @@
         <v>743</v>
       </c>
       <c r="B478" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B479" t="s">
         <v>745</v>
@@ -9814,20 +9814,20 @@
         <v>746</v>
       </c>
       <c r="B480" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="481" spans="1:2">
       <c r="A481" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B481" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B482" t="s">
         <v>749</v>
@@ -9838,12 +9838,12 @@
         <v>750</v>
       </c>
       <c r="B483" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B484" t="s">
         <v>752</v>
@@ -9862,44 +9862,44 @@
         <v>755</v>
       </c>
       <c r="B486" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B487" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B488" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="489" spans="1:2">
       <c r="A489" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B489" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="490" spans="1:2">
       <c r="A490" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B490" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B491" t="s">
         <v>761</v>
@@ -10062,20 +10062,20 @@
         <v>800</v>
       </c>
       <c r="B511" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="512" spans="1:2">
       <c r="A512" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B512" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="A513" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B513" t="s">
         <v>803</v>
@@ -10086,12 +10086,12 @@
         <v>804</v>
       </c>
       <c r="B514" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="A515" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B515" t="s">
         <v>806</v>
@@ -10102,12 +10102,12 @@
         <v>807</v>
       </c>
       <c r="B516" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="517" spans="1:2">
       <c r="A517" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B517" t="s">
         <v>809</v>
@@ -10126,28 +10126,28 @@
         <v>812</v>
       </c>
       <c r="B519" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="520" spans="1:2">
       <c r="A520" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B520" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="521" spans="1:2">
       <c r="A521" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B521" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="522" spans="1:2">
       <c r="A522" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B522" t="s">
         <v>816</v>
@@ -10238,12 +10238,12 @@
         <v>837</v>
       </c>
       <c r="B533" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="534" spans="1:2">
       <c r="A534" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B534" t="s">
         <v>839</v>
@@ -10262,28 +10262,28 @@
         <v>842</v>
       </c>
       <c r="B536" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="537" spans="1:2">
       <c r="A537" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B537" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="538" spans="1:2">
       <c r="A538" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B538" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B539" t="s">
         <v>846</v>
@@ -10294,52 +10294,52 @@
         <v>847</v>
       </c>
       <c r="B540" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B541" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="542" spans="1:2">
       <c r="A542" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B542" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B543" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B544" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B545" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B546" t="s">
         <v>854</v>
@@ -10350,12 +10350,12 @@
         <v>855</v>
       </c>
       <c r="B547" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="548" spans="1:2">
       <c r="A548" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B548" t="s">
         <v>857</v>
@@ -10374,60 +10374,60 @@
         <v>860</v>
       </c>
       <c r="B550" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B551" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="552" spans="1:2">
       <c r="A552" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B552" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B553" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B554" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B555" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B556" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B557" t="s">
         <v>868</v>
@@ -10486,28 +10486,28 @@
         <v>881</v>
       </c>
       <c r="B564" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="565" spans="1:2">
       <c r="A565" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B565" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="566" spans="1:2">
       <c r="A566" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B566" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B567" t="s">
         <v>885</v>
@@ -10526,12 +10526,12 @@
         <v>888</v>
       </c>
       <c r="B569" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="570" spans="1:2">
       <c r="A570" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B570" t="s">
         <v>890</v>
@@ -10550,12 +10550,12 @@
         <v>893</v>
       </c>
       <c r="B572" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="573" spans="1:2">
       <c r="A573" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B573" t="s">
         <v>895</v>
@@ -10582,52 +10582,52 @@
         <v>900</v>
       </c>
       <c r="B576" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="577" spans="1:2">
       <c r="A577" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B577" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B578" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B579" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B580" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B581" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B582" t="s">
         <v>907</v>
@@ -10646,12 +10646,12 @@
         <v>910</v>
       </c>
       <c r="B584" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B585" t="s">
         <v>912</v>
@@ -10686,12 +10686,12 @@
         <v>919</v>
       </c>
       <c r="B589" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="590" spans="1:2">
       <c r="A590" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B590" t="s">
         <v>921</v>
@@ -10710,12 +10710,12 @@
         <v>924</v>
       </c>
       <c r="B592" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="593" spans="1:2">
       <c r="A593" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B593" t="s">
         <v>926</v>
@@ -10766,12 +10766,12 @@
         <v>937</v>
       </c>
       <c r="B599" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B600" t="s">
         <v>939</v>
@@ -10782,20 +10782,20 @@
         <v>940</v>
       </c>
       <c r="B601" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B602" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B603" t="s">
         <v>943</v>
@@ -10838,20 +10838,20 @@
         <v>952</v>
       </c>
       <c r="B608" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="609" spans="1:2">
       <c r="A609" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B609" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B610" t="s">
         <v>955</v>
@@ -10862,20 +10862,20 @@
         <v>956</v>
       </c>
       <c r="B611" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B612" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B613" t="s">
         <v>959</v>
@@ -10886,12 +10886,12 @@
         <v>960</v>
       </c>
       <c r="B614" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B615" t="s">
         <v>962</v>
@@ -10910,20 +10910,20 @@
         <v>965</v>
       </c>
       <c r="B617" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="618" spans="1:2">
       <c r="A618" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B618" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="619" spans="1:2">
       <c r="A619" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B619" t="s">
         <v>968</v>
@@ -10942,20 +10942,20 @@
         <v>971</v>
       </c>
       <c r="B621" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B622" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B623" t="s">
         <v>974</v>
@@ -10990,20 +10990,20 @@
         <v>981</v>
       </c>
       <c r="B627" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B628" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B629" t="s">
         <v>984</v>
@@ -11014,20 +11014,20 @@
         <v>985</v>
       </c>
       <c r="B630" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B631" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B632" t="s">
         <v>988</v>
@@ -11054,92 +11054,92 @@
         <v>993</v>
       </c>
       <c r="B635" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B636" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B637" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B638" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B639" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B640" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B641" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B642" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B643" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B644" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B645" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B646" t="s">
         <v>1005</v>
@@ -11150,36 +11150,36 @@
         <v>1006</v>
       </c>
       <c r="B647" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B648" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="649" spans="1:2">
       <c r="A649" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B649" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B650" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B651" t="s">
         <v>1011</v>
@@ -11214,12 +11214,12 @@
         <v>1018</v>
       </c>
       <c r="B655" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="656" spans="1:2">
       <c r="A656" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B656" t="s">
         <v>1020</v>
@@ -11230,12 +11230,12 @@
         <v>1021</v>
       </c>
       <c r="B657" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B658" t="s">
         <v>1023</v>
@@ -11246,12 +11246,12 @@
         <v>1024</v>
       </c>
       <c r="B659" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="660" spans="1:2">
       <c r="A660" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B660" t="s">
         <v>1026</v>
@@ -11270,12 +11270,12 @@
         <v>1029</v>
       </c>
       <c r="B662" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="663" spans="1:2">
       <c r="A663" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B663" t="s">
         <v>1031</v>
@@ -11334,36 +11334,36 @@
         <v>1044</v>
       </c>
       <c r="B670" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="671" spans="1:2">
       <c r="A671" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B671" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="672" spans="1:2">
       <c r="A672" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B672" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="673" spans="1:2">
       <c r="A673" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B673" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B674" t="s">
         <v>1049</v>
@@ -11382,28 +11382,28 @@
         <v>1052</v>
       </c>
       <c r="B676" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B677" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="678" spans="1:2">
       <c r="A678" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B678" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="679" spans="1:2">
       <c r="A679" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B679" t="s">
         <v>1056</v>
@@ -11414,44 +11414,44 @@
         <v>1057</v>
       </c>
       <c r="B680" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="681" spans="1:2">
       <c r="A681" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B681" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="682" spans="1:2">
       <c r="A682" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B682" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="683" spans="1:2">
       <c r="A683" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B683" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="684" spans="1:2">
       <c r="A684" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B684" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B685" t="s">
         <v>1063</v>
@@ -11470,28 +11470,28 @@
         <v>1066</v>
       </c>
       <c r="B687" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="688" spans="1:2">
       <c r="A688" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B688" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="689" spans="1:2">
       <c r="A689" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B689" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B690" t="s">
         <v>1070</v>
@@ -11574,12 +11574,12 @@
         <v>1089</v>
       </c>
       <c r="B700" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="701" spans="1:2">
       <c r="A701" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B701" t="s">
         <v>1091</v>
@@ -11598,12 +11598,12 @@
         <v>1094</v>
       </c>
       <c r="B703" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B704" t="s">
         <v>1096</v>
@@ -11622,12 +11622,12 @@
         <v>1099</v>
       </c>
       <c r="B706" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="707" spans="1:2">
       <c r="A707" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B707" t="s">
         <v>1101</v>
@@ -11638,20 +11638,20 @@
         <v>1102</v>
       </c>
       <c r="B708" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B709" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B710" t="s">
         <v>1105</v>
@@ -11662,60 +11662,60 @@
         <v>1106</v>
       </c>
       <c r="B711" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B712" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B713" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B714" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B715" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B716" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B717" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B718" t="s">
         <v>1114</v>
@@ -11726,12 +11726,12 @@
         <v>1115</v>
       </c>
       <c r="B719" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B720" t="s">
         <v>1117</v>
@@ -11742,20 +11742,20 @@
         <v>1118</v>
       </c>
       <c r="B721" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="722" spans="1:2">
       <c r="A722" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B722" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="723" spans="1:2">
       <c r="A723" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B723" t="s">
         <v>1121</v>
@@ -11846,12 +11846,12 @@
         <v>1142</v>
       </c>
       <c r="B734" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="735" spans="1:2">
       <c r="A735" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B735" t="s">
         <v>1144</v>
@@ -11870,12 +11870,12 @@
         <v>1147</v>
       </c>
       <c r="B737" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="738" spans="1:2">
       <c r="A738" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B738" t="s">
         <v>1149</v>
@@ -11894,28 +11894,28 @@
         <v>1152</v>
       </c>
       <c r="B740" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="741" spans="1:2">
       <c r="A741" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B741" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="742" spans="1:2">
       <c r="A742" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B742" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B743" t="s">
         <v>1156</v>
@@ -11926,44 +11926,44 @@
         <v>1157</v>
       </c>
       <c r="B744" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="745" spans="1:2">
       <c r="A745" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B745" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="746" spans="1:2">
       <c r="A746" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B746" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B747" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B748" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B749" t="s">
         <v>1163</v>
@@ -11982,36 +11982,36 @@
         <v>1166</v>
       </c>
       <c r="B751" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="752" spans="1:2">
       <c r="A752" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B752" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="753" spans="1:2">
       <c r="A753" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B753" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="754" spans="1:2">
       <c r="A754" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B754" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B755" t="s">
         <v>1171</v>
@@ -12070,12 +12070,12 @@
         <v>1184</v>
       </c>
       <c r="B762" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="763" spans="1:2">
       <c r="A763" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B763" t="s">
         <v>1186</v>
@@ -12102,12 +12102,12 @@
         <v>1191</v>
       </c>
       <c r="B766" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="767" spans="1:2">
       <c r="A767" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B767" t="s">
         <v>1193</v>
@@ -12118,20 +12118,20 @@
         <v>1194</v>
       </c>
       <c r="B768" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="769" spans="1:2">
       <c r="A769" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B769" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B770" t="s">
         <v>1197</v>
@@ -12171,15 +12171,15 @@
     </row>
     <row r="775" spans="1:2">
       <c r="A775" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B775" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="776" spans="1:2">
       <c r="A776" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B776" t="s">
         <v>1207</v>
@@ -12206,28 +12206,28 @@
         <v>1212</v>
       </c>
       <c r="B779" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="780" spans="1:2">
       <c r="A780" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B780" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="781" spans="1:2">
       <c r="A781" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B781" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="782" spans="1:2">
       <c r="A782" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B782" t="s">
         <v>1216</v>
@@ -12238,20 +12238,20 @@
         <v>1217</v>
       </c>
       <c r="B783" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B784" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="785" spans="1:2">
       <c r="A785" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B785" t="s">
         <v>1220</v>
@@ -12286,28 +12286,28 @@
         <v>1227</v>
       </c>
       <c r="B789" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="790" spans="1:2">
       <c r="A790" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B790" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="791" spans="1:2">
       <c r="A791" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B791" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B792" t="s">
         <v>1231</v>
@@ -12326,12 +12326,12 @@
         <v>1234</v>
       </c>
       <c r="B794" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B795" t="s">
         <v>1236</v>
@@ -12342,60 +12342,60 @@
         <v>1237</v>
       </c>
       <c r="B796" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B797" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B798" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B799" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B800" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B801" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B802" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B803" t="s">
         <v>1245</v>
@@ -12406,12 +12406,12 @@
         <v>1246</v>
       </c>
       <c r="B804" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B805" t="s">
         <v>1248</v>
@@ -12478,36 +12478,36 @@
         <v>1263</v>
       </c>
       <c r="B813" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="814" spans="1:2">
       <c r="A814" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B814" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B815" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B816" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B817" t="s">
         <v>1268</v>
@@ -12542,12 +12542,12 @@
         <v>1275</v>
       </c>
       <c r="B821" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="822" spans="1:2">
       <c r="A822" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B822" t="s">
         <v>1277</v>
@@ -12582,12 +12582,12 @@
         <v>1284</v>
       </c>
       <c r="B826" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="B827" t="s">
         <v>1286</v>
@@ -12598,12 +12598,12 @@
         <v>1287</v>
       </c>
       <c r="B828" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B829" t="s">
         <v>1289</v>
@@ -12614,12 +12614,12 @@
         <v>1290</v>
       </c>
       <c r="B830" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B831" t="s">
         <v>1292</v>
@@ -12630,12 +12630,12 @@
         <v>1293</v>
       </c>
       <c r="B832" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B833" t="s">
         <v>1295</v>
@@ -12646,23 +12646,23 @@
         <v>1296</v>
       </c>
       <c r="B834" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B835" t="s">
-        <v>717</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B836" t="s">
-        <v>1299</v>
+        <v>719</v>
       </c>
     </row>
     <row r="837" spans="1:2">
@@ -12678,36 +12678,36 @@
         <v>1302</v>
       </c>
       <c r="B838" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B839" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B840" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B841" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B842" t="s">
         <v>1307</v>
@@ -12742,12 +12742,12 @@
         <v>1314</v>
       </c>
       <c r="B846" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B847" t="s">
         <v>1316</v>
@@ -12766,36 +12766,36 @@
         <v>1319</v>
       </c>
       <c r="B849" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B850" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B851" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B852" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B853" t="s">
         <v>1324</v>
@@ -12902,28 +12902,28 @@
         <v>1349</v>
       </c>
       <c r="B866" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B867" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B868" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B869" t="s">
         <v>1353</v>
@@ -12934,36 +12934,36 @@
         <v>1354</v>
       </c>
       <c r="B870" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B871" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B872" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B873" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B874" t="s">
         <v>1359</v>
@@ -12974,28 +12974,28 @@
         <v>1360</v>
       </c>
       <c r="B875" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B876" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B877" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B878" t="s">
         <v>1364</v>
@@ -13014,12 +13014,12 @@
         <v>1367</v>
       </c>
       <c r="B880" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B881" t="s">
         <v>1369</v>
@@ -13054,15 +13054,15 @@
         <v>1376</v>
       </c>
       <c r="B885" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B886" t="s">
         <v>1377</v>
-      </c>
-      <c r="B886" t="s">
-        <v>1378</v>
       </c>
     </row>
     <row r="887" spans="1:2">
@@ -13070,20 +13070,20 @@
         <v>1379</v>
       </c>
       <c r="B887" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B888" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="B889" t="s">
         <v>1382</v>
@@ -13110,12 +13110,12 @@
         <v>1387</v>
       </c>
       <c r="B892" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B893" t="s">
         <v>1389</v>
@@ -13134,12 +13134,12 @@
         <v>1392</v>
       </c>
       <c r="B895" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="B896" t="s">
         <v>1394</v>
@@ -13150,28 +13150,28 @@
         <v>1395</v>
       </c>
       <c r="B897" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B898" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B899" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="B900" t="s">
         <v>1399</v>
@@ -13182,20 +13182,20 @@
         <v>1400</v>
       </c>
       <c r="B901" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B902" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B903" t="s">
         <v>1403</v>
@@ -13222,20 +13222,20 @@
         <v>1408</v>
       </c>
       <c r="B906" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="B907" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B908" t="s">
         <v>1411</v>
@@ -13278,60 +13278,60 @@
         <v>1420</v>
       </c>
       <c r="B913" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B914" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B915" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B916" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B917" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="B918" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B919" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B920" t="s">
         <v>1428</v>
@@ -13366,20 +13366,20 @@
         <v>1435</v>
       </c>
       <c r="B924" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B925" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="B926" t="s">
         <v>1438</v>
@@ -13422,20 +13422,20 @@
         <v>1447</v>
       </c>
       <c r="B931" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="932" spans="1:2">
       <c r="A932" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="B932" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="B933" t="s">
         <v>1450</v>
@@ -13470,12 +13470,12 @@
         <v>1457</v>
       </c>
       <c r="B937" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B938" t="s">
         <v>1459</v>
@@ -13494,20 +13494,20 @@
         <v>1462</v>
       </c>
       <c r="B940" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B941" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="B942" t="s">
         <v>1465</v>
@@ -13518,12 +13518,12 @@
         <v>1466</v>
       </c>
       <c r="B943" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B944" t="s">
         <v>1468</v>
@@ -13550,12 +13550,12 @@
         <v>1473</v>
       </c>
       <c r="B947" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B948" t="s">
         <v>1475</v>
@@ -13582,36 +13582,36 @@
         <v>1480</v>
       </c>
       <c r="B951" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B952" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B953" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B954" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B955" t="s">
         <v>1485</v>
@@ -13622,52 +13622,52 @@
         <v>1486</v>
       </c>
       <c r="B956" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B957" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B958" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B959" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B960" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="B961" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B962" t="s">
         <v>1493</v>
@@ -13702,20 +13702,20 @@
         <v>1500</v>
       </c>
       <c r="B966" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B967" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B968" t="s">
         <v>1503</v>
@@ -13766,36 +13766,36 @@
         <v>1514</v>
       </c>
       <c r="B974" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B975" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B976" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B977" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="B978" t="s">
         <v>1519</v>
@@ -13814,12 +13814,12 @@
         <v>1522</v>
       </c>
       <c r="B980" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B981" t="s">
         <v>1524</v>
@@ -13886,20 +13886,20 @@
         <v>1539</v>
       </c>
       <c r="B989" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B990" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B991" t="s">
         <v>1542</v>
@@ -13918,28 +13918,28 @@
         <v>1545</v>
       </c>
       <c r="B993" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B994" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B995" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B996" t="s">
         <v>1549</v>
@@ -13982,12 +13982,12 @@
         <v>1558</v>
       </c>
       <c r="B1001" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B1002" t="s">
         <v>1560</v>
@@ -13998,12 +13998,12 @@
         <v>1561</v>
       </c>
       <c r="B1003" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B1004" t="s">
         <v>1563</v>
@@ -14022,28 +14022,28 @@
         <v>1566</v>
       </c>
       <c r="B1006" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B1007" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B1008" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B1009" t="s">
         <v>1570</v>
@@ -14054,12 +14054,12 @@
         <v>1571</v>
       </c>
       <c r="B1010" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B1011" t="s">
         <v>1573</v>
@@ -14078,36 +14078,36 @@
         <v>1576</v>
       </c>
       <c r="B1013" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B1014" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B1015" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="B1016" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B1017" t="s">
         <v>1581</v>
@@ -14118,36 +14118,36 @@
         <v>1582</v>
       </c>
       <c r="B1018" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B1019" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B1020" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B1021" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B1022" t="s">
         <v>1587</v>
@@ -14166,36 +14166,36 @@
         <v>1590</v>
       </c>
       <c r="B1024" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B1025" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B1026" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B1027" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B1028" t="s">
         <v>1595</v>
@@ -14214,12 +14214,12 @@
         <v>1598</v>
       </c>
       <c r="B1030" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B1031" t="s">
         <v>1600</v>
@@ -14246,12 +14246,12 @@
         <v>1605</v>
       </c>
       <c r="B1034" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="B1035" t="s">
         <v>1607</v>
@@ -14262,20 +14262,20 @@
         <v>1608</v>
       </c>
       <c r="B1036" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B1037" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B1038" t="s">
         <v>1611</v>
@@ -14286,52 +14286,52 @@
         <v>1612</v>
       </c>
       <c r="B1039" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B1040" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B1041" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B1042" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B1043" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B1044" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B1045" t="s">
         <v>1619</v>
@@ -14350,12 +14350,12 @@
         <v>1622</v>
       </c>
       <c r="B1047" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B1048" t="s">
         <v>1624</v>
@@ -14382,20 +14382,20 @@
         <v>1629</v>
       </c>
       <c r="B1051" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B1052" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="B1053" t="s">
         <v>1632</v>
@@ -14422,20 +14422,20 @@
         <v>1637</v>
       </c>
       <c r="B1056" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="B1057" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B1058" t="s">
         <v>1640</v>
@@ -14446,20 +14446,20 @@
         <v>1641</v>
       </c>
       <c r="B1059" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="B1060" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1061" t="s">
         <v>1644</v>
@@ -14638,12 +14638,12 @@
         <v>1687</v>
       </c>
       <c r="B1083" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B1084" t="s">
         <v>1689</v>
@@ -14654,36 +14654,36 @@
         <v>1690</v>
       </c>
       <c r="B1085" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B1086" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B1087" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B1088" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B1089" t="s">
         <v>1695</v>
@@ -14694,12 +14694,12 @@
         <v>1696</v>
       </c>
       <c r="B1090" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B1091" t="s">
         <v>1698</v>
@@ -14710,28 +14710,28 @@
         <v>1699</v>
       </c>
       <c r="B1092" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B1093" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B1094" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B1095" t="s">
         <v>1703</v>
@@ -14742,20 +14742,20 @@
         <v>1704</v>
       </c>
       <c r="B1096" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B1097" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B1098" t="s">
         <v>1707</v>
@@ -14790,20 +14790,20 @@
         <v>1714</v>
       </c>
       <c r="B1102" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B1103" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="B1104" t="s">
         <v>1717</v>
@@ -14846,12 +14846,12 @@
         <v>1726</v>
       </c>
       <c r="B1109" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="B1110" t="s">
         <v>1728</v>
@@ -14878,12 +14878,12 @@
         <v>1733</v>
       </c>
       <c r="B1113" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="B1114" t="s">
         <v>1735</v>
@@ -14894,20 +14894,20 @@
         <v>1736</v>
       </c>
       <c r="B1115" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="B1116" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="B1117" t="s">
         <v>1739</v>
@@ -14918,12 +14918,12 @@
         <v>1740</v>
       </c>
       <c r="B1118" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="B1119" t="s">
         <v>1742</v>
@@ -14950,20 +14950,20 @@
         <v>1747</v>
       </c>
       <c r="B1122" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="B1123" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B1124" t="s">
         <v>1750</v>
@@ -15118,44 +15118,44 @@
         <v>1787</v>
       </c>
       <c r="B1143" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="B1144" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="B1145" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="B1146" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="B1147" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B1148" t="s">
         <v>1793</v>
@@ -15174,36 +15174,36 @@
         <v>1796</v>
       </c>
       <c r="B1150" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="B1151" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="B1152" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="B1153" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="B1154" t="s">
         <v>1801</v>
@@ -15214,12 +15214,12 @@
         <v>1802</v>
       </c>
       <c r="B1155" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="B1156" t="s">
         <v>1804</v>
@@ -15246,12 +15246,12 @@
         <v>1809</v>
       </c>
       <c r="B1159" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="B1160" t="s">
         <v>1811</v>
@@ -15262,12 +15262,12 @@
         <v>1812</v>
       </c>
       <c r="B1161" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="B1162" t="s">
         <v>1814</v>
@@ -15278,12 +15278,12 @@
         <v>1815</v>
       </c>
       <c r="B1163" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="B1164" t="s">
         <v>1817</v>
@@ -15318,44 +15318,44 @@
         <v>1824</v>
       </c>
       <c r="B1168" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="B1169" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="B1170" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="B1171" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B1172" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B1173" t="s">
         <v>1830</v>
@@ -15366,28 +15366,28 @@
         <v>1831</v>
       </c>
       <c r="B1174" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="B1175" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="B1176" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B1177" t="s">
         <v>1835</v>
@@ -15398,36 +15398,36 @@
         <v>1836</v>
       </c>
       <c r="B1178" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="B1179" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="B1180" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="B1181" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="B1182" t="s">
         <v>1841</v>
@@ -15446,12 +15446,12 @@
         <v>1844</v>
       </c>
       <c r="B1184" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="B1185" t="s">
         <v>1846</v>
@@ -15462,20 +15462,20 @@
         <v>1847</v>
       </c>
       <c r="B1186" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="B1187" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="B1188" t="s">
         <v>1850</v>
@@ -15510,7 +15510,7 @@
         <v>1856</v>
       </c>
       <c r="B1192" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="1193" spans="1:2">

--- a/lang/es/headTags.xlsx
+++ b/lang/es/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1201</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1871">
   <si>
     <t>en</t>
   </si>
@@ -4112,6 +4112,12 @@
   </si>
   <si>
     <t>Predator</t>
+  </si>
+  <si>
+    <t>Prehistoric Creature</t>
+  </si>
+  <si>
+    <t>Criatura prehistórica</t>
   </si>
   <si>
     <t>Present</t>
@@ -5970,7 +5976,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1200"/>
+  <dimension ref="A1:B1201"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13022,12 +13028,12 @@
         <v>1369</v>
       </c>
       <c r="B881" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B882" t="s">
         <v>1371</v>
@@ -13062,15 +13068,15 @@
         <v>1378</v>
       </c>
       <c r="B886" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B887" t="s">
         <v>1379</v>
-      </c>
-      <c r="B887" t="s">
-        <v>1380</v>
       </c>
     </row>
     <row r="888" spans="1:2">
@@ -13078,20 +13084,20 @@
         <v>1381</v>
       </c>
       <c r="B888" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B889" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="B890" t="s">
         <v>1384</v>
@@ -13118,12 +13124,12 @@
         <v>1389</v>
       </c>
       <c r="B893" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="B894" t="s">
         <v>1391</v>
@@ -13142,12 +13148,12 @@
         <v>1394</v>
       </c>
       <c r="B896" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="B897" t="s">
         <v>1396</v>
@@ -13158,28 +13164,28 @@
         <v>1397</v>
       </c>
       <c r="B898" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="B899" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="B900" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="B901" t="s">
         <v>1401</v>
@@ -13190,20 +13196,20 @@
         <v>1402</v>
       </c>
       <c r="B902" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B903" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B904" t="s">
         <v>1405</v>
@@ -13230,20 +13236,20 @@
         <v>1410</v>
       </c>
       <c r="B907" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="B908" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B909" t="s">
         <v>1413</v>
@@ -13286,60 +13292,60 @@
         <v>1422</v>
       </c>
       <c r="B914" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B915" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B916" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="B917" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B918" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B919" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B920" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B921" t="s">
         <v>1430</v>
@@ -13374,20 +13380,20 @@
         <v>1437</v>
       </c>
       <c r="B925" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B926" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B927" t="s">
         <v>1440</v>
@@ -13430,20 +13436,20 @@
         <v>1449</v>
       </c>
       <c r="B932" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B933" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B934" t="s">
         <v>1452</v>
@@ -13478,12 +13484,12 @@
         <v>1459</v>
       </c>
       <c r="B938" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B939" t="s">
         <v>1461</v>
@@ -13502,20 +13508,20 @@
         <v>1464</v>
       </c>
       <c r="B941" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="B942" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B943" t="s">
         <v>1467</v>
@@ -13526,12 +13532,12 @@
         <v>1468</v>
       </c>
       <c r="B944" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B945" t="s">
         <v>1470</v>
@@ -13558,12 +13564,12 @@
         <v>1475</v>
       </c>
       <c r="B948" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B949" t="s">
         <v>1477</v>
@@ -13590,36 +13596,36 @@
         <v>1482</v>
       </c>
       <c r="B952" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B953" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B954" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B955" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B956" t="s">
         <v>1487</v>
@@ -13630,52 +13636,52 @@
         <v>1488</v>
       </c>
       <c r="B957" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B958" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B959" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="B960" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B961" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="B962" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B963" t="s">
         <v>1495</v>
@@ -13710,20 +13716,20 @@
         <v>1502</v>
       </c>
       <c r="B967" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B968" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B969" t="s">
         <v>1505</v>
@@ -13774,36 +13780,36 @@
         <v>1516</v>
       </c>
       <c r="B975" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B976" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="B977" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B978" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B979" t="s">
         <v>1521</v>
@@ -13822,12 +13828,12 @@
         <v>1524</v>
       </c>
       <c r="B981" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B982" t="s">
         <v>1526</v>
@@ -13894,20 +13900,20 @@
         <v>1541</v>
       </c>
       <c r="B990" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B991" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B992" t="s">
         <v>1544</v>
@@ -13926,28 +13932,28 @@
         <v>1547</v>
       </c>
       <c r="B994" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B995" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B996" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B997" t="s">
         <v>1551</v>
@@ -13990,12 +13996,12 @@
         <v>1560</v>
       </c>
       <c r="B1002" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B1003" t="s">
         <v>1562</v>
@@ -14006,12 +14012,12 @@
         <v>1563</v>
       </c>
       <c r="B1004" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B1005" t="s">
         <v>1565</v>
@@ -14030,28 +14036,28 @@
         <v>1568</v>
       </c>
       <c r="B1007" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B1008" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B1009" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B1010" t="s">
         <v>1572</v>
@@ -14062,12 +14068,12 @@
         <v>1573</v>
       </c>
       <c r="B1011" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B1012" t="s">
         <v>1575</v>
@@ -14086,36 +14092,36 @@
         <v>1578</v>
       </c>
       <c r="B1014" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="B1015" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B1016" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B1017" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B1018" t="s">
         <v>1583</v>
@@ -14126,36 +14132,36 @@
         <v>1584</v>
       </c>
       <c r="B1019" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B1020" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B1021" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B1022" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B1023" t="s">
         <v>1589</v>
@@ -14174,36 +14180,36 @@
         <v>1592</v>
       </c>
       <c r="B1025" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B1026" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B1027" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="B1028" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B1029" t="s">
         <v>1597</v>
@@ -14222,12 +14228,12 @@
         <v>1600</v>
       </c>
       <c r="B1031" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B1032" t="s">
         <v>1602</v>
@@ -14254,12 +14260,12 @@
         <v>1607</v>
       </c>
       <c r="B1035" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B1036" t="s">
         <v>1609</v>
@@ -14270,20 +14276,20 @@
         <v>1610</v>
       </c>
       <c r="B1037" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B1038" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B1039" t="s">
         <v>1613</v>
@@ -14294,52 +14300,52 @@
         <v>1614</v>
       </c>
       <c r="B1040" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B1041" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B1042" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B1043" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B1044" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B1045" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="B1046" t="s">
         <v>1621</v>
@@ -14358,12 +14364,12 @@
         <v>1624</v>
       </c>
       <c r="B1048" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B1049" t="s">
         <v>1626</v>
@@ -14390,20 +14396,20 @@
         <v>1631</v>
       </c>
       <c r="B1052" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B1053" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B1054" t="s">
         <v>1634</v>
@@ -14430,20 +14436,20 @@
         <v>1639</v>
       </c>
       <c r="B1057" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B1058" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B1059" t="s">
         <v>1642</v>
@@ -14454,20 +14460,20 @@
         <v>1643</v>
       </c>
       <c r="B1060" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="B1061" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B1062" t="s">
         <v>1646</v>
@@ -14646,12 +14652,12 @@
         <v>1689</v>
       </c>
       <c r="B1084" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B1085" t="s">
         <v>1691</v>
@@ -14662,36 +14668,36 @@
         <v>1692</v>
       </c>
       <c r="B1086" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B1087" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B1088" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B1089" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B1090" t="s">
         <v>1697</v>
@@ -14702,12 +14708,12 @@
         <v>1698</v>
       </c>
       <c r="B1091" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B1092" t="s">
         <v>1700</v>
@@ -14718,28 +14724,28 @@
         <v>1701</v>
       </c>
       <c r="B1093" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B1094" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B1095" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B1096" t="s">
         <v>1705</v>
@@ -14750,20 +14756,20 @@
         <v>1706</v>
       </c>
       <c r="B1097" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1098" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B1099" t="s">
         <v>1709</v>
@@ -14798,20 +14804,20 @@
         <v>1716</v>
       </c>
       <c r="B1103" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B1104" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="B1105" t="s">
         <v>1719</v>
@@ -14854,12 +14860,12 @@
         <v>1728</v>
       </c>
       <c r="B1110" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="B1111" t="s">
         <v>1730</v>
@@ -14886,12 +14892,12 @@
         <v>1735</v>
       </c>
       <c r="B1114" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="B1115" t="s">
         <v>1737</v>
@@ -14902,20 +14908,20 @@
         <v>1738</v>
       </c>
       <c r="B1116" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="B1117" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="B1118" t="s">
         <v>1741</v>
@@ -14926,12 +14932,12 @@
         <v>1742</v>
       </c>
       <c r="B1119" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="B1120" t="s">
         <v>1744</v>
@@ -14958,20 +14964,20 @@
         <v>1749</v>
       </c>
       <c r="B1123" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="B1124" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="B1125" t="s">
         <v>1752</v>
@@ -15126,44 +15132,44 @@
         <v>1789</v>
       </c>
       <c r="B1144" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="B1145" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="B1146" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B1147" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="B1148" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B1149" t="s">
         <v>1795</v>
@@ -15182,36 +15188,36 @@
         <v>1798</v>
       </c>
       <c r="B1151" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="B1152" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="B1153" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="B1154" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="B1155" t="s">
         <v>1803</v>
@@ -15222,12 +15228,12 @@
         <v>1804</v>
       </c>
       <c r="B1156" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="B1157" t="s">
         <v>1806</v>
@@ -15254,12 +15260,12 @@
         <v>1811</v>
       </c>
       <c r="B1160" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="B1161" t="s">
         <v>1813</v>
@@ -15270,12 +15276,12 @@
         <v>1814</v>
       </c>
       <c r="B1162" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B1163" t="s">
         <v>1816</v>
@@ -15286,12 +15292,12 @@
         <v>1817</v>
       </c>
       <c r="B1164" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B1165" t="s">
         <v>1819</v>
@@ -15326,44 +15332,44 @@
         <v>1826</v>
       </c>
       <c r="B1169" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="B1170" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B1171" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B1172" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="B1173" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="B1174" t="s">
         <v>1832</v>
@@ -15374,28 +15380,28 @@
         <v>1833</v>
       </c>
       <c r="B1175" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B1176" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1177" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B1178" t="s">
         <v>1837</v>
@@ -15406,36 +15412,36 @@
         <v>1838</v>
       </c>
       <c r="B1179" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="B1180" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="B1181" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="B1182" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="B1183" t="s">
         <v>1843</v>
@@ -15454,12 +15460,12 @@
         <v>1846</v>
       </c>
       <c r="B1185" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="B1186" t="s">
         <v>1848</v>
@@ -15470,20 +15476,20 @@
         <v>1849</v>
       </c>
       <c r="B1187" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="B1188" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="B1189" t="s">
         <v>1852</v>
@@ -15502,36 +15508,36 @@
         <v>1855</v>
       </c>
       <c r="B1191" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B1192" t="s">
-        <v>721</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="B1193" t="s">
-        <v>1857</v>
+        <v>721</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B1194" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
       <c r="A1195" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="B1195" t="s">
         <v>1860</v>
@@ -15542,20 +15548,20 @@
         <v>1861</v>
       </c>
       <c r="B1196" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="1197" spans="1:2">
       <c r="A1197" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1197" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="1198" spans="1:2">
       <c r="A1198" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1198" t="s">
         <v>1864</v>
@@ -15577,8 +15583,16 @@
         <v>1868</v>
       </c>
     </row>
+    <row r="1201" spans="1:2">
+      <c r="A1201" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B1201" t="s">
+        <v>1870</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1200"/>
+  <autoFilter ref="A1:B1201"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/es/headTags.xlsx
+++ b/lang/es/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1202</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1871">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1873">
   <si>
     <t>en</t>
   </si>
@@ -320,6 +320,12 @@
   </si>
   <si>
     <t>Regreso al Futuro</t>
+  </si>
+  <si>
+    <t>Backrooms (Movie)</t>
+  </si>
+  <si>
+    <t>Backrooms (película)</t>
   </si>
   <si>
     <t>Bag</t>
@@ -5976,7 +5982,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1201"/>
+  <dimension ref="A1:B1202"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -6532,12 +6538,12 @@
         <v>105</v>
       </c>
       <c r="B69" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B70" t="s">
         <v>107</v>
@@ -6556,20 +6562,20 @@
         <v>110</v>
       </c>
       <c r="B72" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B73" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B74" t="s">
         <v>113</v>
@@ -6580,12 +6586,12 @@
         <v>114</v>
       </c>
       <c r="B75" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B76" t="s">
         <v>116</v>
@@ -6620,12 +6626,12 @@
         <v>123</v>
       </c>
       <c r="B80" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B81" t="s">
         <v>125</v>
@@ -6636,12 +6642,12 @@
         <v>126</v>
       </c>
       <c r="B82" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B83" t="s">
         <v>128</v>
@@ -6668,12 +6674,12 @@
         <v>133</v>
       </c>
       <c r="B86" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B87" t="s">
         <v>135</v>
@@ -6708,20 +6714,20 @@
         <v>142</v>
       </c>
       <c r="B91" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B92" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B93" t="s">
         <v>145</v>
@@ -6732,92 +6738,92 @@
         <v>146</v>
       </c>
       <c r="B94" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B95" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B96" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B97" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B98" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B99" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B100" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B101" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B102" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B103" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B104" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B105" t="s">
         <v>158</v>
@@ -6828,28 +6834,28 @@
         <v>159</v>
       </c>
       <c r="B106" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B107" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B108" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B109" t="s">
         <v>163</v>
@@ -6860,36 +6866,36 @@
         <v>164</v>
       </c>
       <c r="B110" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B111" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B112" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B113" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B114" t="s">
         <v>169</v>
@@ -6964,36 +6970,36 @@
         <v>186</v>
       </c>
       <c r="B123" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B124" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B125" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B126" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B127" t="s">
         <v>191</v>
@@ -7004,12 +7010,12 @@
         <v>192</v>
       </c>
       <c r="B128" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B129" t="s">
         <v>194</v>
@@ -7020,44 +7026,44 @@
         <v>195</v>
       </c>
       <c r="B130" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B131" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B132" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B133" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B134" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B135" t="s">
         <v>201</v>
@@ -7076,20 +7082,20 @@
         <v>204</v>
       </c>
       <c r="B137" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B138" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B139" t="s">
         <v>207</v>
@@ -7108,12 +7114,12 @@
         <v>210</v>
       </c>
       <c r="B141" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B142" t="s">
         <v>212</v>
@@ -7172,44 +7178,44 @@
         <v>225</v>
       </c>
       <c r="B149" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B150" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B151" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B152" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B153" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B154" t="s">
         <v>231</v>
@@ -7228,20 +7234,20 @@
         <v>234</v>
       </c>
       <c r="B156" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B157" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B158" t="s">
         <v>237</v>
@@ -7260,12 +7266,12 @@
         <v>240</v>
       </c>
       <c r="B160" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B161" t="s">
         <v>242</v>
@@ -7356,20 +7362,20 @@
         <v>263</v>
       </c>
       <c r="B172" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B173" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B174" t="s">
         <v>266</v>
@@ -7396,20 +7402,20 @@
         <v>271</v>
       </c>
       <c r="B177" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B178" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B179" t="s">
         <v>274</v>
@@ -7428,20 +7434,20 @@
         <v>277</v>
       </c>
       <c r="B181" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B182" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B183" t="s">
         <v>280</v>
@@ -7452,12 +7458,12 @@
         <v>281</v>
       </c>
       <c r="B184" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B185" t="s">
         <v>282</v>
@@ -7465,15 +7471,15 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B186" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B187" t="s">
         <v>285</v>
@@ -7484,12 +7490,12 @@
         <v>286</v>
       </c>
       <c r="B188" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B189" t="s">
         <v>288</v>
@@ -7580,12 +7586,12 @@
         <v>309</v>
       </c>
       <c r="B200" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B201" t="s">
         <v>311</v>
@@ -7620,28 +7626,28 @@
         <v>318</v>
       </c>
       <c r="B205" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="A206" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B206" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B207" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B208" t="s">
         <v>322</v>
@@ -7652,28 +7658,28 @@
         <v>323</v>
       </c>
       <c r="B209" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B210" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B211" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B212" t="s">
         <v>327</v>
@@ -7684,12 +7690,12 @@
         <v>328</v>
       </c>
       <c r="B213" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B214" t="s">
         <v>330</v>
@@ -7708,12 +7714,12 @@
         <v>333</v>
       </c>
       <c r="B216" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B217" t="s">
         <v>335</v>
@@ -7732,52 +7738,52 @@
         <v>338</v>
       </c>
       <c r="B219" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B220" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="221" spans="1:2">
       <c r="A221" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B221" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B222" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B223" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B224" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B225" t="s">
         <v>345</v>
@@ -7788,36 +7794,36 @@
         <v>346</v>
       </c>
       <c r="B226" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B227" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B228" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B229" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B230" t="s">
         <v>351</v>
@@ -7836,52 +7842,52 @@
         <v>354</v>
       </c>
       <c r="B232" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B233" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B234" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B235" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="236" spans="1:2">
       <c r="A236" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B236" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="237" spans="1:2">
       <c r="A237" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B237" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B238" t="s">
         <v>361</v>
@@ -7924,12 +7930,12 @@
         <v>370</v>
       </c>
       <c r="B243" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B244" t="s">
         <v>372</v>
@@ -7940,12 +7946,12 @@
         <v>373</v>
       </c>
       <c r="B245" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B246" t="s">
         <v>375</v>
@@ -7996,12 +8002,12 @@
         <v>386</v>
       </c>
       <c r="B252" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B253" t="s">
         <v>388</v>
@@ -8012,20 +8018,20 @@
         <v>389</v>
       </c>
       <c r="B254" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B255" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B256" t="s">
         <v>392</v>
@@ -8036,36 +8042,36 @@
         <v>393</v>
       </c>
       <c r="B257" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B258" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B259" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B260" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="261" spans="1:2">
       <c r="A261" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B261" t="s">
         <v>398</v>
@@ -8108,20 +8114,20 @@
         <v>407</v>
       </c>
       <c r="B266" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="267" spans="1:2">
       <c r="A267" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B267" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B268" t="s">
         <v>410</v>
@@ -8140,28 +8146,28 @@
         <v>413</v>
       </c>
       <c r="B270" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B271" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B272" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B273" t="s">
         <v>417</v>
@@ -8172,44 +8178,44 @@
         <v>418</v>
       </c>
       <c r="B274" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B275" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="276" spans="1:2">
       <c r="A276" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B276" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="277" spans="1:2">
       <c r="A277" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B277" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B278" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="279" spans="1:2">
       <c r="A279" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B279" t="s">
         <v>424</v>
@@ -8236,36 +8242,36 @@
         <v>429</v>
       </c>
       <c r="B282" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="283" spans="1:2">
       <c r="A283" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B283" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="284" spans="1:2">
       <c r="A284" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B284" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B285" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B286" t="s">
         <v>434</v>
@@ -8276,12 +8282,12 @@
         <v>435</v>
       </c>
       <c r="B287" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B288" t="s">
         <v>437</v>
@@ -8292,12 +8298,12 @@
         <v>438</v>
       </c>
       <c r="B289" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="290" spans="1:2">
       <c r="A290" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B290" t="s">
         <v>440</v>
@@ -8308,12 +8314,12 @@
         <v>441</v>
       </c>
       <c r="B291" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B292" t="s">
         <v>443</v>
@@ -8324,15 +8330,15 @@
         <v>444</v>
       </c>
       <c r="B293" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="294" spans="1:2">
       <c r="A294" t="s">
+        <v>446</v>
+      </c>
+      <c r="B294" t="s">
         <v>445</v>
-      </c>
-      <c r="B294" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -8348,20 +8354,20 @@
         <v>449</v>
       </c>
       <c r="B296" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B297" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B298" t="s">
         <v>452</v>
@@ -8396,12 +8402,12 @@
         <v>459</v>
       </c>
       <c r="B302" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B303" t="s">
         <v>461</v>
@@ -8412,12 +8418,12 @@
         <v>462</v>
       </c>
       <c r="B304" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="305" spans="1:2">
       <c r="A305" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B305" t="s">
         <v>464</v>
@@ -8460,20 +8466,20 @@
         <v>473</v>
       </c>
       <c r="B310" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="311" spans="1:2">
       <c r="A311" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B311" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B312" t="s">
         <v>476</v>
@@ -8492,20 +8498,20 @@
         <v>479</v>
       </c>
       <c r="B314" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="315" spans="1:2">
       <c r="A315" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B315" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B316" t="s">
         <v>482</v>
@@ -8540,44 +8546,44 @@
         <v>489</v>
       </c>
       <c r="B320" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B321" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B322" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="323" spans="1:2">
       <c r="A323" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B323" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B324" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="325" spans="1:2">
       <c r="A325" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B325" t="s">
         <v>495</v>
@@ -8588,36 +8594,36 @@
         <v>496</v>
       </c>
       <c r="B326" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B327" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B328" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B329" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="330" spans="1:2">
       <c r="A330" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B330" t="s">
         <v>501</v>
@@ -8628,28 +8634,28 @@
         <v>502</v>
       </c>
       <c r="B331" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="332" spans="1:2">
       <c r="A332" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B332" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B333" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B334" t="s">
         <v>506</v>
@@ -8660,12 +8666,12 @@
         <v>507</v>
       </c>
       <c r="B335" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="336" spans="1:2">
       <c r="A336" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B336" t="s">
         <v>509</v>
@@ -8716,12 +8722,12 @@
         <v>520</v>
       </c>
       <c r="B342" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B343" t="s">
         <v>522</v>
@@ -8876,12 +8882,12 @@
         <v>559</v>
       </c>
       <c r="B362" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="363" spans="1:2">
       <c r="A363" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B363" t="s">
         <v>561</v>
@@ -8908,12 +8914,12 @@
         <v>566</v>
       </c>
       <c r="B366" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B367" t="s">
         <v>568</v>
@@ -8964,15 +8970,15 @@
         <v>579</v>
       </c>
       <c r="B373" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="374" spans="1:2">
       <c r="A374" t="s">
+        <v>581</v>
+      </c>
+      <c r="B374" t="s">
         <v>580</v>
-      </c>
-      <c r="B374" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -8988,20 +8994,20 @@
         <v>584</v>
       </c>
       <c r="B376" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="377" spans="1:2">
       <c r="A377" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B377" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="378" spans="1:2">
       <c r="A378" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B378" t="s">
         <v>587</v>
@@ -9012,12 +9018,12 @@
         <v>588</v>
       </c>
       <c r="B379" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="380" spans="1:2">
       <c r="A380" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B380" t="s">
         <v>590</v>
@@ -9044,31 +9050,31 @@
         <v>595</v>
       </c>
       <c r="B383" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
     </row>
     <row r="384" spans="1:2">
       <c r="A384" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B384" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="385" spans="1:2">
       <c r="A385" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B385" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="386" spans="1:2">
       <c r="A386" t="s">
+        <v>599</v>
+      </c>
+      <c r="B386" t="s">
         <v>598</v>
-      </c>
-      <c r="B386" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -9084,12 +9090,12 @@
         <v>602</v>
       </c>
       <c r="B388" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="389" spans="1:2">
       <c r="A389" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B389" t="s">
         <v>604</v>
@@ -9100,12 +9106,12 @@
         <v>605</v>
       </c>
       <c r="B390" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="391" spans="1:2">
       <c r="A391" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B391" t="s">
         <v>607</v>
@@ -9124,116 +9130,116 @@
         <v>610</v>
       </c>
       <c r="B393" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="394" spans="1:2">
       <c r="A394" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B394" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="395" spans="1:2">
       <c r="A395" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B395" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="396" spans="1:2">
       <c r="A396" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B396" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="397" spans="1:2">
       <c r="A397" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B397" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="398" spans="1:2">
       <c r="A398" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B398" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="399" spans="1:2">
       <c r="A399" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B399" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="400" spans="1:2">
       <c r="A400" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B400" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="401" spans="1:2">
       <c r="A401" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B401" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="402" spans="1:2">
       <c r="A402" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B402" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="403" spans="1:2">
       <c r="A403" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B403" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="404" spans="1:2">
       <c r="A404" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B404" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="405" spans="1:2">
       <c r="A405" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B405" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="406" spans="1:2">
       <c r="A406" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B406" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="407" spans="1:2">
       <c r="A407" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B407" t="s">
         <v>625</v>
@@ -9257,10 +9263,10 @@
     </row>
     <row r="410" spans="1:2">
       <c r="A410" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B410" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -9292,20 +9298,20 @@
         <v>637</v>
       </c>
       <c r="B414" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="415" spans="1:2">
       <c r="A415" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B415" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="416" spans="1:2">
       <c r="A416" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B416" t="s">
         <v>640</v>
@@ -9316,20 +9322,20 @@
         <v>641</v>
       </c>
       <c r="B417" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="418" spans="1:2">
       <c r="A418" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B418" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="419" spans="1:2">
       <c r="A419" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B419" t="s">
         <v>644</v>
@@ -9340,20 +9346,20 @@
         <v>645</v>
       </c>
       <c r="B420" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="421" spans="1:2">
       <c r="A421" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B421" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="422" spans="1:2">
       <c r="A422" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B422" t="s">
         <v>648</v>
@@ -9452,36 +9458,36 @@
         <v>671</v>
       </c>
       <c r="B434" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="435" spans="1:2">
       <c r="A435" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B435" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="436" spans="1:2">
       <c r="A436" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B436" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B437" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B438" t="s">
         <v>676</v>
@@ -9492,12 +9498,12 @@
         <v>677</v>
       </c>
       <c r="B439" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="440" spans="1:2">
       <c r="A440" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B440" t="s">
         <v>679</v>
@@ -9572,12 +9578,12 @@
         <v>696</v>
       </c>
       <c r="B449" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="450" spans="1:2">
       <c r="A450" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B450" t="s">
         <v>698</v>
@@ -9628,12 +9634,12 @@
         <v>709</v>
       </c>
       <c r="B456" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="457" spans="1:2">
       <c r="A457" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B457" t="s">
         <v>711</v>
@@ -9708,36 +9714,36 @@
         <v>728</v>
       </c>
       <c r="B466" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="467" spans="1:2">
       <c r="A467" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B467" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B468" t="s">
-        <v>488</v>
+        <v>731</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B469" t="s">
-        <v>731</v>
+        <v>490</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B470" t="s">
         <v>733</v>
@@ -9756,12 +9762,12 @@
         <v>736</v>
       </c>
       <c r="B472" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="473" spans="1:2">
       <c r="A473" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B473" t="s">
         <v>738</v>
@@ -9772,36 +9778,36 @@
         <v>739</v>
       </c>
       <c r="B474" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="475" spans="1:2">
       <c r="A475" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B475" t="s">
-        <v>488</v>
+        <v>741</v>
       </c>
     </row>
     <row r="476" spans="1:2">
       <c r="A476" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B476" t="s">
-        <v>741</v>
+        <v>490</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B477" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B478" t="s">
         <v>744</v>
@@ -9812,12 +9818,12 @@
         <v>745</v>
       </c>
       <c r="B479" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B480" t="s">
         <v>747</v>
@@ -9828,20 +9834,20 @@
         <v>748</v>
       </c>
       <c r="B481" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B482" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="483" spans="1:2">
       <c r="A483" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B483" t="s">
         <v>751</v>
@@ -9852,12 +9858,12 @@
         <v>752</v>
       </c>
       <c r="B484" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B485" t="s">
         <v>754</v>
@@ -9876,44 +9882,44 @@
         <v>757</v>
       </c>
       <c r="B487" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B488" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="489" spans="1:2">
       <c r="A489" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B489" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="490" spans="1:2">
       <c r="A490" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B490" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B491" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B492" t="s">
         <v>763</v>
@@ -10076,20 +10082,20 @@
         <v>802</v>
       </c>
       <c r="B512" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="A513" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B513" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="514" spans="1:2">
       <c r="A514" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B514" t="s">
         <v>805</v>
@@ -10100,12 +10106,12 @@
         <v>806</v>
       </c>
       <c r="B515" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="516" spans="1:2">
       <c r="A516" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B516" t="s">
         <v>808</v>
@@ -10116,12 +10122,12 @@
         <v>809</v>
       </c>
       <c r="B517" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B518" t="s">
         <v>811</v>
@@ -10140,28 +10146,28 @@
         <v>814</v>
       </c>
       <c r="B520" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="521" spans="1:2">
       <c r="A521" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B521" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="522" spans="1:2">
       <c r="A522" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B522" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="523" spans="1:2">
       <c r="A523" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B523" t="s">
         <v>818</v>
@@ -10252,12 +10258,12 @@
         <v>839</v>
       </c>
       <c r="B534" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B535" t="s">
         <v>841</v>
@@ -10276,28 +10282,28 @@
         <v>844</v>
       </c>
       <c r="B537" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="538" spans="1:2">
       <c r="A538" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B538" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B539" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B540" t="s">
         <v>848</v>
@@ -10308,52 +10314,52 @@
         <v>849</v>
       </c>
       <c r="B541" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="542" spans="1:2">
       <c r="A542" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B542" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B543" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B544" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B545" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B546" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="547" spans="1:2">
       <c r="A547" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B547" t="s">
         <v>856</v>
@@ -10364,12 +10370,12 @@
         <v>857</v>
       </c>
       <c r="B548" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B549" t="s">
         <v>859</v>
@@ -10388,60 +10394,60 @@
         <v>862</v>
       </c>
       <c r="B551" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="552" spans="1:2">
       <c r="A552" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B552" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B553" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B554" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B555" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B556" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B557" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B558" t="s">
         <v>870</v>
@@ -10500,28 +10506,28 @@
         <v>883</v>
       </c>
       <c r="B565" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="566" spans="1:2">
       <c r="A566" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B566" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B567" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B568" t="s">
         <v>887</v>
@@ -10540,12 +10546,12 @@
         <v>890</v>
       </c>
       <c r="B570" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="571" spans="1:2">
       <c r="A571" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B571" t="s">
         <v>892</v>
@@ -10564,12 +10570,12 @@
         <v>895</v>
       </c>
       <c r="B573" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="574" spans="1:2">
       <c r="A574" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B574" t="s">
         <v>897</v>
@@ -10596,52 +10602,52 @@
         <v>902</v>
       </c>
       <c r="B577" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B578" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B579" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B580" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B581" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B582" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B583" t="s">
         <v>909</v>
@@ -10660,12 +10666,12 @@
         <v>912</v>
       </c>
       <c r="B585" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="586" spans="1:2">
       <c r="A586" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B586" t="s">
         <v>914</v>
@@ -10700,12 +10706,12 @@
         <v>921</v>
       </c>
       <c r="B590" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B591" t="s">
         <v>923</v>
@@ -10724,12 +10730,12 @@
         <v>926</v>
       </c>
       <c r="B593" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B594" t="s">
         <v>928</v>
@@ -10780,12 +10786,12 @@
         <v>939</v>
       </c>
       <c r="B600" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B601" t="s">
         <v>941</v>
@@ -10796,20 +10802,20 @@
         <v>942</v>
       </c>
       <c r="B602" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B603" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B604" t="s">
         <v>945</v>
@@ -10852,20 +10858,20 @@
         <v>954</v>
       </c>
       <c r="B609" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B610" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B611" t="s">
         <v>957</v>
@@ -10876,20 +10882,20 @@
         <v>958</v>
       </c>
       <c r="B612" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B613" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="614" spans="1:2">
       <c r="A614" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B614" t="s">
         <v>961</v>
@@ -10900,12 +10906,12 @@
         <v>962</v>
       </c>
       <c r="B615" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B616" t="s">
         <v>964</v>
@@ -10924,20 +10930,20 @@
         <v>967</v>
       </c>
       <c r="B618" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="619" spans="1:2">
       <c r="A619" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B619" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="620" spans="1:2">
       <c r="A620" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B620" t="s">
         <v>970</v>
@@ -10956,20 +10962,20 @@
         <v>973</v>
       </c>
       <c r="B622" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B623" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B624" t="s">
         <v>976</v>
@@ -11004,20 +11010,20 @@
         <v>983</v>
       </c>
       <c r="B628" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B629" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="630" spans="1:2">
       <c r="A630" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B630" t="s">
         <v>986</v>
@@ -11028,20 +11034,20 @@
         <v>987</v>
       </c>
       <c r="B631" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B632" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B633" t="s">
         <v>990</v>
@@ -11068,92 +11074,92 @@
         <v>995</v>
       </c>
       <c r="B636" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B637" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B638" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B639" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B640" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B641" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B642" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B643" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B644" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B645" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B646" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B647" t="s">
         <v>1007</v>
@@ -11164,36 +11170,36 @@
         <v>1008</v>
       </c>
       <c r="B648" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="649" spans="1:2">
       <c r="A649" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B649" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B650" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B651" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B652" t="s">
         <v>1013</v>
@@ -11228,12 +11234,12 @@
         <v>1020</v>
       </c>
       <c r="B656" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="657" spans="1:2">
       <c r="A657" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B657" t="s">
         <v>1022</v>
@@ -11244,12 +11250,12 @@
         <v>1023</v>
       </c>
       <c r="B658" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B659" t="s">
         <v>1025</v>
@@ -11260,12 +11266,12 @@
         <v>1026</v>
       </c>
       <c r="B660" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="661" spans="1:2">
       <c r="A661" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B661" t="s">
         <v>1028</v>
@@ -11284,12 +11290,12 @@
         <v>1031</v>
       </c>
       <c r="B663" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="664" spans="1:2">
       <c r="A664" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B664" t="s">
         <v>1033</v>
@@ -11348,36 +11354,36 @@
         <v>1046</v>
       </c>
       <c r="B671" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="672" spans="1:2">
       <c r="A672" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B672" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="673" spans="1:2">
       <c r="A673" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B673" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B674" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B675" t="s">
         <v>1051</v>
@@ -11396,28 +11402,28 @@
         <v>1054</v>
       </c>
       <c r="B677" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="678" spans="1:2">
       <c r="A678" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B678" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="679" spans="1:2">
       <c r="A679" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B679" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="680" spans="1:2">
       <c r="A680" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B680" t="s">
         <v>1058</v>
@@ -11428,44 +11434,44 @@
         <v>1059</v>
       </c>
       <c r="B681" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="682" spans="1:2">
       <c r="A682" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B682" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="683" spans="1:2">
       <c r="A683" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B683" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="684" spans="1:2">
       <c r="A684" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B684" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B685" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B686" t="s">
         <v>1065</v>
@@ -11484,28 +11490,28 @@
         <v>1068</v>
       </c>
       <c r="B688" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="689" spans="1:2">
       <c r="A689" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B689" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B690" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B691" t="s">
         <v>1072</v>
@@ -11588,12 +11594,12 @@
         <v>1091</v>
       </c>
       <c r="B701" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="702" spans="1:2">
       <c r="A702" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B702" t="s">
         <v>1093</v>
@@ -11612,12 +11618,12 @@
         <v>1096</v>
       </c>
       <c r="B704" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="705" spans="1:2">
       <c r="A705" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B705" t="s">
         <v>1098</v>
@@ -11636,12 +11642,12 @@
         <v>1101</v>
       </c>
       <c r="B707" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="708" spans="1:2">
       <c r="A708" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B708" t="s">
         <v>1103</v>
@@ -11652,20 +11658,20 @@
         <v>1104</v>
       </c>
       <c r="B709" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B710" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B711" t="s">
         <v>1107</v>
@@ -11676,60 +11682,60 @@
         <v>1108</v>
       </c>
       <c r="B712" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B713" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B714" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B715" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B716" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B717" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B718" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B719" t="s">
         <v>1116</v>
@@ -11740,12 +11746,12 @@
         <v>1117</v>
       </c>
       <c r="B720" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B721" t="s">
         <v>1119</v>
@@ -11756,20 +11762,20 @@
         <v>1120</v>
       </c>
       <c r="B722" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="723" spans="1:2">
       <c r="A723" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B723" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="724" spans="1:2">
       <c r="A724" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B724" t="s">
         <v>1123</v>
@@ -11860,12 +11866,12 @@
         <v>1144</v>
       </c>
       <c r="B735" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="736" spans="1:2">
       <c r="A736" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B736" t="s">
         <v>1146</v>
@@ -11884,12 +11890,12 @@
         <v>1149</v>
       </c>
       <c r="B738" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B739" t="s">
         <v>1151</v>
@@ -11908,28 +11914,28 @@
         <v>1154</v>
       </c>
       <c r="B741" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="742" spans="1:2">
       <c r="A742" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B742" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B743" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="744" spans="1:2">
       <c r="A744" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B744" t="s">
         <v>1158</v>
@@ -11940,44 +11946,44 @@
         <v>1159</v>
       </c>
       <c r="B745" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="746" spans="1:2">
       <c r="A746" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B746" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B747" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B748" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B749" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B750" t="s">
         <v>1165</v>
@@ -11996,36 +12002,36 @@
         <v>1168</v>
       </c>
       <c r="B752" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="753" spans="1:2">
       <c r="A753" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B753" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="754" spans="1:2">
       <c r="A754" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B754" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B755" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B756" t="s">
         <v>1173</v>
@@ -12084,12 +12090,12 @@
         <v>1186</v>
       </c>
       <c r="B763" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B764" t="s">
         <v>1188</v>
@@ -12116,12 +12122,12 @@
         <v>1193</v>
       </c>
       <c r="B767" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="768" spans="1:2">
       <c r="A768" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B768" t="s">
         <v>1195</v>
@@ -12132,20 +12138,20 @@
         <v>1196</v>
       </c>
       <c r="B769" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B770" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B771" t="s">
         <v>1199</v>
@@ -12185,15 +12191,15 @@
     </row>
     <row r="776" spans="1:2">
       <c r="A776" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B776" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="777" spans="1:2">
       <c r="A777" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B777" t="s">
         <v>1209</v>
@@ -12220,28 +12226,28 @@
         <v>1214</v>
       </c>
       <c r="B780" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="781" spans="1:2">
       <c r="A781" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B781" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="782" spans="1:2">
       <c r="A782" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B782" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="783" spans="1:2">
       <c r="A783" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B783" t="s">
         <v>1218</v>
@@ -12252,20 +12258,20 @@
         <v>1219</v>
       </c>
       <c r="B784" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="785" spans="1:2">
       <c r="A785" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B785" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B786" t="s">
         <v>1222</v>
@@ -12300,28 +12306,28 @@
         <v>1229</v>
       </c>
       <c r="B790" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="791" spans="1:2">
       <c r="A791" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B791" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B792" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B793" t="s">
         <v>1233</v>
@@ -12340,12 +12346,12 @@
         <v>1236</v>
       </c>
       <c r="B795" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B796" t="s">
         <v>1238</v>
@@ -12356,60 +12362,60 @@
         <v>1239</v>
       </c>
       <c r="B797" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B798" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B799" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B800" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B801" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B802" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B803" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B804" t="s">
         <v>1247</v>
@@ -12420,12 +12426,12 @@
         <v>1248</v>
       </c>
       <c r="B805" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B806" t="s">
         <v>1250</v>
@@ -12492,36 +12498,36 @@
         <v>1265</v>
       </c>
       <c r="B814" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B815" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B816" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B817" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B818" t="s">
         <v>1270</v>
@@ -12556,12 +12562,12 @@
         <v>1277</v>
       </c>
       <c r="B822" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B823" t="s">
         <v>1279</v>
@@ -12596,12 +12602,12 @@
         <v>1286</v>
       </c>
       <c r="B827" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="828" spans="1:2">
       <c r="A828" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B828" t="s">
         <v>1288</v>
@@ -12612,12 +12618,12 @@
         <v>1289</v>
       </c>
       <c r="B829" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B830" t="s">
         <v>1291</v>
@@ -12628,12 +12634,12 @@
         <v>1292</v>
       </c>
       <c r="B831" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="832" spans="1:2">
       <c r="A832" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B832" t="s">
         <v>1294</v>
@@ -12644,12 +12650,12 @@
         <v>1295</v>
       </c>
       <c r="B833" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B834" t="s">
         <v>1297</v>
@@ -12660,23 +12666,23 @@
         <v>1298</v>
       </c>
       <c r="B835" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B836" t="s">
-        <v>719</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B837" t="s">
-        <v>1301</v>
+        <v>721</v>
       </c>
     </row>
     <row r="838" spans="1:2">
@@ -12692,36 +12698,36 @@
         <v>1304</v>
       </c>
       <c r="B839" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B840" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B841" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B842" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B843" t="s">
         <v>1309</v>
@@ -12756,12 +12762,12 @@
         <v>1316</v>
       </c>
       <c r="B847" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B848" t="s">
         <v>1318</v>
@@ -12780,36 +12786,36 @@
         <v>1321</v>
       </c>
       <c r="B850" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B851" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B852" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B853" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B854" t="s">
         <v>1326</v>
@@ -12916,28 +12922,28 @@
         <v>1351</v>
       </c>
       <c r="B867" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B868" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B869" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B870" t="s">
         <v>1355</v>
@@ -12948,36 +12954,36 @@
         <v>1356</v>
       </c>
       <c r="B871" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B872" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B873" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B874" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B875" t="s">
         <v>1361</v>
@@ -12988,28 +12994,28 @@
         <v>1362</v>
       </c>
       <c r="B876" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B877" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B878" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B879" t="s">
         <v>1366</v>
@@ -13036,12 +13042,12 @@
         <v>1371</v>
       </c>
       <c r="B882" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B883" t="s">
         <v>1373</v>
@@ -13076,15 +13082,15 @@
         <v>1380</v>
       </c>
       <c r="B887" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B888" t="s">
         <v>1381</v>
-      </c>
-      <c r="B888" t="s">
-        <v>1382</v>
       </c>
     </row>
     <row r="889" spans="1:2">
@@ -13092,20 +13098,20 @@
         <v>1383</v>
       </c>
       <c r="B889" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="B890" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="B891" t="s">
         <v>1386</v>
@@ -13132,12 +13138,12 @@
         <v>1391</v>
       </c>
       <c r="B894" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="B895" t="s">
         <v>1393</v>
@@ -13156,12 +13162,12 @@
         <v>1396</v>
       </c>
       <c r="B897" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B898" t="s">
         <v>1398</v>
@@ -13172,28 +13178,28 @@
         <v>1399</v>
       </c>
       <c r="B899" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="B900" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B901" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B902" t="s">
         <v>1403</v>
@@ -13204,20 +13210,20 @@
         <v>1404</v>
       </c>
       <c r="B903" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="B904" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B905" t="s">
         <v>1407</v>
@@ -13244,20 +13250,20 @@
         <v>1412</v>
       </c>
       <c r="B908" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="B909" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="B910" t="s">
         <v>1415</v>
@@ -13300,60 +13306,60 @@
         <v>1424</v>
       </c>
       <c r="B915" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="B916" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B917" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B918" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B919" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B920" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B921" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B922" t="s">
         <v>1432</v>
@@ -13388,20 +13394,20 @@
         <v>1439</v>
       </c>
       <c r="B926" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B927" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B928" t="s">
         <v>1442</v>
@@ -13444,20 +13450,20 @@
         <v>1451</v>
       </c>
       <c r="B933" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="B934" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="B935" t="s">
         <v>1454</v>
@@ -13492,12 +13498,12 @@
         <v>1461</v>
       </c>
       <c r="B939" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B940" t="s">
         <v>1463</v>
@@ -13516,20 +13522,20 @@
         <v>1466</v>
       </c>
       <c r="B942" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B943" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B944" t="s">
         <v>1469</v>
@@ -13540,12 +13546,12 @@
         <v>1470</v>
       </c>
       <c r="B945" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B946" t="s">
         <v>1472</v>
@@ -13572,12 +13578,12 @@
         <v>1477</v>
       </c>
       <c r="B949" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B950" t="s">
         <v>1479</v>
@@ -13604,36 +13610,36 @@
         <v>1484</v>
       </c>
       <c r="B953" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B954" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B955" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B956" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B957" t="s">
         <v>1489</v>
@@ -13644,52 +13650,52 @@
         <v>1490</v>
       </c>
       <c r="B958" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="B959" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B960" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="B961" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B962" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="B963" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B964" t="s">
         <v>1497</v>
@@ -13724,20 +13730,20 @@
         <v>1504</v>
       </c>
       <c r="B968" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B969" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B970" t="s">
         <v>1507</v>
@@ -13788,36 +13794,36 @@
         <v>1518</v>
       </c>
       <c r="B976" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B977" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B978" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B979" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="B980" t="s">
         <v>1523</v>
@@ -13836,12 +13842,12 @@
         <v>1526</v>
       </c>
       <c r="B982" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B983" t="s">
         <v>1528</v>
@@ -13908,20 +13914,20 @@
         <v>1543</v>
       </c>
       <c r="B991" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B992" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B993" t="s">
         <v>1546</v>
@@ -13940,28 +13946,28 @@
         <v>1549</v>
       </c>
       <c r="B995" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B996" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B997" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B998" t="s">
         <v>1553</v>
@@ -14004,12 +14010,12 @@
         <v>1562</v>
       </c>
       <c r="B1003" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B1004" t="s">
         <v>1564</v>
@@ -14020,12 +14026,12 @@
         <v>1565</v>
       </c>
       <c r="B1005" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B1006" t="s">
         <v>1567</v>
@@ -14044,28 +14050,28 @@
         <v>1570</v>
       </c>
       <c r="B1008" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B1009" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B1010" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B1011" t="s">
         <v>1574</v>
@@ -14076,12 +14082,12 @@
         <v>1575</v>
       </c>
       <c r="B1012" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="B1013" t="s">
         <v>1577</v>
@@ -14100,36 +14106,36 @@
         <v>1580</v>
       </c>
       <c r="B1015" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B1016" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B1017" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B1018" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B1019" t="s">
         <v>1585</v>
@@ -14140,36 +14146,36 @@
         <v>1586</v>
       </c>
       <c r="B1020" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B1021" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B1022" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B1023" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B1024" t="s">
         <v>1591</v>
@@ -14188,36 +14194,36 @@
         <v>1594</v>
       </c>
       <c r="B1026" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="B1027" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B1028" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B1029" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1030" t="s">
         <v>1599</v>
@@ -14236,12 +14242,12 @@
         <v>1602</v>
       </c>
       <c r="B1032" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="B1033" t="s">
         <v>1604</v>
@@ -14268,12 +14274,12 @@
         <v>1609</v>
       </c>
       <c r="B1036" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B1037" t="s">
         <v>1611</v>
@@ -14284,20 +14290,20 @@
         <v>1612</v>
       </c>
       <c r="B1038" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B1039" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B1040" t="s">
         <v>1615</v>
@@ -14308,52 +14314,52 @@
         <v>1616</v>
       </c>
       <c r="B1041" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B1042" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B1043" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B1044" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="B1045" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B1046" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="B1047" t="s">
         <v>1623</v>
@@ -14372,12 +14378,12 @@
         <v>1626</v>
       </c>
       <c r="B1049" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B1050" t="s">
         <v>1628</v>
@@ -14404,20 +14410,20 @@
         <v>1633</v>
       </c>
       <c r="B1053" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B1054" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B1055" t="s">
         <v>1636</v>
@@ -14444,20 +14450,20 @@
         <v>1641</v>
       </c>
       <c r="B1058" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="B1059" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1060" t="s">
         <v>1644</v>
@@ -14468,20 +14474,20 @@
         <v>1645</v>
       </c>
       <c r="B1061" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B1062" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="B1063" t="s">
         <v>1648</v>
@@ -14660,12 +14666,12 @@
         <v>1691</v>
       </c>
       <c r="B1085" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B1086" t="s">
         <v>1693</v>
@@ -14676,36 +14682,36 @@
         <v>1694</v>
       </c>
       <c r="B1087" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B1088" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B1089" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B1090" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B1091" t="s">
         <v>1699</v>
@@ -14716,12 +14722,12 @@
         <v>1700</v>
       </c>
       <c r="B1092" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B1093" t="s">
         <v>1702</v>
@@ -14732,28 +14738,28 @@
         <v>1703</v>
       </c>
       <c r="B1094" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B1095" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B1096" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B1097" t="s">
         <v>1707</v>
@@ -14764,20 +14770,20 @@
         <v>1708</v>
       </c>
       <c r="B1098" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B1099" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B1100" t="s">
         <v>1711</v>
@@ -14812,20 +14818,20 @@
         <v>1718</v>
       </c>
       <c r="B1104" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="B1105" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="B1106" t="s">
         <v>1721</v>
@@ -14868,12 +14874,12 @@
         <v>1730</v>
       </c>
       <c r="B1111" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="B1112" t="s">
         <v>1732</v>
@@ -14900,12 +14906,12 @@
         <v>1737</v>
       </c>
       <c r="B1115" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="B1116" t="s">
         <v>1739</v>
@@ -14916,20 +14922,20 @@
         <v>1740</v>
       </c>
       <c r="B1117" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="B1118" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="B1119" t="s">
         <v>1743</v>
@@ -14940,12 +14946,12 @@
         <v>1744</v>
       </c>
       <c r="B1120" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="B1121" t="s">
         <v>1746</v>
@@ -14972,20 +14978,20 @@
         <v>1751</v>
       </c>
       <c r="B1124" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B1125" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="B1126" t="s">
         <v>1754</v>
@@ -15140,44 +15146,44 @@
         <v>1791</v>
       </c>
       <c r="B1145" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B1146" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="B1147" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B1148" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="B1149" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B1150" t="s">
         <v>1797</v>
@@ -15196,36 +15202,36 @@
         <v>1800</v>
       </c>
       <c r="B1152" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="B1153" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="B1154" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="B1155" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="B1156" t="s">
         <v>1805</v>
@@ -15236,12 +15242,12 @@
         <v>1806</v>
       </c>
       <c r="B1157" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="B1158" t="s">
         <v>1808</v>
@@ -15268,12 +15274,12 @@
         <v>1813</v>
       </c>
       <c r="B1161" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="B1162" t="s">
         <v>1815</v>
@@ -15284,12 +15290,12 @@
         <v>1816</v>
       </c>
       <c r="B1163" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="B1164" t="s">
         <v>1818</v>
@@ -15300,12 +15306,12 @@
         <v>1819</v>
       </c>
       <c r="B1165" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="B1166" t="s">
         <v>1821</v>
@@ -15340,44 +15346,44 @@
         <v>1828</v>
       </c>
       <c r="B1170" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B1171" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="B1172" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="B1173" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="B1174" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="B1175" t="s">
         <v>1834</v>
@@ -15388,28 +15394,28 @@
         <v>1835</v>
       </c>
       <c r="B1176" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B1177" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="B1178" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="B1179" t="s">
         <v>1839</v>
@@ -15420,36 +15426,36 @@
         <v>1840</v>
       </c>
       <c r="B1180" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="B1181" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="B1182" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="B1183" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="B1184" t="s">
         <v>1845</v>
@@ -15468,12 +15474,12 @@
         <v>1848</v>
       </c>
       <c r="B1186" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="B1187" t="s">
         <v>1850</v>
@@ -15484,20 +15490,20 @@
         <v>1851</v>
       </c>
       <c r="B1188" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="B1189" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B1190" t="s">
         <v>1854</v>
@@ -15516,36 +15522,36 @@
         <v>1857</v>
       </c>
       <c r="B1192" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B1193" t="s">
-        <v>721</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="B1194" t="s">
-        <v>1859</v>
+        <v>723</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
       <c r="A1195" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="B1195" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="1196" spans="1:2">
       <c r="A1196" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="B1196" t="s">
         <v>1862</v>
@@ -15556,20 +15562,20 @@
         <v>1863</v>
       </c>
       <c r="B1197" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="1198" spans="1:2">
       <c r="A1198" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="B1198" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1199" spans="1:2">
       <c r="A1199" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="B1199" t="s">
         <v>1866</v>
@@ -15591,8 +15597,16 @@
         <v>1870</v>
       </c>
     </row>
+    <row r="1202" spans="1:2">
+      <c r="A1202" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B1202" t="s">
+        <v>1872</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1201"/>
+  <autoFilter ref="A1:B1202"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/es/headTags.xlsx
+++ b/lang/es/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1203</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1873">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1875">
   <si>
     <t>en</t>
   </si>
@@ -1193,6 +1193,12 @@
   </si>
   <si>
     <t>Diablo</t>
+  </si>
+  <si>
+    <t>Die of Death</t>
+  </si>
+  <si>
+    <t>Matriz de la Muerte</t>
   </si>
   <si>
     <t>Digimon</t>
@@ -5982,7 +5988,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1202"/>
+  <dimension ref="A1:B1203"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -8034,12 +8040,12 @@
         <v>392</v>
       </c>
       <c r="B256" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B257" t="s">
         <v>394</v>
@@ -8050,36 +8056,36 @@
         <v>395</v>
       </c>
       <c r="B258" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B259" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B260" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="261" spans="1:2">
       <c r="A261" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B261" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="262" spans="1:2">
       <c r="A262" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B262" t="s">
         <v>400</v>
@@ -8122,20 +8128,20 @@
         <v>409</v>
       </c>
       <c r="B267" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B268" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B269" t="s">
         <v>412</v>
@@ -8154,28 +8160,28 @@
         <v>415</v>
       </c>
       <c r="B271" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B272" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B273" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B274" t="s">
         <v>419</v>
@@ -8186,44 +8192,44 @@
         <v>420</v>
       </c>
       <c r="B275" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="276" spans="1:2">
       <c r="A276" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B276" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="277" spans="1:2">
       <c r="A277" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B277" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B278" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="279" spans="1:2">
       <c r="A279" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B279" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="280" spans="1:2">
       <c r="A280" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B280" t="s">
         <v>426</v>
@@ -8250,36 +8256,36 @@
         <v>431</v>
       </c>
       <c r="B283" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="284" spans="1:2">
       <c r="A284" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B284" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B285" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B286" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="287" spans="1:2">
       <c r="A287" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B287" t="s">
         <v>436</v>
@@ -8290,12 +8296,12 @@
         <v>437</v>
       </c>
       <c r="B288" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B289" t="s">
         <v>439</v>
@@ -8306,12 +8312,12 @@
         <v>440</v>
       </c>
       <c r="B290" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="291" spans="1:2">
       <c r="A291" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B291" t="s">
         <v>442</v>
@@ -8322,12 +8328,12 @@
         <v>443</v>
       </c>
       <c r="B292" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="293" spans="1:2">
       <c r="A293" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B293" t="s">
         <v>445</v>
@@ -8338,15 +8344,15 @@
         <v>446</v>
       </c>
       <c r="B294" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="295" spans="1:2">
       <c r="A295" t="s">
+        <v>448</v>
+      </c>
+      <c r="B295" t="s">
         <v>447</v>
-      </c>
-      <c r="B295" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -8362,20 +8368,20 @@
         <v>451</v>
       </c>
       <c r="B297" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B298" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B299" t="s">
         <v>454</v>
@@ -8410,12 +8416,12 @@
         <v>461</v>
       </c>
       <c r="B303" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="304" spans="1:2">
       <c r="A304" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B304" t="s">
         <v>463</v>
@@ -8426,12 +8432,12 @@
         <v>464</v>
       </c>
       <c r="B305" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B306" t="s">
         <v>466</v>
@@ -8474,20 +8480,20 @@
         <v>475</v>
       </c>
       <c r="B311" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B312" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B313" t="s">
         <v>478</v>
@@ -8506,20 +8512,20 @@
         <v>481</v>
       </c>
       <c r="B315" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B316" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="317" spans="1:2">
       <c r="A317" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B317" t="s">
         <v>484</v>
@@ -8554,44 +8560,44 @@
         <v>491</v>
       </c>
       <c r="B321" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B322" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="323" spans="1:2">
       <c r="A323" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B323" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B324" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="325" spans="1:2">
       <c r="A325" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B325" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="326" spans="1:2">
       <c r="A326" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B326" t="s">
         <v>497</v>
@@ -8602,36 +8608,36 @@
         <v>498</v>
       </c>
       <c r="B327" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B328" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B329" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="330" spans="1:2">
       <c r="A330" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B330" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B331" t="s">
         <v>503</v>
@@ -8642,28 +8648,28 @@
         <v>504</v>
       </c>
       <c r="B332" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B333" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B334" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B335" t="s">
         <v>508</v>
@@ -8674,12 +8680,12 @@
         <v>509</v>
       </c>
       <c r="B336" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="337" spans="1:2">
       <c r="A337" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B337" t="s">
         <v>511</v>
@@ -8730,12 +8736,12 @@
         <v>522</v>
       </c>
       <c r="B343" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="344" spans="1:2">
       <c r="A344" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B344" t="s">
         <v>524</v>
@@ -8890,12 +8896,12 @@
         <v>561</v>
       </c>
       <c r="B363" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="364" spans="1:2">
       <c r="A364" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B364" t="s">
         <v>563</v>
@@ -8922,12 +8928,12 @@
         <v>568</v>
       </c>
       <c r="B367" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="368" spans="1:2">
       <c r="A368" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B368" t="s">
         <v>570</v>
@@ -8978,15 +8984,15 @@
         <v>581</v>
       </c>
       <c r="B374" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="375" spans="1:2">
       <c r="A375" t="s">
+        <v>583</v>
+      </c>
+      <c r="B375" t="s">
         <v>582</v>
-      </c>
-      <c r="B375" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -9002,20 +9008,20 @@
         <v>586</v>
       </c>
       <c r="B377" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="378" spans="1:2">
       <c r="A378" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B378" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="379" spans="1:2">
       <c r="A379" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B379" t="s">
         <v>589</v>
@@ -9026,12 +9032,12 @@
         <v>590</v>
       </c>
       <c r="B380" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="381" spans="1:2">
       <c r="A381" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B381" t="s">
         <v>592</v>
@@ -9058,31 +9064,31 @@
         <v>597</v>
       </c>
       <c r="B384" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
     </row>
     <row r="385" spans="1:2">
       <c r="A385" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B385" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="386" spans="1:2">
       <c r="A386" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B386" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="387" spans="1:2">
       <c r="A387" t="s">
+        <v>601</v>
+      </c>
+      <c r="B387" t="s">
         <v>600</v>
-      </c>
-      <c r="B387" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -9098,12 +9104,12 @@
         <v>604</v>
       </c>
       <c r="B389" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="390" spans="1:2">
       <c r="A390" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B390" t="s">
         <v>606</v>
@@ -9114,12 +9120,12 @@
         <v>607</v>
       </c>
       <c r="B391" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="392" spans="1:2">
       <c r="A392" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B392" t="s">
         <v>609</v>
@@ -9138,116 +9144,116 @@
         <v>612</v>
       </c>
       <c r="B394" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="395" spans="1:2">
       <c r="A395" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B395" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="396" spans="1:2">
       <c r="A396" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B396" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="397" spans="1:2">
       <c r="A397" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B397" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="398" spans="1:2">
       <c r="A398" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B398" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="399" spans="1:2">
       <c r="A399" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B399" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="400" spans="1:2">
       <c r="A400" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B400" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="401" spans="1:2">
       <c r="A401" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B401" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="402" spans="1:2">
       <c r="A402" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B402" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="403" spans="1:2">
       <c r="A403" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B403" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="404" spans="1:2">
       <c r="A404" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B404" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="405" spans="1:2">
       <c r="A405" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B405" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="406" spans="1:2">
       <c r="A406" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B406" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="407" spans="1:2">
       <c r="A407" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B407" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="408" spans="1:2">
       <c r="A408" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B408" t="s">
         <v>627</v>
@@ -9271,10 +9277,10 @@
     </row>
     <row r="411" spans="1:2">
       <c r="A411" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B411" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -9306,20 +9312,20 @@
         <v>639</v>
       </c>
       <c r="B415" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="416" spans="1:2">
       <c r="A416" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B416" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="417" spans="1:2">
       <c r="A417" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B417" t="s">
         <v>642</v>
@@ -9330,20 +9336,20 @@
         <v>643</v>
       </c>
       <c r="B418" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="419" spans="1:2">
       <c r="A419" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B419" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="420" spans="1:2">
       <c r="A420" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B420" t="s">
         <v>646</v>
@@ -9354,20 +9360,20 @@
         <v>647</v>
       </c>
       <c r="B421" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="422" spans="1:2">
       <c r="A422" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B422" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="423" spans="1:2">
       <c r="A423" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B423" t="s">
         <v>650</v>
@@ -9466,36 +9472,36 @@
         <v>673</v>
       </c>
       <c r="B435" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="436" spans="1:2">
       <c r="A436" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B436" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B437" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B438" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="439" spans="1:2">
       <c r="A439" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B439" t="s">
         <v>678</v>
@@ -9506,12 +9512,12 @@
         <v>679</v>
       </c>
       <c r="B440" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="441" spans="1:2">
       <c r="A441" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B441" t="s">
         <v>681</v>
@@ -9586,12 +9592,12 @@
         <v>698</v>
       </c>
       <c r="B450" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="451" spans="1:2">
       <c r="A451" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B451" t="s">
         <v>700</v>
@@ -9642,12 +9648,12 @@
         <v>711</v>
       </c>
       <c r="B457" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="458" spans="1:2">
       <c r="A458" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B458" t="s">
         <v>713</v>
@@ -9722,36 +9728,36 @@
         <v>730</v>
       </c>
       <c r="B467" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B468" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B469" t="s">
-        <v>490</v>
+        <v>733</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B470" t="s">
-        <v>733</v>
+        <v>492</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B471" t="s">
         <v>735</v>
@@ -9770,12 +9776,12 @@
         <v>738</v>
       </c>
       <c r="B473" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="474" spans="1:2">
       <c r="A474" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B474" t="s">
         <v>740</v>
@@ -9786,36 +9792,36 @@
         <v>741</v>
       </c>
       <c r="B475" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="476" spans="1:2">
       <c r="A476" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B476" t="s">
-        <v>490</v>
+        <v>743</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B477" t="s">
-        <v>743</v>
+        <v>492</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B478" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B479" t="s">
         <v>746</v>
@@ -9826,12 +9832,12 @@
         <v>747</v>
       </c>
       <c r="B480" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="481" spans="1:2">
       <c r="A481" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B481" t="s">
         <v>749</v>
@@ -9842,20 +9848,20 @@
         <v>750</v>
       </c>
       <c r="B482" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="483" spans="1:2">
       <c r="A483" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B483" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B484" t="s">
         <v>753</v>
@@ -9866,12 +9872,12 @@
         <v>754</v>
       </c>
       <c r="B485" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="486" spans="1:2">
       <c r="A486" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B486" t="s">
         <v>756</v>
@@ -9890,44 +9896,44 @@
         <v>759</v>
       </c>
       <c r="B488" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="489" spans="1:2">
       <c r="A489" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B489" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="490" spans="1:2">
       <c r="A490" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B490" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B491" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B492" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B493" t="s">
         <v>765</v>
@@ -10090,20 +10096,20 @@
         <v>804</v>
       </c>
       <c r="B513" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="514" spans="1:2">
       <c r="A514" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B514" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="A515" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B515" t="s">
         <v>807</v>
@@ -10114,12 +10120,12 @@
         <v>808</v>
       </c>
       <c r="B516" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="517" spans="1:2">
       <c r="A517" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B517" t="s">
         <v>810</v>
@@ -10130,12 +10136,12 @@
         <v>811</v>
       </c>
       <c r="B518" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="519" spans="1:2">
       <c r="A519" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B519" t="s">
         <v>813</v>
@@ -10154,28 +10160,28 @@
         <v>816</v>
       </c>
       <c r="B521" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="522" spans="1:2">
       <c r="A522" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B522" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="523" spans="1:2">
       <c r="A523" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B523" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="A524" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B524" t="s">
         <v>820</v>
@@ -10266,12 +10272,12 @@
         <v>841</v>
       </c>
       <c r="B535" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="536" spans="1:2">
       <c r="A536" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B536" t="s">
         <v>843</v>
@@ -10290,28 +10296,28 @@
         <v>846</v>
       </c>
       <c r="B538" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B539" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B540" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B541" t="s">
         <v>850</v>
@@ -10322,52 +10328,52 @@
         <v>851</v>
       </c>
       <c r="B542" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B543" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B544" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B545" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B546" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="547" spans="1:2">
       <c r="A547" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B547" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="548" spans="1:2">
       <c r="A548" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B548" t="s">
         <v>858</v>
@@ -10378,12 +10384,12 @@
         <v>859</v>
       </c>
       <c r="B549" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B550" t="s">
         <v>861</v>
@@ -10402,60 +10408,60 @@
         <v>864</v>
       </c>
       <c r="B552" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B553" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B554" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B555" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B556" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B557" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B558" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B559" t="s">
         <v>872</v>
@@ -10514,28 +10520,28 @@
         <v>885</v>
       </c>
       <c r="B566" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B567" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B568" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="569" spans="1:2">
       <c r="A569" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B569" t="s">
         <v>889</v>
@@ -10554,12 +10560,12 @@
         <v>892</v>
       </c>
       <c r="B571" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="572" spans="1:2">
       <c r="A572" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B572" t="s">
         <v>894</v>
@@ -10578,12 +10584,12 @@
         <v>897</v>
       </c>
       <c r="B574" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="575" spans="1:2">
       <c r="A575" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B575" t="s">
         <v>899</v>
@@ -10610,52 +10616,52 @@
         <v>904</v>
       </c>
       <c r="B578" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B579" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B580" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B581" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B582" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B583" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B584" t="s">
         <v>911</v>
@@ -10674,12 +10680,12 @@
         <v>914</v>
       </c>
       <c r="B586" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="587" spans="1:2">
       <c r="A587" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B587" t="s">
         <v>916</v>
@@ -10714,12 +10720,12 @@
         <v>923</v>
       </c>
       <c r="B591" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="592" spans="1:2">
       <c r="A592" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B592" t="s">
         <v>925</v>
@@ -10738,12 +10744,12 @@
         <v>928</v>
       </c>
       <c r="B594" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="595" spans="1:2">
       <c r="A595" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B595" t="s">
         <v>930</v>
@@ -10794,12 +10800,12 @@
         <v>941</v>
       </c>
       <c r="B601" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B602" t="s">
         <v>943</v>
@@ -10810,20 +10816,20 @@
         <v>944</v>
       </c>
       <c r="B603" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B604" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B605" t="s">
         <v>947</v>
@@ -10866,20 +10872,20 @@
         <v>956</v>
       </c>
       <c r="B610" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B611" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B612" t="s">
         <v>959</v>
@@ -10890,20 +10896,20 @@
         <v>960</v>
       </c>
       <c r="B613" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="614" spans="1:2">
       <c r="A614" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B614" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B615" t="s">
         <v>963</v>
@@ -10914,12 +10920,12 @@
         <v>964</v>
       </c>
       <c r="B616" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B617" t="s">
         <v>966</v>
@@ -10938,20 +10944,20 @@
         <v>969</v>
       </c>
       <c r="B619" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="620" spans="1:2">
       <c r="A620" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B620" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="621" spans="1:2">
       <c r="A621" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B621" t="s">
         <v>972</v>
@@ -10970,20 +10976,20 @@
         <v>975</v>
       </c>
       <c r="B623" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B624" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B625" t="s">
         <v>978</v>
@@ -11018,20 +11024,20 @@
         <v>985</v>
       </c>
       <c r="B629" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="630" spans="1:2">
       <c r="A630" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B630" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B631" t="s">
         <v>988</v>
@@ -11042,20 +11048,20 @@
         <v>989</v>
       </c>
       <c r="B632" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B633" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B634" t="s">
         <v>992</v>
@@ -11082,92 +11088,92 @@
         <v>997</v>
       </c>
       <c r="B637" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B638" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B639" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B640" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B641" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B642" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B643" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B644" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B645" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B646" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B647" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B648" t="s">
         <v>1009</v>
@@ -11178,36 +11184,36 @@
         <v>1010</v>
       </c>
       <c r="B649" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B650" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B651" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B652" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B653" t="s">
         <v>1015</v>
@@ -11242,12 +11248,12 @@
         <v>1022</v>
       </c>
       <c r="B657" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B658" t="s">
         <v>1024</v>
@@ -11258,12 +11264,12 @@
         <v>1025</v>
       </c>
       <c r="B659" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="660" spans="1:2">
       <c r="A660" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B660" t="s">
         <v>1027</v>
@@ -11274,12 +11280,12 @@
         <v>1028</v>
       </c>
       <c r="B661" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="662" spans="1:2">
       <c r="A662" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B662" t="s">
         <v>1030</v>
@@ -11298,12 +11304,12 @@
         <v>1033</v>
       </c>
       <c r="B664" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="665" spans="1:2">
       <c r="A665" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B665" t="s">
         <v>1035</v>
@@ -11362,36 +11368,36 @@
         <v>1048</v>
       </c>
       <c r="B672" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="673" spans="1:2">
       <c r="A673" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B673" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B674" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B675" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="676" spans="1:2">
       <c r="A676" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B676" t="s">
         <v>1053</v>
@@ -11410,28 +11416,28 @@
         <v>1056</v>
       </c>
       <c r="B678" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="679" spans="1:2">
       <c r="A679" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B679" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="680" spans="1:2">
       <c r="A680" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B680" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="681" spans="1:2">
       <c r="A681" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B681" t="s">
         <v>1060</v>
@@ -11442,44 +11448,44 @@
         <v>1061</v>
       </c>
       <c r="B682" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="683" spans="1:2">
       <c r="A683" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B683" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="684" spans="1:2">
       <c r="A684" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B684" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B685" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B686" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B687" t="s">
         <v>1067</v>
@@ -11498,28 +11504,28 @@
         <v>1070</v>
       </c>
       <c r="B689" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B690" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B691" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B692" t="s">
         <v>1074</v>
@@ -11602,12 +11608,12 @@
         <v>1093</v>
       </c>
       <c r="B702" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="703" spans="1:2">
       <c r="A703" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B703" t="s">
         <v>1095</v>
@@ -11626,12 +11632,12 @@
         <v>1098</v>
       </c>
       <c r="B705" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="706" spans="1:2">
       <c r="A706" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B706" t="s">
         <v>1100</v>
@@ -11650,12 +11656,12 @@
         <v>1103</v>
       </c>
       <c r="B708" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B709" t="s">
         <v>1105</v>
@@ -11666,20 +11672,20 @@
         <v>1106</v>
       </c>
       <c r="B710" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B711" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B712" t="s">
         <v>1109</v>
@@ -11690,60 +11696,60 @@
         <v>1110</v>
       </c>
       <c r="B713" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B714" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B715" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B716" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B717" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B718" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B719" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B720" t="s">
         <v>1118</v>
@@ -11754,12 +11760,12 @@
         <v>1119</v>
       </c>
       <c r="B721" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="722" spans="1:2">
       <c r="A722" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B722" t="s">
         <v>1121</v>
@@ -11770,20 +11776,20 @@
         <v>1122</v>
       </c>
       <c r="B723" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="724" spans="1:2">
       <c r="A724" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B724" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B725" t="s">
         <v>1125</v>
@@ -11874,12 +11880,12 @@
         <v>1146</v>
       </c>
       <c r="B736" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="737" spans="1:2">
       <c r="A737" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B737" t="s">
         <v>1148</v>
@@ -11898,12 +11904,12 @@
         <v>1151</v>
       </c>
       <c r="B739" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="740" spans="1:2">
       <c r="A740" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B740" t="s">
         <v>1153</v>
@@ -11922,28 +11928,28 @@
         <v>1156</v>
       </c>
       <c r="B742" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B743" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="744" spans="1:2">
       <c r="A744" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B744" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="745" spans="1:2">
       <c r="A745" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B745" t="s">
         <v>1160</v>
@@ -11954,44 +11960,44 @@
         <v>1161</v>
       </c>
       <c r="B746" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B747" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B748" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B749" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B750" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B751" t="s">
         <v>1167</v>
@@ -12010,36 +12016,36 @@
         <v>1170</v>
       </c>
       <c r="B753" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="754" spans="1:2">
       <c r="A754" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B754" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B755" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B756" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B757" t="s">
         <v>1175</v>
@@ -12098,12 +12104,12 @@
         <v>1188</v>
       </c>
       <c r="B764" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="765" spans="1:2">
       <c r="A765" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B765" t="s">
         <v>1190</v>
@@ -12130,12 +12136,12 @@
         <v>1195</v>
       </c>
       <c r="B768" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="769" spans="1:2">
       <c r="A769" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B769" t="s">
         <v>1197</v>
@@ -12146,20 +12152,20 @@
         <v>1198</v>
       </c>
       <c r="B770" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B771" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B772" t="s">
         <v>1201</v>
@@ -12199,15 +12205,15 @@
     </row>
     <row r="777" spans="1:2">
       <c r="A777" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B777" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="778" spans="1:2">
       <c r="A778" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B778" t="s">
         <v>1211</v>
@@ -12234,28 +12240,28 @@
         <v>1216</v>
       </c>
       <c r="B781" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="782" spans="1:2">
       <c r="A782" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B782" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="783" spans="1:2">
       <c r="A783" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B783" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B784" t="s">
         <v>1220</v>
@@ -12266,20 +12272,20 @@
         <v>1221</v>
       </c>
       <c r="B785" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B786" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="787" spans="1:2">
       <c r="A787" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B787" t="s">
         <v>1224</v>
@@ -12314,28 +12320,28 @@
         <v>1231</v>
       </c>
       <c r="B791" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B792" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B793" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B794" t="s">
         <v>1235</v>
@@ -12354,12 +12360,12 @@
         <v>1238</v>
       </c>
       <c r="B796" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B797" t="s">
         <v>1240</v>
@@ -12370,60 +12376,60 @@
         <v>1241</v>
       </c>
       <c r="B798" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B799" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B800" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B801" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B802" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B803" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B804" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B805" t="s">
         <v>1249</v>
@@ -12434,12 +12440,12 @@
         <v>1250</v>
       </c>
       <c r="B806" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B807" t="s">
         <v>1252</v>
@@ -12506,36 +12512,36 @@
         <v>1267</v>
       </c>
       <c r="B815" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B816" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B817" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B818" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B819" t="s">
         <v>1272</v>
@@ -12570,12 +12576,12 @@
         <v>1279</v>
       </c>
       <c r="B823" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="824" spans="1:2">
       <c r="A824" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B824" t="s">
         <v>1281</v>
@@ -12610,12 +12616,12 @@
         <v>1288</v>
       </c>
       <c r="B828" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B829" t="s">
         <v>1290</v>
@@ -12626,12 +12632,12 @@
         <v>1291</v>
       </c>
       <c r="B830" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B831" t="s">
         <v>1293</v>
@@ -12642,12 +12648,12 @@
         <v>1294</v>
       </c>
       <c r="B832" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B833" t="s">
         <v>1296</v>
@@ -12658,12 +12664,12 @@
         <v>1297</v>
       </c>
       <c r="B834" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B835" t="s">
         <v>1299</v>
@@ -12674,23 +12680,23 @@
         <v>1300</v>
       </c>
       <c r="B836" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B837" t="s">
-        <v>721</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B838" t="s">
-        <v>1303</v>
+        <v>723</v>
       </c>
     </row>
     <row r="839" spans="1:2">
@@ -12706,36 +12712,36 @@
         <v>1306</v>
       </c>
       <c r="B840" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B841" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B842" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B843" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B844" t="s">
         <v>1311</v>
@@ -12770,12 +12776,12 @@
         <v>1318</v>
       </c>
       <c r="B848" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B849" t="s">
         <v>1320</v>
@@ -12794,36 +12800,36 @@
         <v>1323</v>
       </c>
       <c r="B851" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B852" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B853" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B854" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B855" t="s">
         <v>1328</v>
@@ -12930,28 +12936,28 @@
         <v>1353</v>
       </c>
       <c r="B868" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B869" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B870" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B871" t="s">
         <v>1357</v>
@@ -12962,36 +12968,36 @@
         <v>1358</v>
       </c>
       <c r="B872" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B873" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B874" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B875" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B876" t="s">
         <v>1363</v>
@@ -13002,28 +13008,28 @@
         <v>1364</v>
       </c>
       <c r="B877" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B878" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B879" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B880" t="s">
         <v>1368</v>
@@ -13050,12 +13056,12 @@
         <v>1373</v>
       </c>
       <c r="B883" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B884" t="s">
         <v>1375</v>
@@ -13090,15 +13096,15 @@
         <v>1382</v>
       </c>
       <c r="B888" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B889" t="s">
         <v>1383</v>
-      </c>
-      <c r="B889" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="890" spans="1:2">
@@ -13106,20 +13112,20 @@
         <v>1385</v>
       </c>
       <c r="B890" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="B891" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="B892" t="s">
         <v>1388</v>
@@ -13146,12 +13152,12 @@
         <v>1393</v>
       </c>
       <c r="B895" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B896" t="s">
         <v>1395</v>
@@ -13170,12 +13176,12 @@
         <v>1398</v>
       </c>
       <c r="B898" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="B899" t="s">
         <v>1400</v>
@@ -13186,28 +13192,28 @@
         <v>1401</v>
       </c>
       <c r="B900" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B901" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B902" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B903" t="s">
         <v>1405</v>
@@ -13218,20 +13224,20 @@
         <v>1406</v>
       </c>
       <c r="B904" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="B905" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B906" t="s">
         <v>1409</v>
@@ -13258,20 +13264,20 @@
         <v>1414</v>
       </c>
       <c r="B909" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B910" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="B911" t="s">
         <v>1417</v>
@@ -13314,60 +13320,60 @@
         <v>1426</v>
       </c>
       <c r="B916" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B917" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B918" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B919" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B920" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B921" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B922" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B923" t="s">
         <v>1434</v>
@@ -13402,20 +13408,20 @@
         <v>1441</v>
       </c>
       <c r="B927" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="B928" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B929" t="s">
         <v>1444</v>
@@ -13458,20 +13464,20 @@
         <v>1453</v>
       </c>
       <c r="B934" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="B935" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B936" t="s">
         <v>1456</v>
@@ -13506,12 +13512,12 @@
         <v>1463</v>
       </c>
       <c r="B940" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="B941" t="s">
         <v>1465</v>
@@ -13530,20 +13536,20 @@
         <v>1468</v>
       </c>
       <c r="B943" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B944" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B945" t="s">
         <v>1471</v>
@@ -13554,12 +13560,12 @@
         <v>1472</v>
       </c>
       <c r="B946" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B947" t="s">
         <v>1474</v>
@@ -13586,12 +13592,12 @@
         <v>1479</v>
       </c>
       <c r="B950" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B951" t="s">
         <v>1481</v>
@@ -13618,36 +13624,36 @@
         <v>1486</v>
       </c>
       <c r="B954" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B955" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B956" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B957" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B958" t="s">
         <v>1491</v>
@@ -13658,52 +13664,52 @@
         <v>1492</v>
       </c>
       <c r="B959" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="B960" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B961" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="B962" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B963" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B964" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B965" t="s">
         <v>1499</v>
@@ -13738,20 +13744,20 @@
         <v>1506</v>
       </c>
       <c r="B969" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B970" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B971" t="s">
         <v>1509</v>
@@ -13802,36 +13808,36 @@
         <v>1520</v>
       </c>
       <c r="B977" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B978" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="B979" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B980" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="B981" t="s">
         <v>1525</v>
@@ -13850,12 +13856,12 @@
         <v>1528</v>
       </c>
       <c r="B983" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B984" t="s">
         <v>1530</v>
@@ -13922,20 +13928,20 @@
         <v>1545</v>
       </c>
       <c r="B992" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B993" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B994" t="s">
         <v>1548</v>
@@ -13954,28 +13960,28 @@
         <v>1551</v>
       </c>
       <c r="B996" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B997" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B998" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B999" t="s">
         <v>1555</v>
@@ -14018,12 +14024,12 @@
         <v>1564</v>
       </c>
       <c r="B1004" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B1005" t="s">
         <v>1566</v>
@@ -14034,12 +14040,12 @@
         <v>1567</v>
       </c>
       <c r="B1006" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B1007" t="s">
         <v>1569</v>
@@ -14058,28 +14064,28 @@
         <v>1572</v>
       </c>
       <c r="B1009" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B1010" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B1011" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B1012" t="s">
         <v>1576</v>
@@ -14090,12 +14096,12 @@
         <v>1577</v>
       </c>
       <c r="B1013" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B1014" t="s">
         <v>1579</v>
@@ -14114,36 +14120,36 @@
         <v>1582</v>
       </c>
       <c r="B1016" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B1017" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B1018" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B1019" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B1020" t="s">
         <v>1587</v>
@@ -14154,36 +14160,36 @@
         <v>1588</v>
       </c>
       <c r="B1021" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B1022" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B1023" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B1024" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B1025" t="s">
         <v>1593</v>
@@ -14202,36 +14208,36 @@
         <v>1596</v>
       </c>
       <c r="B1027" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B1028" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1029" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B1030" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B1031" t="s">
         <v>1601</v>
@@ -14250,12 +14256,12 @@
         <v>1604</v>
       </c>
       <c r="B1033" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="B1034" t="s">
         <v>1606</v>
@@ -14282,12 +14288,12 @@
         <v>1611</v>
       </c>
       <c r="B1037" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B1038" t="s">
         <v>1613</v>
@@ -14298,20 +14304,20 @@
         <v>1614</v>
       </c>
       <c r="B1039" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B1040" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B1041" t="s">
         <v>1617</v>
@@ -14322,52 +14328,52 @@
         <v>1618</v>
       </c>
       <c r="B1042" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B1043" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="B1044" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B1045" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="B1046" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B1047" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B1048" t="s">
         <v>1625</v>
@@ -14386,12 +14392,12 @@
         <v>1628</v>
       </c>
       <c r="B1050" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B1051" t="s">
         <v>1630</v>
@@ -14418,20 +14424,20 @@
         <v>1635</v>
       </c>
       <c r="B1054" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="B1055" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B1056" t="s">
         <v>1638</v>
@@ -14458,20 +14464,20 @@
         <v>1643</v>
       </c>
       <c r="B1059" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="B1060" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B1061" t="s">
         <v>1646</v>
@@ -14482,20 +14488,20 @@
         <v>1647</v>
       </c>
       <c r="B1062" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B1063" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="B1064" t="s">
         <v>1650</v>
@@ -14674,12 +14680,12 @@
         <v>1693</v>
       </c>
       <c r="B1086" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B1087" t="s">
         <v>1695</v>
@@ -14690,36 +14696,36 @@
         <v>1696</v>
       </c>
       <c r="B1088" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B1089" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B1090" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B1091" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B1092" t="s">
         <v>1701</v>
@@ -14730,12 +14736,12 @@
         <v>1702</v>
       </c>
       <c r="B1093" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B1094" t="s">
         <v>1704</v>
@@ -14746,28 +14752,28 @@
         <v>1705</v>
       </c>
       <c r="B1095" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B1096" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1097" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B1098" t="s">
         <v>1709</v>
@@ -14778,20 +14784,20 @@
         <v>1710</v>
       </c>
       <c r="B1099" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B1100" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B1101" t="s">
         <v>1713</v>
@@ -14826,20 +14832,20 @@
         <v>1720</v>
       </c>
       <c r="B1105" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="B1106" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="B1107" t="s">
         <v>1723</v>
@@ -14882,12 +14888,12 @@
         <v>1732</v>
       </c>
       <c r="B1112" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B1113" t="s">
         <v>1734</v>
@@ -14914,12 +14920,12 @@
         <v>1739</v>
       </c>
       <c r="B1116" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="B1117" t="s">
         <v>1741</v>
@@ -14930,20 +14936,20 @@
         <v>1742</v>
       </c>
       <c r="B1118" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="B1119" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="B1120" t="s">
         <v>1745</v>
@@ -14954,12 +14960,12 @@
         <v>1746</v>
       </c>
       <c r="B1121" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="B1122" t="s">
         <v>1748</v>
@@ -14986,20 +14992,20 @@
         <v>1753</v>
       </c>
       <c r="B1125" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="B1126" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="B1127" t="s">
         <v>1756</v>
@@ -15154,44 +15160,44 @@
         <v>1793</v>
       </c>
       <c r="B1146" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B1147" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="B1148" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B1149" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="B1150" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="B1151" t="s">
         <v>1799</v>
@@ -15210,36 +15216,36 @@
         <v>1802</v>
       </c>
       <c r="B1153" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="B1154" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="B1155" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="B1156" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="B1157" t="s">
         <v>1807</v>
@@ -15250,12 +15256,12 @@
         <v>1808</v>
       </c>
       <c r="B1158" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B1159" t="s">
         <v>1810</v>
@@ -15282,12 +15288,12 @@
         <v>1815</v>
       </c>
       <c r="B1162" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="B1163" t="s">
         <v>1817</v>
@@ -15298,12 +15304,12 @@
         <v>1818</v>
       </c>
       <c r="B1164" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B1165" t="s">
         <v>1820</v>
@@ -15314,12 +15320,12 @@
         <v>1821</v>
       </c>
       <c r="B1166" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="B1167" t="s">
         <v>1823</v>
@@ -15354,44 +15360,44 @@
         <v>1830</v>
       </c>
       <c r="B1171" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="B1172" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="B1173" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="B1174" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B1175" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1176" t="s">
         <v>1836</v>
@@ -15402,28 +15408,28 @@
         <v>1837</v>
       </c>
       <c r="B1177" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="B1178" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="B1179" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="B1180" t="s">
         <v>1841</v>
@@ -15434,36 +15440,36 @@
         <v>1842</v>
       </c>
       <c r="B1181" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="B1182" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="B1183" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="B1184" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="B1185" t="s">
         <v>1847</v>
@@ -15482,12 +15488,12 @@
         <v>1850</v>
       </c>
       <c r="B1187" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="B1188" t="s">
         <v>1852</v>
@@ -15498,20 +15504,20 @@
         <v>1853</v>
       </c>
       <c r="B1189" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B1190" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="B1191" t="s">
         <v>1856</v>
@@ -15530,36 +15536,36 @@
         <v>1859</v>
       </c>
       <c r="B1193" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="B1194" t="s">
-        <v>723</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
       <c r="A1195" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="B1195" t="s">
-        <v>1861</v>
+        <v>725</v>
       </c>
     </row>
     <row r="1196" spans="1:2">
       <c r="A1196" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1196" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="1197" spans="1:2">
       <c r="A1197" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1197" t="s">
         <v>1864</v>
@@ -15570,20 +15576,20 @@
         <v>1865</v>
       </c>
       <c r="B1198" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="1199" spans="1:2">
       <c r="A1199" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="B1199" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="1200" spans="1:2">
       <c r="A1200" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="B1200" t="s">
         <v>1868</v>
@@ -15605,8 +15611,16 @@
         <v>1872</v>
       </c>
     </row>
+    <row r="1203" spans="1:2">
+      <c r="A1203" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B1203" t="s">
+        <v>1874</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1202"/>
+  <autoFilter ref="A1:B1203"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/es/headTags.xlsx
+++ b/lang/es/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1204</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1877">
   <si>
     <t>en</t>
   </si>
@@ -1934,6 +1934,12 @@
   </si>
   <si>
     <t>Font (Naranja)</t>
+  </si>
+  <si>
+    <t>Font (Pale Oak)</t>
+  </si>
+  <si>
+    <t>Fuente (Roble pálido)</t>
   </si>
   <si>
     <t>Font (Pink)</t>
@@ -5988,7 +5994,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1203"/>
+  <dimension ref="A1:B1204"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -9320,20 +9326,20 @@
         <v>641</v>
       </c>
       <c r="B416" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="417" spans="1:2">
       <c r="A417" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B417" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="418" spans="1:2">
       <c r="A418" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B418" t="s">
         <v>644</v>
@@ -9344,20 +9350,20 @@
         <v>645</v>
       </c>
       <c r="B419" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="420" spans="1:2">
       <c r="A420" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B420" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="421" spans="1:2">
       <c r="A421" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B421" t="s">
         <v>648</v>
@@ -9368,20 +9374,20 @@
         <v>649</v>
       </c>
       <c r="B422" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="423" spans="1:2">
       <c r="A423" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B423" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="424" spans="1:2">
       <c r="A424" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B424" t="s">
         <v>652</v>
@@ -9480,36 +9486,36 @@
         <v>675</v>
       </c>
       <c r="B436" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B437" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B438" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="439" spans="1:2">
       <c r="A439" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B439" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="440" spans="1:2">
       <c r="A440" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B440" t="s">
         <v>680</v>
@@ -9520,12 +9526,12 @@
         <v>681</v>
       </c>
       <c r="B441" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="442" spans="1:2">
       <c r="A442" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B442" t="s">
         <v>683</v>
@@ -9600,12 +9606,12 @@
         <v>700</v>
       </c>
       <c r="B451" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="452" spans="1:2">
       <c r="A452" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B452" t="s">
         <v>702</v>
@@ -9656,12 +9662,12 @@
         <v>713</v>
       </c>
       <c r="B458" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="459" spans="1:2">
       <c r="A459" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B459" t="s">
         <v>715</v>
@@ -9736,36 +9742,36 @@
         <v>732</v>
       </c>
       <c r="B468" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B469" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B470" t="s">
-        <v>492</v>
+        <v>735</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B471" t="s">
-        <v>735</v>
+        <v>492</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B472" t="s">
         <v>737</v>
@@ -9784,12 +9790,12 @@
         <v>740</v>
       </c>
       <c r="B474" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="475" spans="1:2">
       <c r="A475" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B475" t="s">
         <v>742</v>
@@ -9800,36 +9806,36 @@
         <v>743</v>
       </c>
       <c r="B476" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B477" t="s">
-        <v>492</v>
+        <v>745</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B478" t="s">
-        <v>745</v>
+        <v>492</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B479" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B480" t="s">
         <v>748</v>
@@ -9840,12 +9846,12 @@
         <v>749</v>
       </c>
       <c r="B481" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B482" t="s">
         <v>751</v>
@@ -9856,20 +9862,20 @@
         <v>752</v>
       </c>
       <c r="B483" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B484" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B485" t="s">
         <v>755</v>
@@ -9880,12 +9886,12 @@
         <v>756</v>
       </c>
       <c r="B486" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B487" t="s">
         <v>758</v>
@@ -9904,44 +9910,44 @@
         <v>761</v>
       </c>
       <c r="B489" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="490" spans="1:2">
       <c r="A490" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B490" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B491" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B492" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B493" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="494" spans="1:2">
       <c r="A494" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B494" t="s">
         <v>767</v>
@@ -10104,20 +10110,20 @@
         <v>806</v>
       </c>
       <c r="B514" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="A515" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B515" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="516" spans="1:2">
       <c r="A516" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B516" t="s">
         <v>809</v>
@@ -10128,12 +10134,12 @@
         <v>810</v>
       </c>
       <c r="B517" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B518" t="s">
         <v>812</v>
@@ -10144,12 +10150,12 @@
         <v>813</v>
       </c>
       <c r="B519" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="520" spans="1:2">
       <c r="A520" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B520" t="s">
         <v>815</v>
@@ -10168,28 +10174,28 @@
         <v>818</v>
       </c>
       <c r="B522" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="523" spans="1:2">
       <c r="A523" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B523" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="A524" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B524" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="525" spans="1:2">
       <c r="A525" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B525" t="s">
         <v>822</v>
@@ -10280,12 +10286,12 @@
         <v>843</v>
       </c>
       <c r="B536" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="537" spans="1:2">
       <c r="A537" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B537" t="s">
         <v>845</v>
@@ -10304,28 +10310,28 @@
         <v>848</v>
       </c>
       <c r="B539" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B540" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B541" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="542" spans="1:2">
       <c r="A542" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B542" t="s">
         <v>852</v>
@@ -10336,52 +10342,52 @@
         <v>853</v>
       </c>
       <c r="B543" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B544" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B545" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B546" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="547" spans="1:2">
       <c r="A547" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B547" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="548" spans="1:2">
       <c r="A548" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B548" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B549" t="s">
         <v>860</v>
@@ -10392,12 +10398,12 @@
         <v>861</v>
       </c>
       <c r="B550" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B551" t="s">
         <v>863</v>
@@ -10416,60 +10422,60 @@
         <v>866</v>
       </c>
       <c r="B553" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B554" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B555" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B556" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B557" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B558" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B559" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B560" t="s">
         <v>874</v>
@@ -10528,28 +10534,28 @@
         <v>887</v>
       </c>
       <c r="B567" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B568" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="569" spans="1:2">
       <c r="A569" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B569" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="570" spans="1:2">
       <c r="A570" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B570" t="s">
         <v>891</v>
@@ -10568,12 +10574,12 @@
         <v>894</v>
       </c>
       <c r="B572" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="573" spans="1:2">
       <c r="A573" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B573" t="s">
         <v>896</v>
@@ -10592,12 +10598,12 @@
         <v>899</v>
       </c>
       <c r="B575" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="576" spans="1:2">
       <c r="A576" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B576" t="s">
         <v>901</v>
@@ -10624,52 +10630,52 @@
         <v>906</v>
       </c>
       <c r="B579" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B580" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B581" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B582" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B583" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B584" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B585" t="s">
         <v>913</v>
@@ -10688,12 +10694,12 @@
         <v>916</v>
       </c>
       <c r="B587" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B588" t="s">
         <v>918</v>
@@ -10728,12 +10734,12 @@
         <v>925</v>
       </c>
       <c r="B592" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="593" spans="1:2">
       <c r="A593" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B593" t="s">
         <v>927</v>
@@ -10752,12 +10758,12 @@
         <v>930</v>
       </c>
       <c r="B595" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B596" t="s">
         <v>932</v>
@@ -10808,12 +10814,12 @@
         <v>943</v>
       </c>
       <c r="B602" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B603" t="s">
         <v>945</v>
@@ -10824,20 +10830,20 @@
         <v>946</v>
       </c>
       <c r="B604" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B605" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="606" spans="1:2">
       <c r="A606" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B606" t="s">
         <v>949</v>
@@ -10880,20 +10886,20 @@
         <v>958</v>
       </c>
       <c r="B611" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B612" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B613" t="s">
         <v>961</v>
@@ -10904,20 +10910,20 @@
         <v>962</v>
       </c>
       <c r="B614" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B615" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B616" t="s">
         <v>965</v>
@@ -10928,12 +10934,12 @@
         <v>966</v>
       </c>
       <c r="B617" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="618" spans="1:2">
       <c r="A618" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B618" t="s">
         <v>968</v>
@@ -10952,20 +10958,20 @@
         <v>971</v>
       </c>
       <c r="B620" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="621" spans="1:2">
       <c r="A621" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B621" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B622" t="s">
         <v>974</v>
@@ -10984,20 +10990,20 @@
         <v>977</v>
       </c>
       <c r="B624" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B625" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="626" spans="1:2">
       <c r="A626" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B626" t="s">
         <v>980</v>
@@ -11032,20 +11038,20 @@
         <v>987</v>
       </c>
       <c r="B630" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B631" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B632" t="s">
         <v>990</v>
@@ -11056,20 +11062,20 @@
         <v>991</v>
       </c>
       <c r="B633" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B634" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="635" spans="1:2">
       <c r="A635" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B635" t="s">
         <v>994</v>
@@ -11096,92 +11102,92 @@
         <v>999</v>
       </c>
       <c r="B638" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B639" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B640" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B641" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B642" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B643" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B644" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B645" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B646" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B647" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B648" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="649" spans="1:2">
       <c r="A649" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B649" t="s">
         <v>1011</v>
@@ -11192,36 +11198,36 @@
         <v>1012</v>
       </c>
       <c r="B650" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B651" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B652" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B653" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B654" t="s">
         <v>1017</v>
@@ -11256,12 +11262,12 @@
         <v>1024</v>
       </c>
       <c r="B658" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B659" t="s">
         <v>1026</v>
@@ -11272,12 +11278,12 @@
         <v>1027</v>
       </c>
       <c r="B660" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="661" spans="1:2">
       <c r="A661" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B661" t="s">
         <v>1029</v>
@@ -11288,12 +11294,12 @@
         <v>1030</v>
       </c>
       <c r="B662" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="663" spans="1:2">
       <c r="A663" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B663" t="s">
         <v>1032</v>
@@ -11312,12 +11318,12 @@
         <v>1035</v>
       </c>
       <c r="B665" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="666" spans="1:2">
       <c r="A666" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B666" t="s">
         <v>1037</v>
@@ -11376,36 +11382,36 @@
         <v>1050</v>
       </c>
       <c r="B673" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B674" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B675" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="676" spans="1:2">
       <c r="A676" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B676" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B677" t="s">
         <v>1055</v>
@@ -11424,28 +11430,28 @@
         <v>1058</v>
       </c>
       <c r="B679" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="680" spans="1:2">
       <c r="A680" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B680" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="681" spans="1:2">
       <c r="A681" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B681" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="682" spans="1:2">
       <c r="A682" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B682" t="s">
         <v>1062</v>
@@ -11456,44 +11462,44 @@
         <v>1063</v>
       </c>
       <c r="B683" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="684" spans="1:2">
       <c r="A684" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B684" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B685" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B686" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B687" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="688" spans="1:2">
       <c r="A688" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B688" t="s">
         <v>1069</v>
@@ -11512,28 +11518,28 @@
         <v>1072</v>
       </c>
       <c r="B690" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B691" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B692" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="693" spans="1:2">
       <c r="A693" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B693" t="s">
         <v>1076</v>
@@ -11616,12 +11622,12 @@
         <v>1095</v>
       </c>
       <c r="B703" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B704" t="s">
         <v>1097</v>
@@ -11640,12 +11646,12 @@
         <v>1100</v>
       </c>
       <c r="B706" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="707" spans="1:2">
       <c r="A707" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B707" t="s">
         <v>1102</v>
@@ -11664,12 +11670,12 @@
         <v>1105</v>
       </c>
       <c r="B709" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B710" t="s">
         <v>1107</v>
@@ -11680,20 +11686,20 @@
         <v>1108</v>
       </c>
       <c r="B711" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B712" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B713" t="s">
         <v>1111</v>
@@ -11704,60 +11710,60 @@
         <v>1112</v>
       </c>
       <c r="B714" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B715" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B716" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B717" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B718" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B719" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B720" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B721" t="s">
         <v>1120</v>
@@ -11768,12 +11774,12 @@
         <v>1121</v>
       </c>
       <c r="B722" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="723" spans="1:2">
       <c r="A723" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B723" t="s">
         <v>1123</v>
@@ -11784,20 +11790,20 @@
         <v>1124</v>
       </c>
       <c r="B724" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B725" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B726" t="s">
         <v>1127</v>
@@ -11888,12 +11894,12 @@
         <v>1148</v>
       </c>
       <c r="B737" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="738" spans="1:2">
       <c r="A738" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B738" t="s">
         <v>1150</v>
@@ -11912,12 +11918,12 @@
         <v>1153</v>
       </c>
       <c r="B740" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="741" spans="1:2">
       <c r="A741" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B741" t="s">
         <v>1155</v>
@@ -11936,28 +11942,28 @@
         <v>1158</v>
       </c>
       <c r="B743" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="744" spans="1:2">
       <c r="A744" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B744" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="745" spans="1:2">
       <c r="A745" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B745" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="746" spans="1:2">
       <c r="A746" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B746" t="s">
         <v>1162</v>
@@ -11968,44 +11974,44 @@
         <v>1163</v>
       </c>
       <c r="B747" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B748" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B749" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B750" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B751" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="752" spans="1:2">
       <c r="A752" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B752" t="s">
         <v>1169</v>
@@ -12024,36 +12030,36 @@
         <v>1172</v>
       </c>
       <c r="B754" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B755" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B756" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B757" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="758" spans="1:2">
       <c r="A758" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B758" t="s">
         <v>1177</v>
@@ -12112,12 +12118,12 @@
         <v>1190</v>
       </c>
       <c r="B765" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="766" spans="1:2">
       <c r="A766" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B766" t="s">
         <v>1192</v>
@@ -12144,12 +12150,12 @@
         <v>1197</v>
       </c>
       <c r="B769" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B770" t="s">
         <v>1199</v>
@@ -12160,20 +12166,20 @@
         <v>1200</v>
       </c>
       <c r="B771" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B772" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="773" spans="1:2">
       <c r="A773" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B773" t="s">
         <v>1203</v>
@@ -12213,15 +12219,15 @@
     </row>
     <row r="778" spans="1:2">
       <c r="A778" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B778" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="779" spans="1:2">
       <c r="A779" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B779" t="s">
         <v>1213</v>
@@ -12248,28 +12254,28 @@
         <v>1218</v>
       </c>
       <c r="B782" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="783" spans="1:2">
       <c r="A783" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B783" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B784" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="785" spans="1:2">
       <c r="A785" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B785" t="s">
         <v>1222</v>
@@ -12280,20 +12286,20 @@
         <v>1223</v>
       </c>
       <c r="B786" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="787" spans="1:2">
       <c r="A787" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B787" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="788" spans="1:2">
       <c r="A788" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B788" t="s">
         <v>1226</v>
@@ -12328,28 +12334,28 @@
         <v>1233</v>
       </c>
       <c r="B792" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B793" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B794" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B795" t="s">
         <v>1237</v>
@@ -12368,12 +12374,12 @@
         <v>1240</v>
       </c>
       <c r="B797" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B798" t="s">
         <v>1242</v>
@@ -12384,60 +12390,60 @@
         <v>1243</v>
       </c>
       <c r="B799" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B800" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B801" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B802" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B803" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B804" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B805" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B806" t="s">
         <v>1251</v>
@@ -12448,12 +12454,12 @@
         <v>1252</v>
       </c>
       <c r="B807" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B808" t="s">
         <v>1254</v>
@@ -12520,36 +12526,36 @@
         <v>1269</v>
       </c>
       <c r="B816" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B817" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B818" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B819" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="820" spans="1:2">
       <c r="A820" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B820" t="s">
         <v>1274</v>
@@ -12584,12 +12590,12 @@
         <v>1281</v>
       </c>
       <c r="B824" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B825" t="s">
         <v>1283</v>
@@ -12624,12 +12630,12 @@
         <v>1290</v>
       </c>
       <c r="B829" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B830" t="s">
         <v>1292</v>
@@ -12640,12 +12646,12 @@
         <v>1293</v>
       </c>
       <c r="B831" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="832" spans="1:2">
       <c r="A832" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B832" t="s">
         <v>1295</v>
@@ -12656,12 +12662,12 @@
         <v>1296</v>
       </c>
       <c r="B833" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B834" t="s">
         <v>1298</v>
@@ -12672,12 +12678,12 @@
         <v>1299</v>
       </c>
       <c r="B835" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B836" t="s">
         <v>1301</v>
@@ -12688,23 +12694,23 @@
         <v>1302</v>
       </c>
       <c r="B837" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B838" t="s">
-        <v>723</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B839" t="s">
-        <v>1305</v>
+        <v>725</v>
       </c>
     </row>
     <row r="840" spans="1:2">
@@ -12720,36 +12726,36 @@
         <v>1308</v>
       </c>
       <c r="B841" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B842" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B843" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B844" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B845" t="s">
         <v>1313</v>
@@ -12784,12 +12790,12 @@
         <v>1320</v>
       </c>
       <c r="B849" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B850" t="s">
         <v>1322</v>
@@ -12808,36 +12814,36 @@
         <v>1325</v>
       </c>
       <c r="B852" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B853" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B854" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B855" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B856" t="s">
         <v>1330</v>
@@ -12944,28 +12950,28 @@
         <v>1355</v>
       </c>
       <c r="B869" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B870" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B871" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B872" t="s">
         <v>1359</v>
@@ -12976,36 +12982,36 @@
         <v>1360</v>
       </c>
       <c r="B873" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B874" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B875" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B876" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B877" t="s">
         <v>1365</v>
@@ -13016,28 +13022,28 @@
         <v>1366</v>
       </c>
       <c r="B878" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B879" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B880" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B881" t="s">
         <v>1370</v>
@@ -13064,12 +13070,12 @@
         <v>1375</v>
       </c>
       <c r="B884" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B885" t="s">
         <v>1377</v>
@@ -13104,15 +13110,15 @@
         <v>1384</v>
       </c>
       <c r="B889" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B890" t="s">
         <v>1385</v>
-      </c>
-      <c r="B890" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="891" spans="1:2">
@@ -13120,20 +13126,20 @@
         <v>1387</v>
       </c>
       <c r="B891" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B892" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="B893" t="s">
         <v>1390</v>
@@ -13160,12 +13166,12 @@
         <v>1395</v>
       </c>
       <c r="B896" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B897" t="s">
         <v>1397</v>
@@ -13184,12 +13190,12 @@
         <v>1400</v>
       </c>
       <c r="B899" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B900" t="s">
         <v>1402</v>
@@ -13200,28 +13206,28 @@
         <v>1403</v>
       </c>
       <c r="B901" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B902" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="B903" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B904" t="s">
         <v>1407</v>
@@ -13232,20 +13238,20 @@
         <v>1408</v>
       </c>
       <c r="B905" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="B906" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B907" t="s">
         <v>1411</v>
@@ -13272,20 +13278,20 @@
         <v>1416</v>
       </c>
       <c r="B910" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B911" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B912" t="s">
         <v>1419</v>
@@ -13328,60 +13334,60 @@
         <v>1428</v>
       </c>
       <c r="B917" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B918" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B919" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B920" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B921" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B922" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B923" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B924" t="s">
         <v>1436</v>
@@ -13416,20 +13422,20 @@
         <v>1443</v>
       </c>
       <c r="B928" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B929" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="B930" t="s">
         <v>1446</v>
@@ -13472,20 +13478,20 @@
         <v>1455</v>
       </c>
       <c r="B935" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B936" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="B937" t="s">
         <v>1458</v>
@@ -13520,12 +13526,12 @@
         <v>1465</v>
       </c>
       <c r="B941" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B942" t="s">
         <v>1467</v>
@@ -13544,20 +13550,20 @@
         <v>1470</v>
       </c>
       <c r="B944" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B945" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B946" t="s">
         <v>1473</v>
@@ -13568,12 +13574,12 @@
         <v>1474</v>
       </c>
       <c r="B947" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B948" t="s">
         <v>1476</v>
@@ -13600,12 +13606,12 @@
         <v>1481</v>
       </c>
       <c r="B951" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B952" t="s">
         <v>1483</v>
@@ -13632,36 +13638,36 @@
         <v>1488</v>
       </c>
       <c r="B955" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B956" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B957" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="B958" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B959" t="s">
         <v>1493</v>
@@ -13672,52 +13678,52 @@
         <v>1494</v>
       </c>
       <c r="B960" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="B961" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B962" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B963" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B964" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B965" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B966" t="s">
         <v>1501</v>
@@ -13752,20 +13758,20 @@
         <v>1508</v>
       </c>
       <c r="B970" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="B971" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="B972" t="s">
         <v>1511</v>
@@ -13816,36 +13822,36 @@
         <v>1522</v>
       </c>
       <c r="B978" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B979" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="B980" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B981" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="B982" t="s">
         <v>1527</v>
@@ -13864,12 +13870,12 @@
         <v>1530</v>
       </c>
       <c r="B984" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B985" t="s">
         <v>1532</v>
@@ -13936,20 +13942,20 @@
         <v>1547</v>
       </c>
       <c r="B993" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B994" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B995" t="s">
         <v>1550</v>
@@ -13968,28 +13974,28 @@
         <v>1553</v>
       </c>
       <c r="B997" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B998" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B999" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B1000" t="s">
         <v>1557</v>
@@ -14032,12 +14038,12 @@
         <v>1566</v>
       </c>
       <c r="B1005" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B1006" t="s">
         <v>1568</v>
@@ -14048,12 +14054,12 @@
         <v>1569</v>
       </c>
       <c r="B1007" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B1008" t="s">
         <v>1571</v>
@@ -14072,28 +14078,28 @@
         <v>1574</v>
       </c>
       <c r="B1010" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B1011" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="B1012" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B1013" t="s">
         <v>1578</v>
@@ -14104,12 +14110,12 @@
         <v>1579</v>
       </c>
       <c r="B1014" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B1015" t="s">
         <v>1581</v>
@@ -14128,36 +14134,36 @@
         <v>1584</v>
       </c>
       <c r="B1017" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B1018" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B1019" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B1020" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B1021" t="s">
         <v>1589</v>
@@ -14168,36 +14174,36 @@
         <v>1590</v>
       </c>
       <c r="B1022" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B1023" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B1024" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B1025" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B1026" t="s">
         <v>1595</v>
@@ -14216,36 +14222,36 @@
         <v>1598</v>
       </c>
       <c r="B1028" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B1029" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B1030" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B1031" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B1032" t="s">
         <v>1603</v>
@@ -14264,12 +14270,12 @@
         <v>1606</v>
       </c>
       <c r="B1034" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B1035" t="s">
         <v>1608</v>
@@ -14296,12 +14302,12 @@
         <v>1613</v>
       </c>
       <c r="B1038" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B1039" t="s">
         <v>1615</v>
@@ -14312,20 +14318,20 @@
         <v>1616</v>
       </c>
       <c r="B1040" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B1041" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B1042" t="s">
         <v>1619</v>
@@ -14336,52 +14342,52 @@
         <v>1620</v>
       </c>
       <c r="B1043" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B1044" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="B1045" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B1046" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B1047" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B1048" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="B1049" t="s">
         <v>1627</v>
@@ -14400,12 +14406,12 @@
         <v>1630</v>
       </c>
       <c r="B1051" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="B1052" t="s">
         <v>1632</v>
@@ -14432,20 +14438,20 @@
         <v>1637</v>
       </c>
       <c r="B1055" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="B1056" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B1057" t="s">
         <v>1640</v>
@@ -14472,20 +14478,20 @@
         <v>1645</v>
       </c>
       <c r="B1060" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B1061" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="B1062" t="s">
         <v>1648</v>
@@ -14496,20 +14502,20 @@
         <v>1649</v>
       </c>
       <c r="B1063" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B1064" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="B1065" t="s">
         <v>1652</v>
@@ -14688,12 +14694,12 @@
         <v>1695</v>
       </c>
       <c r="B1087" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B1088" t="s">
         <v>1697</v>
@@ -14704,36 +14710,36 @@
         <v>1698</v>
       </c>
       <c r="B1089" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B1090" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B1091" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B1092" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B1093" t="s">
         <v>1703</v>
@@ -14744,12 +14750,12 @@
         <v>1704</v>
       </c>
       <c r="B1094" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B1095" t="s">
         <v>1706</v>
@@ -14760,28 +14766,28 @@
         <v>1707</v>
       </c>
       <c r="B1096" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B1097" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B1098" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B1099" t="s">
         <v>1711</v>
@@ -14792,20 +14798,20 @@
         <v>1712</v>
       </c>
       <c r="B1100" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="B1101" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="B1102" t="s">
         <v>1715</v>
@@ -14840,20 +14846,20 @@
         <v>1722</v>
       </c>
       <c r="B1106" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="B1107" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="B1108" t="s">
         <v>1725</v>
@@ -14896,12 +14902,12 @@
         <v>1734</v>
       </c>
       <c r="B1113" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="B1114" t="s">
         <v>1736</v>
@@ -14928,12 +14934,12 @@
         <v>1741</v>
       </c>
       <c r="B1117" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="B1118" t="s">
         <v>1743</v>
@@ -14944,20 +14950,20 @@
         <v>1744</v>
       </c>
       <c r="B1119" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="B1120" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="B1121" t="s">
         <v>1747</v>
@@ -14968,12 +14974,12 @@
         <v>1748</v>
       </c>
       <c r="B1122" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B1123" t="s">
         <v>1750</v>
@@ -15000,20 +15006,20 @@
         <v>1755</v>
       </c>
       <c r="B1126" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="B1127" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="B1128" t="s">
         <v>1758</v>
@@ -15168,44 +15174,44 @@
         <v>1795</v>
       </c>
       <c r="B1147" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B1148" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="B1149" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="B1150" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="B1151" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="B1152" t="s">
         <v>1801</v>
@@ -15224,36 +15230,36 @@
         <v>1804</v>
       </c>
       <c r="B1154" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="B1155" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="B1156" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="B1157" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1158" t="s">
         <v>1809</v>
@@ -15264,12 +15270,12 @@
         <v>1810</v>
       </c>
       <c r="B1159" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B1160" t="s">
         <v>1812</v>
@@ -15296,12 +15302,12 @@
         <v>1817</v>
       </c>
       <c r="B1163" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B1164" t="s">
         <v>1819</v>
@@ -15312,12 +15318,12 @@
         <v>1820</v>
       </c>
       <c r="B1165" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="B1166" t="s">
         <v>1822</v>
@@ -15328,12 +15334,12 @@
         <v>1823</v>
       </c>
       <c r="B1167" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1168" t="s">
         <v>1825</v>
@@ -15368,44 +15374,44 @@
         <v>1832</v>
       </c>
       <c r="B1172" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="B1173" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B1174" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1175" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B1176" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="B1177" t="s">
         <v>1838</v>
@@ -15416,28 +15422,28 @@
         <v>1839</v>
       </c>
       <c r="B1178" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="B1179" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="B1180" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="B1181" t="s">
         <v>1843</v>
@@ -15448,36 +15454,36 @@
         <v>1844</v>
       </c>
       <c r="B1182" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="B1183" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="B1184" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="B1185" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="B1186" t="s">
         <v>1849</v>
@@ -15496,12 +15502,12 @@
         <v>1852</v>
       </c>
       <c r="B1188" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B1189" t="s">
         <v>1854</v>
@@ -15512,20 +15518,20 @@
         <v>1855</v>
       </c>
       <c r="B1190" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B1191" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="B1192" t="s">
         <v>1858</v>
@@ -15544,36 +15550,36 @@
         <v>1861</v>
       </c>
       <c r="B1194" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
       <c r="A1195" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1195" t="s">
-        <v>725</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="1196" spans="1:2">
       <c r="A1196" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1196" t="s">
-        <v>1863</v>
+        <v>727</v>
       </c>
     </row>
     <row r="1197" spans="1:2">
       <c r="A1197" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="B1197" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1198" spans="1:2">
       <c r="A1198" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="B1198" t="s">
         <v>1866</v>
@@ -15584,20 +15590,20 @@
         <v>1867</v>
       </c>
       <c r="B1199" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="1200" spans="1:2">
       <c r="A1200" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="B1200" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="1201" spans="1:2">
       <c r="A1201" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="B1201" t="s">
         <v>1870</v>
@@ -15619,8 +15625,16 @@
         <v>1874</v>
       </c>
     </row>
+    <row r="1204" spans="1:2">
+      <c r="A1204" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B1204" t="s">
+        <v>1876</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1203"/>
+  <autoFilter ref="A1:B1204"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
